--- a/jogos_2025-09-05.xlsx
+++ b/jogos_2025-09-05.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK30"/>
+  <dimension ref="A1:AK33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -923,7 +923,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45905.60416666666</v>
+        <v>45905.5625</v>
       </c>
     </row>
     <row r="6">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45905.60416666666</v>
+        <v>45905.5625</v>
       </c>
     </row>
     <row r="7">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45905.60416666666</v>
+        <v>45905.5625</v>
       </c>
     </row>
     <row r="8">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45905.60416666666</v>
+        <v>45905.5625</v>
       </c>
     </row>
     <row r="9">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45905.60416666666</v>
+        <v>45905.5625</v>
       </c>
     </row>
     <row r="10">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45905.60416666666</v>
+        <v>45905.5625</v>
       </c>
     </row>
     <row r="11">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45905.60416666666</v>
+        <v>45905.5625</v>
       </c>
     </row>
     <row r="12">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2391,10 +2391,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2434,27 +2434,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45905.65625</v>
+        <v>45905.64583333334</v>
       </c>
     </row>
     <row r="17">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45905.65625</v>
+        <v>45905.64583333334</v>
       </c>
     </row>
     <row r="18">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2950,27 +2950,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45905.6875</v>
+        <v>45905.65625</v>
       </c>
     </row>
     <row r="21">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45905.70833333334</v>
+        <v>45905.65625</v>
       </c>
     </row>
     <row r="22">
@@ -3208,27 +3208,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45905.70833333334</v>
+        <v>45905.6875</v>
       </c>
     </row>
     <row r="23">
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45905.79166666666</v>
+        <v>45905.70833333334</v>
       </c>
     </row>
     <row r="24">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3595,12 +3595,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45905.83333333334</v>
+        <v>45905.79166666666</v>
       </c>
     </row>
     <row r="26">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45905.85416666666</v>
+        <v>45905.79166666666</v>
       </c>
     </row>
     <row r="27">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45905.875</v>
+        <v>45905.83333333334</v>
       </c>
     </row>
     <row r="28">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45905.89583333334</v>
+        <v>45905.83333333334</v>
       </c>
     </row>
     <row r="29">
@@ -4111,12 +4111,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45905.97916666666</v>
+        <v>45905.85416666666</v>
       </c>
     </row>
     <row r="30">
@@ -4240,126 +4240,513 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Racing Louisville</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Portland Thorns</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" s="3" t="n">
+        <v>45905.875</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>45905</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Ferroviária</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" s="3" t="n">
+        <v>45905.89583333334</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>45905</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>23:30</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Phoenix Rising</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Las Vegas Lights</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" s="3" t="n">
+        <v>45905.97916666666</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>45905</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
         <is>
           <t>Canada Canadian Premier League</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Vancouver FC</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>Valour FC</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="inlineStr">
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK30" s="3" t="n">
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" s="3" t="n">
         <v>45905.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-09-05.xlsx
+++ b/jogos_2025-09-05.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2649,10 +2649,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G33" t="n">

--- a/jogos_2025-09-05.xlsx
+++ b/jogos_2025-09-05.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="G33" t="n">

--- a/jogos_2025-09-05.xlsx
+++ b/jogos_2025-09-05.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2649,10 +2649,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="G26" t="n">

--- a/jogos_2025-09-05.xlsx
+++ b/jogos_2025-09-05.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G28" t="n">

--- a/jogos_2025-09-05.xlsx
+++ b/jogos_2025-09-05.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2649,10 +2649,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G33" t="n">

--- a/jogos_2025-09-05.xlsx
+++ b/jogos_2025-09-05.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2649,10 +2649,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="G33" t="n">

--- a/jogos_2025-09-05.xlsx
+++ b/jogos_2025-09-05.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2649,10 +2649,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G33" t="n">

--- a/jogos_2025-09-05.xlsx
+++ b/jogos_2025-09-05.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK33"/>
+  <dimension ref="A1:AK36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -628,27 +628,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -748,7 +748,7 @@
         <v>0</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>45905.54166666666</v>
+        <v>45905.47916666666</v>
       </c>
     </row>
     <row r="3">
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -886,27 +886,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.21</v>
+        <v>2.93</v>
       </c>
       <c r="M4" t="n">
-        <v>3.05</v>
+        <v>3.34</v>
       </c>
       <c r="N4" t="n">
-        <v>3.1</v>
+        <v>2.18</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>45905.5625</v>
+        <v>45905.54166666666</v>
       </c>
     </row>
     <row r="5">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Real Betis II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Gimnàstic de Tarragona</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45905.5625</v>
+        <v>45905.59375</v>
       </c>
     </row>
     <row r="7">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45905.5625</v>
+        <v>45905.60416666666</v>
       </c>
     </row>
     <row r="8">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45905.5625</v>
+        <v>45905.60416666666</v>
       </c>
     </row>
     <row r="9">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45905.5625</v>
+        <v>45905.60416666666</v>
       </c>
     </row>
     <row r="10">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1710,52 +1710,52 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45905.5625</v>
+        <v>45905.60416666666</v>
       </c>
     </row>
     <row r="11">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45905.5625</v>
+        <v>45905.60416666666</v>
       </c>
     </row>
     <row r="12">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45905.625</v>
+        <v>45905.60416666666</v>
       </c>
     </row>
     <row r="14">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45905.625</v>
+        <v>45905.60416666666</v>
       </c>
     </row>
     <row r="15">
@@ -2305,27 +2305,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45905.64583333334</v>
+        <v>45905.625</v>
       </c>
     </row>
     <row r="16">
@@ -2434,27 +2434,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45905.64583333334</v>
+        <v>45905.625</v>
       </c>
     </row>
     <row r="17">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2649,10 +2649,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45905.65625</v>
+        <v>45905.64583333334</v>
       </c>
     </row>
     <row r="19">
@@ -2821,27 +2821,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2907,10 +2907,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45905.65625</v>
+        <v>45905.64583333334</v>
       </c>
     </row>
     <row r="20">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3208,27 +3208,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45905.6875</v>
+        <v>45905.65625</v>
       </c>
     </row>
     <row r="23">
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45905.70833333334</v>
+        <v>45905.65625</v>
       </c>
     </row>
     <row r="24">
@@ -3466,27 +3466,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45905.79166666666</v>
+        <v>45905.6875</v>
       </c>
     </row>
     <row r="25">
@@ -3595,27 +3595,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45905.79166666666</v>
+        <v>45905.6875</v>
       </c>
     </row>
     <row r="26">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45905.79166666666</v>
+        <v>45905.70833333334</v>
       </c>
     </row>
     <row r="27">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45905.83333333334</v>
+        <v>45905.79166666666</v>
       </c>
     </row>
     <row r="28">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45905.83333333334</v>
+        <v>45905.79166666666</v>
       </c>
     </row>
     <row r="29">
@@ -4111,12 +4111,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45905.85416666666</v>
+        <v>45905.79166666666</v>
       </c>
     </row>
     <row r="30">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45905.875</v>
+        <v>45905.83333333334</v>
       </c>
     </row>
     <row r="31">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45905.89583333334</v>
+        <v>45905.83333333334</v>
       </c>
     </row>
     <row r="32">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4618,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
-        <v>45905.97916666666</v>
+        <v>45905.85416666666</v>
       </c>
     </row>
     <row r="33">
@@ -4627,126 +4627,513 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Racing Louisville</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Portland Thorns</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" s="3" t="n">
+        <v>45905.875</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>45905</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Ferroviária</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK34" s="3" t="n">
+        <v>45905.89583333334</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>45905</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
           <t>23:30</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Canada Canadian Premier League</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Vancouver FC</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Valour FC</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK35" s="3" t="n">
+        <v>45905.97916666666</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>45905</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
         <is>
           <t>USA USL Championship</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Phoenix Rising</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>Las Vegas Lights</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="inlineStr">
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0</v>
-      </c>
-      <c r="X33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK33" s="3" t="n">
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK36" s="3" t="n">
         <v>45905.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-09-05.xlsx
+++ b/jogos_2025-09-05.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK36"/>
+  <dimension ref="A1:AK35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45905.83333333334</v>
+        <v>45905.85416666666</v>
       </c>
     </row>
     <row r="32">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4618,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
-        <v>45905.85416666666</v>
+        <v>45905.875</v>
       </c>
     </row>
     <row r="33">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4747,7 +4747,7 @@
         <v>0</v>
       </c>
       <c r="AK33" s="3" t="n">
-        <v>45905.875</v>
+        <v>45905.89583333334</v>
       </c>
     </row>
     <row r="34">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>45905.89583333334</v>
+        <v>45905.97916666666</v>
       </c>
     </row>
     <row r="35">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5005,135 +5005,6 @@
         <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
-        <v>45905.97916666666</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="n">
-        <v>45905</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Phoenix Rising</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Las Vegas Lights</t>
-        </is>
-      </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" t="n">
-        <v>0</v>
-      </c>
-      <c r="X36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK36" s="3" t="n">
         <v>45905.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-09-05.xlsx
+++ b/jogos_2025-09-05.xlsx
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1581,52 +1581,52 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1710,52 +1710,52 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2778,10 +2778,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2907,10 +2907,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G28" t="n">

--- a/jogos_2025-09-05.xlsx
+++ b/jogos_2025-09-05.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK35"/>
+  <dimension ref="A1:AK36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.5</v>
+        <v>2.21</v>
       </c>
       <c r="M7" t="n">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="N7" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="O7" t="n">
-        <v>3.3</v>
+        <v>2.87</v>
       </c>
       <c r="P7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC7" t="n">
         <v>1.92</v>
       </c>
-      <c r="Q7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="X7" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.12</v>
-      </c>
       <c r="AD7" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1452,52 +1452,52 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1581,52 +1581,52 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2778,10 +2778,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2907,10 +2907,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45905.85416666666</v>
+        <v>45905.83333333334</v>
       </c>
     </row>
     <row r="32">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4618,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
-        <v>45905.875</v>
+        <v>45905.85416666666</v>
       </c>
     </row>
     <row r="33">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4747,7 +4747,7 @@
         <v>0</v>
       </c>
       <c r="AK33" s="3" t="n">
-        <v>45905.89583333334</v>
+        <v>45905.875</v>
       </c>
     </row>
     <row r="34">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>45905.97916666666</v>
+        <v>45905.89583333334</v>
       </c>
     </row>
     <row r="35">
@@ -5005,6 +5005,135 @@
         <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
+        <v>45905.97916666666</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>45905</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Canada Canadian Premier League</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Vancouver FC</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Valour FC</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK36" s="3" t="n">
         <v>45905.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-09-05.xlsx
+++ b/jogos_2025-09-05.xlsx
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2778,10 +2778,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2907,10 +2907,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G29" t="n">

--- a/jogos_2025-09-05.xlsx
+++ b/jogos_2025-09-05.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1452,52 +1452,52 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,28 +2217,28 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2.87</v>
+        <v>2.62</v>
       </c>
       <c r="P14" t="n">
         <v>2.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.9</v>
+        <v>4.61</v>
       </c>
       <c r="R14" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S14" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="T14" t="n">
         <v>3</v>
@@ -2250,28 +2250,28 @@
         <v>1.05</v>
       </c>
       <c r="W14" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="X14" t="n">
         <v>2.8</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AA14" t="n">
         <v>3.9</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2778,10 +2778,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2907,10 +2907,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G36" t="n">

--- a/jogos_2025-09-05.xlsx
+++ b/jogos_2025-09-05.xlsx
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,28 +1701,28 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.87</v>
+        <v>2.62</v>
       </c>
       <c r="P10" t="n">
         <v>2.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.9</v>
+        <v>4.61</v>
       </c>
       <c r="R10" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S10" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="T10" t="n">
         <v>3</v>
@@ -1734,28 +1734,28 @@
         <v>1.05</v>
       </c>
       <c r="W10" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="X10" t="n">
         <v>2.8</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AA10" t="n">
         <v>3.9</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2226,52 +2226,52 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2649,10 +2649,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2907,10 +2907,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4443,10 +4443,10 @@
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y31" t="n">
         <v>0</v>

--- a/jogos_2025-09-05.xlsx
+++ b/jogos_2025-09-05.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.46</v>
+        <v>2.93</v>
       </c>
       <c r="M3" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="N3" t="n">
-        <v>2.46</v>
+        <v>2.18</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.93</v>
+        <v>2.46</v>
       </c>
       <c r="M4" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="N4" t="n">
-        <v>2.18</v>
+        <v>2.46</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1710,52 +1710,52 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,28 +1959,28 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2.87</v>
+        <v>2.62</v>
       </c>
       <c r="P12" t="n">
         <v>2.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.9</v>
+        <v>4.61</v>
       </c>
       <c r="R12" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S12" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="T12" t="n">
         <v>3</v>
@@ -1992,28 +1992,28 @@
         <v>1.05</v>
       </c>
       <c r="W12" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="X12" t="n">
         <v>2.8</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AA12" t="n">
         <v>3.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2649,10 +2649,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2778,10 +2778,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.49</v>
+        <v>2.85</v>
       </c>
       <c r="M21" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="N21" t="n">
-        <v>5.4</v>
+        <v>2.29</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.8</v>
+        <v>1.49</v>
       </c>
       <c r="M23" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="N23" t="n">
-        <v>1.79</v>
+        <v>5.4</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>

--- a/jogos_2025-09-05.xlsx
+++ b/jogos_2025-09-05.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.93</v>
+        <v>2.46</v>
       </c>
       <c r="M3" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="N3" t="n">
-        <v>2.18</v>
+        <v>2.46</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.46</v>
+        <v>2.93</v>
       </c>
       <c r="M4" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="N4" t="n">
-        <v>2.46</v>
+        <v>2.18</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.5</v>
+        <v>2.21</v>
       </c>
       <c r="M7" t="n">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="N7" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="O7" t="n">
-        <v>3.3</v>
+        <v>2.87</v>
       </c>
       <c r="P7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC7" t="n">
         <v>1.92</v>
       </c>
-      <c r="Q7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="X7" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.12</v>
-      </c>
       <c r="AD7" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1839,52 +1839,52 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O12" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2778,10 +2778,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2907,10 +2907,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.8</v>
+        <v>1.49</v>
       </c>
       <c r="M20" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="N20" t="n">
-        <v>1.79</v>
+        <v>5.4</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.85</v>
+        <v>3.8</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="N21" t="n">
-        <v>2.29</v>
+        <v>1.79</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="G36" t="n">

--- a/jogos_2025-09-05.xlsx
+++ b/jogos_2025-09-05.xlsx
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2649,10 +2649,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2907,10 +2907,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="G29" t="n">

--- a/jogos_2025-09-05.xlsx
+++ b/jogos_2025-09-05.xlsx
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1065,52 +1065,52 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Real Betis II</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gimnàstic de Tarragona</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45905.59375</v>
+        <v>45905.5625</v>
       </c>
     </row>
     <row r="7">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45905.60416666666</v>
+        <v>45905.5625</v>
       </c>
     </row>
     <row r="8">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.21</v>
+        <v>2.5</v>
       </c>
       <c r="M8" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="N8" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="O8" t="n">
-        <v>2.87</v>
+        <v>3.3</v>
       </c>
       <c r="P8" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="R8" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="S8" t="n">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="T8" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="U8" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="V8" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="W8" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="X8" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.16</v>
+        <v>2.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.92</v>
+        <v>2.12</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45905.60416666666</v>
+        <v>45905.5625</v>
       </c>
     </row>
     <row r="9">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45905.60416666666</v>
+        <v>45905.5625</v>
       </c>
     </row>
     <row r="10">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45905.60416666666</v>
+        <v>45905.5625</v>
       </c>
     </row>
     <row r="11">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1839,52 +1839,52 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45905.60416666666</v>
+        <v>45905.5625</v>
       </c>
     </row>
     <row r="12">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45905.60416666666</v>
+        <v>45905.5625</v>
       </c>
     </row>
     <row r="13">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Real Betis II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Gimnàstic de Tarragona</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45905.60416666666</v>
+        <v>45905.59375</v>
       </c>
     </row>
     <row r="14">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.8</v>
+        <v>2.85</v>
       </c>
       <c r="M21" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="N21" t="n">
-        <v>1.79</v>
+        <v>2.29</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.49</v>
+        <v>3.8</v>
       </c>
       <c r="M23" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="N23" t="n">
-        <v>5.4</v>
+        <v>1.79</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="M25" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="N25" t="n">
-        <v>2.85</v>
+        <v>3.09</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4314,10 +4314,10 @@
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4443,10 +4443,10 @@
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G36" t="n">

--- a/jogos_2025-09-05.xlsx
+++ b/jogos_2025-09-05.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK36"/>
+  <dimension ref="A1:AK38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.46</v>
+        <v>2.93</v>
       </c>
       <c r="M3" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="N3" t="n">
-        <v>2.46</v>
+        <v>2.18</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.93</v>
+        <v>2.46</v>
       </c>
       <c r="M4" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="N4" t="n">
-        <v>2.18</v>
+        <v>2.46</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1065,52 +1065,52 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1323,52 +1323,52 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1568,65 +1568,65 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="M14" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="N14" t="n">
-        <v>5.2</v>
+        <v>4.1</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45905.625</v>
+        <v>45905.60416666666</v>
       </c>
     </row>
     <row r="16">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2649,10 +2649,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45905.64583333334</v>
+        <v>45905.625</v>
       </c>
     </row>
     <row r="18">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2950,27 +2950,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="M20" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="N20" t="n">
-        <v>5.4</v>
+        <v>4.4</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3036,10 +3036,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45905.65625</v>
+        <v>45905.64583333334</v>
       </c>
     </row>
     <row r="21">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.85</v>
+        <v>1.49</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="N21" t="n">
-        <v>2.29</v>
+        <v>5.4</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3466,27 +3466,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45905.6875</v>
+        <v>45905.65625</v>
       </c>
     </row>
     <row r="25">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3724,27 +3724,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45905.70833333334</v>
+        <v>45905.6875</v>
       </c>
     </row>
     <row r="27">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45905.79166666666</v>
+        <v>45905.70833333334</v>
       </c>
     </row>
     <row r="28">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45905.79166666666</v>
+        <v>45905.70833333334</v>
       </c>
     </row>
     <row r="29">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4314,10 +4314,10 @@
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
         <v>0</v>
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45905.83333333334</v>
+        <v>45905.79166666666</v>
       </c>
     </row>
     <row r="31">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45905.83333333334</v>
+        <v>45905.79166666666</v>
       </c>
     </row>
     <row r="32">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4618,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
-        <v>45905.85416666666</v>
+        <v>45905.83333333334</v>
       </c>
     </row>
     <row r="33">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="M33" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="N33" t="n">
-        <v>2.17</v>
+        <v>2.6</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4701,10 +4701,10 @@
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y33" t="n">
         <v>0</v>
@@ -4747,7 +4747,7 @@
         <v>0</v>
       </c>
       <c r="AK33" s="3" t="n">
-        <v>45905.875</v>
+        <v>45905.83333333334</v>
       </c>
     </row>
     <row r="34">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>45905.89583333334</v>
+        <v>45905.85416666666</v>
       </c>
     </row>
     <row r="35">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5005,7 +5005,7 @@
         <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
-        <v>45905.97916666666</v>
+        <v>45905.875</v>
       </c>
     </row>
     <row r="36">
@@ -5014,126 +5014,384 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Ferroviária</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK36" s="3" t="n">
+        <v>45905.89583333334</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>45905</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
           <t>23:30</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>USA USL Championship</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Phoenix Rising</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>Las Vegas Lights</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="inlineStr">
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" t="n">
-        <v>0</v>
-      </c>
-      <c r="X36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK36" s="3" t="n">
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK37" s="3" t="n">
+        <v>45905.97916666666</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>45905</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Canada Canadian Premier League</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Vancouver FC</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Valour FC</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" s="3" t="n">
         <v>45905.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-09-05.xlsx
+++ b/jogos_2025-09-05.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK38"/>
+  <dimension ref="A1:AK39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1323,52 +1323,52 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,28 +1959,28 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2.87</v>
+        <v>2.62</v>
       </c>
       <c r="P12" t="n">
         <v>2.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.9</v>
+        <v>4.61</v>
       </c>
       <c r="R12" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S12" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="T12" t="n">
         <v>3</v>
@@ -1992,28 +1992,28 @@
         <v>1.05</v>
       </c>
       <c r="W12" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="X12" t="n">
         <v>2.8</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AA12" t="n">
         <v>3.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="N14" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="M15" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>5.2</v>
+        <v>4.1</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3036,10 +3036,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3079,27 +3079,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="M21" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="N21" t="n">
-        <v>5.4</v>
+        <v>4.4</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3165,10 +3165,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45905.65625</v>
+        <v>45905.64583333334</v>
       </c>
     </row>
     <row r="22">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.85</v>
+        <v>1.49</v>
       </c>
       <c r="M22" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="N22" t="n">
-        <v>2.29</v>
+        <v>5.4</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.8</v>
+        <v>2.85</v>
       </c>
       <c r="M24" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="N24" t="n">
-        <v>1.79</v>
+        <v>2.29</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3595,27 +3595,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45905.6875</v>
+        <v>45905.65625</v>
       </c>
     </row>
     <row r="26">
@@ -3853,27 +3853,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45905.70833333334</v>
+        <v>45905.6875</v>
       </c>
     </row>
     <row r="28">
@@ -4111,12 +4111,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45905.79166666666</v>
+        <v>45905.70833333334</v>
       </c>
     </row>
     <row r="30">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4498,7 +4498,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4618,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
-        <v>45905.83333333334</v>
+        <v>45905.79166666666</v>
       </c>
     </row>
     <row r="33">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4701,10 +4701,10 @@
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
         <v>0</v>
@@ -4756,12 +4756,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4830,10 +4830,10 @@
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y34" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>45905.85416666666</v>
+        <v>45905.83333333334</v>
       </c>
     </row>
     <row r="35">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5005,7 +5005,7 @@
         <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
-        <v>45905.875</v>
+        <v>45905.85416666666</v>
       </c>
     </row>
     <row r="36">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45905.89583333334</v>
+        <v>45905.875</v>
       </c>
     </row>
     <row r="37">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="AK37" s="3" t="n">
-        <v>45905.97916666666</v>
+        <v>45905.89583333334</v>
       </c>
     </row>
     <row r="38">
@@ -5392,6 +5392,135 @@
         <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
+        <v>45905.97916666666</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>45905</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Phoenix Rising</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Las Vegas Lights</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="M39" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N39" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK39" s="3" t="n">
         <v>45905.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-09-05.xlsx
+++ b/jogos_2025-09-05.xlsx
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1052,65 +1052,65 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1181,65 +1181,65 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1452,52 +1452,52 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1968,52 +1968,52 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,14 +2217,14 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="M14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N14" t="n">
         <v>4.1</v>
       </c>
-      <c r="N14" t="n">
-        <v>5.6</v>
-      </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="N15" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.65</v>
+        <v>1.58</v>
       </c>
       <c r="M18" t="n">
-        <v>3.15</v>
+        <v>3.9</v>
       </c>
       <c r="N18" t="n">
-        <v>2.48</v>
+        <v>4.4</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,16 +2772,16 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3165,10 +3165,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.49</v>
+        <v>5.2</v>
       </c>
       <c r="M22" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="N22" t="n">
-        <v>5.4</v>
+        <v>1.51</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>5.2</v>
+        <v>3.8</v>
       </c>
       <c r="M23" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="N23" t="n">
-        <v>1.51</v>
+        <v>1.79</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.85</v>
+        <v>1.49</v>
       </c>
       <c r="M24" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="N24" t="n">
-        <v>2.29</v>
+        <v>5.4</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.8</v>
+        <v>2.85</v>
       </c>
       <c r="M25" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="N25" t="n">
-        <v>1.79</v>
+        <v>2.29</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>

--- a/jogos_2025-09-05.xlsx
+++ b/jogos_2025-09-05.xlsx
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,28 +1056,28 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2.87</v>
+        <v>2.62</v>
       </c>
       <c r="P5" t="n">
         <v>2.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.9</v>
+        <v>4.61</v>
       </c>
       <c r="R5" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S5" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="T5" t="n">
         <v>3</v>
@@ -1089,28 +1089,28 @@
         <v>1.05</v>
       </c>
       <c r="W5" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="X5" t="n">
         <v>2.8</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AA5" t="n">
         <v>3.9</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1452,52 +1452,52 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.58</v>
+        <v>2.65</v>
       </c>
       <c r="M18" t="n">
-        <v>3.9</v>
+        <v>3.15</v>
       </c>
       <c r="N18" t="n">
-        <v>4.4</v>
+        <v>2.48</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,16 +2772,16 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.65</v>
+        <v>1.58</v>
       </c>
       <c r="M19" t="n">
-        <v>3.15</v>
+        <v>3.9</v>
       </c>
       <c r="N19" t="n">
-        <v>2.48</v>
+        <v>4.4</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,16 +2901,16 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>5.2</v>
+        <v>3.8</v>
       </c>
       <c r="M22" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="N22" t="n">
-        <v>1.51</v>
+        <v>1.79</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.8</v>
+        <v>1.49</v>
       </c>
       <c r="M23" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="N23" t="n">
-        <v>1.79</v>
+        <v>5.4</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.49</v>
+        <v>2.85</v>
       </c>
       <c r="M24" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="N24" t="n">
-        <v>5.4</v>
+        <v>2.29</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.85</v>
+        <v>5.2</v>
       </c>
       <c r="M25" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="N25" t="n">
-        <v>2.29</v>
+        <v>1.51</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>

--- a/jogos_2025-09-05.xlsx
+++ b/jogos_2025-09-05.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.93</v>
+        <v>2.46</v>
       </c>
       <c r="M3" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="N3" t="n">
-        <v>2.18</v>
+        <v>2.46</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.46</v>
+        <v>2.93</v>
       </c>
       <c r="M4" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="N4" t="n">
-        <v>2.46</v>
+        <v>2.18</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1065,52 +1065,52 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2.87</v>
+        <v>2.62</v>
       </c>
       <c r="P11" t="n">
         <v>2.05</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.9</v>
+        <v>4.61</v>
       </c>
       <c r="R11" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S11" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="T11" t="n">
         <v>3</v>
@@ -1863,28 +1863,28 @@
         <v>1.05</v>
       </c>
       <c r="W11" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="X11" t="n">
         <v>2.8</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AA11" t="n">
         <v>3.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.58</v>
+        <v>2.7</v>
       </c>
       <c r="M19" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="N19" t="n">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,16 +2901,16 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3165,10 +3165,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.8</v>
+        <v>2.95</v>
       </c>
       <c r="M22" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N22" t="n">
-        <v>1.79</v>
+        <v>2.3</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.49</v>
+        <v>3.95</v>
       </c>
       <c r="M23" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="N23" t="n">
-        <v>5.4</v>
+        <v>1.8</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.85</v>
+        <v>1.5</v>
       </c>
       <c r="M24" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="N24" t="n">
-        <v>2.29</v>
+        <v>5.5</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.82</v>
+        <v>2.2</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="M25" t="n">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="N25" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="M36" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N36" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="M39" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="N39" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>

--- a/jogos_2025-09-05.xlsx
+++ b/jogos_2025-09-05.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.46</v>
+        <v>2.93</v>
       </c>
       <c r="M3" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="N3" t="n">
-        <v>2.46</v>
+        <v>2.18</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.93</v>
+        <v>2.46</v>
       </c>
       <c r="M4" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="N4" t="n">
-        <v>2.18</v>
+        <v>2.46</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O11" t="n">
-        <v>2.62</v>
+        <v>3.3</v>
       </c>
       <c r="P11" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.61</v>
+        <v>3.6</v>
       </c>
       <c r="R11" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="S11" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="T11" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="U11" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="V11" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="W11" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="X11" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.17</v>
+        <v>2.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AC11" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.78</v>
+        <v>1.45</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1968,52 +1968,52 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2778,10 +2778,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.58</v>
+        <v>2.7</v>
       </c>
       <c r="M21" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="N21" t="n">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,16 +3159,16 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.95</v>
+        <v>5.5</v>
       </c>
       <c r="M22" t="n">
-        <v>3.3</v>
+        <v>4.15</v>
       </c>
       <c r="N22" t="n">
-        <v>2.3</v>
+        <v>1.52</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>5.5</v>
+        <v>2.95</v>
       </c>
       <c r="M25" t="n">
-        <v>4.15</v>
+        <v>3.3</v>
       </c>
       <c r="N25" t="n">
-        <v>1.52</v>
+        <v>2.3</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="M34" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="N34" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4830,10 +4830,10 @@
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="X34" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Y34" t="n">
         <v>0</v>
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>

--- a/jogos_2025-09-05.xlsx
+++ b/jogos_2025-09-05.xlsx
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1439,65 +1439,65 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.3</v>
+        <v>2.62</v>
       </c>
       <c r="P11" t="n">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.6</v>
+        <v>4.61</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="S11" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="T11" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="U11" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="V11" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="W11" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="X11" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.5</v>
+        <v>2.17</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.45</v>
+        <v>1.78</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1968,52 +1968,52 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="N14" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,14 +2346,14 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="M15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N15" t="n">
         <v>4.1</v>
       </c>
-      <c r="N15" t="n">
-        <v>5.6</v>
-      </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2778,10 +2778,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2907,10 +2907,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.5</v>
+        <v>2.95</v>
       </c>
       <c r="M24" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="N24" t="n">
-        <v>5.5</v>
+        <v>2.3</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.95</v>
+        <v>1.5</v>
       </c>
       <c r="M25" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="N25" t="n">
-        <v>2.3</v>
+        <v>5.5</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>

--- a/jogos_2025-09-05.xlsx
+++ b/jogos_2025-09-05.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.93</v>
+        <v>2.46</v>
       </c>
       <c r="M3" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="N3" t="n">
-        <v>2.18</v>
+        <v>2.46</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.46</v>
+        <v>2.93</v>
       </c>
       <c r="M4" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="N4" t="n">
-        <v>2.46</v>
+        <v>2.18</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.3</v>
+        <v>2.62</v>
       </c>
       <c r="P6" t="n">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.6</v>
+        <v>4.61</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="S6" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="T6" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="U6" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="V6" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="W6" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="X6" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.5</v>
+        <v>2.17</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.45</v>
+        <v>1.78</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1439,65 +1439,65 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O11" t="n">
-        <v>2.62</v>
+        <v>2.87</v>
       </c>
       <c r="P11" t="n">
         <v>2.05</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.61</v>
+        <v>3.9</v>
       </c>
       <c r="R11" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S11" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="T11" t="n">
         <v>3</v>
@@ -1863,28 +1863,28 @@
         <v>1.05</v>
       </c>
       <c r="W11" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="X11" t="n">
         <v>2.8</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AA11" t="n">
         <v>3.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AC11" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,14 +2217,14 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="M14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N14" t="n">
         <v>4.1</v>
       </c>
-      <c r="N14" t="n">
-        <v>5.6</v>
-      </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.85</v>
+        <v>1.99</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.95</v>
+        <v>1.76</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N15" t="n">
-        <v>4.1</v>
+        <v>3.89</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2778,10 +2778,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2907,10 +2907,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>5.5</v>
+        <v>3.95</v>
       </c>
       <c r="M22" t="n">
-        <v>4.15</v>
+        <v>3.7</v>
       </c>
       <c r="N22" t="n">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.95</v>
+        <v>1.5</v>
       </c>
       <c r="M23" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="N23" t="n">
-        <v>1.8</v>
+        <v>5.5</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.82</v>
+        <v>1.6</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="M25" t="n">
-        <v>4.3</v>
+        <v>4.15</v>
       </c>
       <c r="N25" t="n">
-        <v>5.5</v>
+        <v>1.52</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>

--- a/jogos_2025-09-05.xlsx
+++ b/jogos_2025-09-05.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.46</v>
+        <v>2.93</v>
       </c>
       <c r="M3" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="N3" t="n">
-        <v>2.46</v>
+        <v>2.18</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.93</v>
+        <v>2.46</v>
       </c>
       <c r="M4" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="N4" t="n">
-        <v>2.18</v>
+        <v>2.46</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Z4" t="n">
         <v>1.8</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.89</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -1194,52 +1194,52 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1439,65 +1439,65 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1710,52 +1710,52 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2778,10 +2778,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.7</v>
+        <v>1.58</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="N20" t="n">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,16 +3030,16 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45905.64583333334</v>
+        <v>45905.65625</v>
       </c>
     </row>
     <row r="22">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.95</v>
+        <v>2.67</v>
       </c>
       <c r="M22" t="n">
-        <v>3.7</v>
+        <v>3.02</v>
       </c>
       <c r="N22" t="n">
-        <v>1.8</v>
+        <v>2.42</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.5</v>
+        <v>2.89</v>
       </c>
       <c r="M23" t="n">
-        <v>4.3</v>
+        <v>3.18</v>
       </c>
       <c r="N23" t="n">
-        <v>5.5</v>
+        <v>2.18</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.95</v>
+        <v>4.8</v>
       </c>
       <c r="M24" t="n">
-        <v>3.3</v>
+        <v>3.84</v>
       </c>
       <c r="N24" t="n">
-        <v>2.3</v>
+        <v>1.54</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>5.5</v>
+        <v>1.48</v>
       </c>
       <c r="M25" t="n">
-        <v>4.15</v>
+        <v>3.94</v>
       </c>
       <c r="N25" t="n">
-        <v>1.52</v>
+        <v>5.2</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="M30" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="N30" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4314,10 +4314,10 @@
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4701,10 +4701,10 @@
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4830,10 +4830,10 @@
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
         <v>0</v>
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="M37" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N37" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>

--- a/jogos_2025-09-05.xlsx
+++ b/jogos_2025-09-05.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK39"/>
+  <dimension ref="A1:AK38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.3</v>
+        <v>2.62</v>
       </c>
       <c r="P8" t="n">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.6</v>
+        <v>4.61</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="S8" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="T8" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="U8" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="V8" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="W8" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="X8" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.5</v>
+        <v>2.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.45</v>
+        <v>1.78</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1710,52 +1710,52 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N14" t="n">
-        <v>4.1</v>
+        <v>3.89</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45905.60416666666</v>
+        <v>45905.625</v>
       </c>
     </row>
     <row r="16">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2563,27 +2563,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45905.625</v>
+        <v>45905.64583333334</v>
       </c>
     </row>
     <row r="18">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2778,10 +2778,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2950,27 +2950,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.58</v>
+        <v>4.8</v>
       </c>
       <c r="M20" t="n">
-        <v>3.9</v>
+        <v>3.84</v>
       </c>
       <c r="N20" t="n">
-        <v>4.4</v>
+        <v>1.54</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,16 +3030,16 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45905.64583333334</v>
+        <v>45905.65625</v>
       </c>
     </row>
     <row r="21">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.66</v>
+        <v>2.89</v>
       </c>
       <c r="M21" t="n">
-        <v>3.55</v>
+        <v>3.18</v>
       </c>
       <c r="N21" t="n">
-        <v>1.77</v>
+        <v>2.18</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.67</v>
+        <v>3.66</v>
       </c>
       <c r="M22" t="n">
-        <v>3.02</v>
+        <v>3.55</v>
       </c>
       <c r="N22" t="n">
-        <v>2.42</v>
+        <v>1.77</v>
       </c>
       <c r="O22" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Z22" t="n">
         <v>1.89</v>
       </c>
-      <c r="Z22" t="n">
-        <v>1.81</v>
-      </c>
       <c r="AA22" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.89</v>
+        <v>2.67</v>
       </c>
       <c r="M23" t="n">
-        <v>3.18</v>
+        <v>3.02</v>
       </c>
       <c r="N23" t="n">
-        <v>2.18</v>
+        <v>2.42</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4.8</v>
+        <v>1.48</v>
       </c>
       <c r="M24" t="n">
-        <v>3.84</v>
+        <v>3.94</v>
       </c>
       <c r="N24" t="n">
-        <v>1.54</v>
+        <v>5.2</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3595,27 +3595,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.48</v>
+        <v>2.15</v>
       </c>
       <c r="M25" t="n">
-        <v>3.94</v>
+        <v>3.55</v>
       </c>
       <c r="N25" t="n">
-        <v>5.2</v>
+        <v>3.09</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="Z25" t="n">
         <v>2.2</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45905.65625</v>
+        <v>45905.6875</v>
       </c>
     </row>
     <row r="26">
@@ -3853,27 +3853,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45905.6875</v>
+        <v>45905.70833333334</v>
       </c>
     </row>
     <row r="28">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4111,7 +4111,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="M29" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="N29" t="n">
-        <v>3.45</v>
+        <v>3.86</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4185,16 +4185,16 @@
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45905.70833333334</v>
+        <v>45905.79166666666</v>
       </c>
     </row>
     <row r="30">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="M30" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="N30" t="n">
-        <v>3.75</v>
+        <v>2.8</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4314,16 +4314,16 @@
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4498,7 +4498,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4572,10 +4572,10 @@
         <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y32" t="n">
         <v>0</v>
@@ -4618,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
-        <v>45905.79166666666</v>
+        <v>45905.83333333334</v>
       </c>
     </row>
     <row r="33">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4701,10 +4701,10 @@
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
         <v>0</v>
@@ -4756,12 +4756,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>45905.83333333334</v>
+        <v>45905.85416666666</v>
       </c>
     </row>
     <row r="35">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5005,7 +5005,7 @@
         <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
-        <v>45905.85416666666</v>
+        <v>45905.875</v>
       </c>
     </row>
     <row r="36">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.1</v>
+        <v>1.52</v>
       </c>
       <c r="M36" t="n">
-        <v>3.25</v>
+        <v>3.37</v>
       </c>
       <c r="N36" t="n">
-        <v>2.25</v>
+        <v>6</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45905.875</v>
+        <v>45905.89583333334</v>
       </c>
     </row>
     <row r="37">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="M37" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="N37" t="n">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="AK37" s="3" t="n">
-        <v>45905.89583333334</v>
+        <v>45905.97916666666</v>
       </c>
     </row>
     <row r="38">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5392,135 +5392,6 @@
         <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45905.97916666666</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="n">
-        <v>45905</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Canada Canadian Premier League</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Vancouver FC</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Valour FC</t>
-        </is>
-      </c>
-      <c r="G39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK39" s="3" t="n">
         <v>45905.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-09-05.xlsx
+++ b/jogos_2025-09-05.xlsx
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1052,65 +1052,65 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1452,52 +1452,52 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.3</v>
+        <v>2.62</v>
       </c>
       <c r="P11" t="n">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.6</v>
+        <v>4.61</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="S11" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="T11" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="U11" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="V11" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="W11" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="X11" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.5</v>
+        <v>2.17</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.45</v>
+        <v>1.78</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2778,10 +2778,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2907,10 +2907,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.89</v>
+        <v>3.66</v>
       </c>
       <c r="M21" t="n">
-        <v>3.18</v>
+        <v>3.55</v>
       </c>
       <c r="N21" t="n">
-        <v>2.18</v>
+        <v>1.77</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.66</v>
+        <v>2.67</v>
       </c>
       <c r="M22" t="n">
-        <v>3.55</v>
+        <v>3.02</v>
       </c>
       <c r="N22" t="n">
-        <v>1.77</v>
+        <v>2.42</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Y22" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Z22" t="n">
         <v>1.81</v>
       </c>
-      <c r="Z22" t="n">
-        <v>1.89</v>
-      </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.67</v>
+        <v>1.48</v>
       </c>
       <c r="M23" t="n">
-        <v>3.02</v>
+        <v>3.94</v>
       </c>
       <c r="N23" t="n">
-        <v>2.42</v>
+        <v>5.2</v>
       </c>
       <c r="O23" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.89</v>
+        <v>1.6</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.81</v>
+        <v>2.2</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.48</v>
+        <v>2.89</v>
       </c>
       <c r="M24" t="n">
-        <v>3.94</v>
+        <v>3.18</v>
       </c>
       <c r="N24" t="n">
-        <v>5.2</v>
+        <v>2.18</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,49 +4152,49 @@
         </is>
       </c>
       <c r="L29" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
         <v>1.9</v>
       </c>
-      <c r="M29" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="N29" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="X29" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>2.38</v>
-      </c>
       <c r="Z29" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,49 +4281,49 @@
         </is>
       </c>
       <c r="L30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M30" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X30" t="n">
         <v>2.35</v>
       </c>
-      <c r="M30" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N30" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
       <c r="Y30" t="n">
-        <v>1.9</v>
+        <v>2.38</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>

--- a/jogos_2025-09-05.xlsx
+++ b/jogos_2025-09-05.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.93</v>
+        <v>2.46</v>
       </c>
       <c r="M3" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="N3" t="n">
-        <v>2.18</v>
+        <v>2.46</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Z3" t="n">
         <v>1.8</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.89</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.46</v>
+        <v>2.93</v>
       </c>
       <c r="M4" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="N4" t="n">
-        <v>2.46</v>
+        <v>2.18</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z4" t="n">
         <v>1.89</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.8</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.3</v>
+        <v>2.62</v>
       </c>
       <c r="P5" t="n">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.6</v>
+        <v>4.61</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="S5" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="T5" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="V5" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="W5" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="X5" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.5</v>
+        <v>2.17</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.45</v>
+        <v>1.78</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O11" t="n">
-        <v>2.62</v>
+        <v>2.87</v>
       </c>
       <c r="P11" t="n">
         <v>2.05</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.61</v>
+        <v>3.9</v>
       </c>
       <c r="R11" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S11" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="T11" t="n">
         <v>3</v>
@@ -1863,28 +1863,28 @@
         <v>1.05</v>
       </c>
       <c r="W11" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="X11" t="n">
         <v>2.8</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AA11" t="n">
         <v>3.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AC11" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2778,10 +2778,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2907,10 +2907,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4.8</v>
+        <v>2.67</v>
       </c>
       <c r="M20" t="n">
-        <v>3.84</v>
+        <v>3.02</v>
       </c>
       <c r="N20" t="n">
-        <v>1.54</v>
+        <v>2.42</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.66</v>
+        <v>1.48</v>
       </c>
       <c r="M21" t="n">
-        <v>3.55</v>
+        <v>3.94</v>
       </c>
       <c r="N21" t="n">
-        <v>1.77</v>
+        <v>5.2</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.81</v>
+        <v>1.6</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.67</v>
+        <v>4.8</v>
       </c>
       <c r="M22" t="n">
-        <v>3.02</v>
+        <v>3.84</v>
       </c>
       <c r="N22" t="n">
-        <v>2.42</v>
+        <v>1.54</v>
       </c>
       <c r="O22" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.48</v>
+        <v>3.66</v>
       </c>
       <c r="M23" t="n">
-        <v>3.94</v>
+        <v>3.55</v>
       </c>
       <c r="N23" t="n">
-        <v>5.2</v>
+        <v>1.77</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.6</v>
+        <v>1.81</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.2</v>
+        <v>1.89</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,49 +4152,49 @@
         </is>
       </c>
       <c r="L29" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M29" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X29" t="n">
         <v>2.35</v>
       </c>
-      <c r="M29" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N29" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
       <c r="Y29" t="n">
-        <v>1.9</v>
+        <v>2.38</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,49 +4281,49 @@
         </is>
       </c>
       <c r="L30" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
         <v>1.9</v>
       </c>
-      <c r="M30" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="N30" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="X30" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>2.38</v>
-      </c>
       <c r="Z30" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>

--- a/jogos_2025-09-05.xlsx
+++ b/jogos_2025-09-05.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK38"/>
+  <dimension ref="A1:AK37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.46</v>
+        <v>2.93</v>
       </c>
       <c r="M3" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="N3" t="n">
-        <v>2.46</v>
+        <v>2.18</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z3" t="n">
         <v>1.89</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.8</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.93</v>
+        <v>2.46</v>
       </c>
       <c r="M4" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="N4" t="n">
-        <v>2.18</v>
+        <v>2.46</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Z4" t="n">
         <v>1.8</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.89</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1065,52 +1065,52 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1194,52 +1194,52 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1310,65 +1310,65 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.21</v>
+        <v>2.5</v>
       </c>
       <c r="M11" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="N11" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="O11" t="n">
-        <v>2.87</v>
+        <v>3.3</v>
       </c>
       <c r="P11" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="R11" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="S11" t="n">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="T11" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="U11" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="V11" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="W11" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="X11" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.16</v>
+        <v>2.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.92</v>
+        <v>2.12</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2649,10 +2649,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2778,10 +2778,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.67</v>
+        <v>4.8</v>
       </c>
       <c r="M20" t="n">
-        <v>3.02</v>
+        <v>3.84</v>
       </c>
       <c r="N20" t="n">
-        <v>2.42</v>
+        <v>1.54</v>
       </c>
       <c r="O20" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.48</v>
+        <v>3.66</v>
       </c>
       <c r="M21" t="n">
-        <v>3.94</v>
+        <v>3.55</v>
       </c>
       <c r="N21" t="n">
-        <v>5.2</v>
+        <v>1.77</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.6</v>
+        <v>1.81</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.2</v>
+        <v>1.89</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4.8</v>
+        <v>1.48</v>
       </c>
       <c r="M22" t="n">
-        <v>3.84</v>
+        <v>3.94</v>
       </c>
       <c r="N22" t="n">
-        <v>1.54</v>
+        <v>5.2</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.66</v>
+        <v>2.89</v>
       </c>
       <c r="M23" t="n">
-        <v>3.55</v>
+        <v>3.18</v>
       </c>
       <c r="N23" t="n">
-        <v>1.77</v>
+        <v>2.18</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.89</v>
+        <v>2.67</v>
       </c>
       <c r="M24" t="n">
-        <v>3.18</v>
+        <v>3.02</v>
       </c>
       <c r="N24" t="n">
-        <v>2.18</v>
+        <v>2.42</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3982,12 +3982,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.02</v>
+        <v>2.35</v>
       </c>
       <c r="M28" t="n">
-        <v>2.99</v>
+        <v>3.3</v>
       </c>
       <c r="N28" t="n">
-        <v>3.45</v>
+        <v>2.8</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.12</v>
+        <v>1.9</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45905.70833333334</v>
+        <v>45905.79166666666</v>
       </c>
     </row>
     <row r="29">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4185,16 +4185,16 @@
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,49 +4281,49 @@
         </is>
       </c>
       <c r="L30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M30" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X30" t="n">
         <v>2.35</v>
       </c>
-      <c r="M30" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N30" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
       <c r="Y30" t="n">
-        <v>1.9</v>
+        <v>2.38</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4369,7 +4369,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45905.79166666666</v>
+        <v>45905.83333333334</v>
       </c>
     </row>
     <row r="32">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4747,7 +4747,7 @@
         <v>0</v>
       </c>
       <c r="AK33" s="3" t="n">
-        <v>45905.83333333334</v>
+        <v>45905.85416666666</v>
       </c>
     </row>
     <row r="34">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>45905.85416666666</v>
+        <v>45905.875</v>
       </c>
     </row>
     <row r="35">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.1</v>
+        <v>1.52</v>
       </c>
       <c r="M35" t="n">
-        <v>3.25</v>
+        <v>3.37</v>
       </c>
       <c r="N35" t="n">
-        <v>2.25</v>
+        <v>6</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5005,7 +5005,7 @@
         <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
-        <v>45905.875</v>
+        <v>45905.89583333334</v>
       </c>
     </row>
     <row r="36">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="M36" t="n">
-        <v>3.37</v>
+        <v>3.8</v>
       </c>
       <c r="N36" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45905.89583333334</v>
+        <v>45905.97916666666</v>
       </c>
     </row>
     <row r="37">
@@ -5263,135 +5263,6 @@
         <v>0</v>
       </c>
       <c r="AK37" s="3" t="n">
-        <v>45905.97916666666</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="n">
-        <v>45905</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Phoenix Rising</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Las Vegas Lights</t>
-        </is>
-      </c>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L38" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="M38" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N38" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" t="n">
-        <v>0</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK38" s="3" t="n">
         <v>45905.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-09-05.xlsx
+++ b/jogos_2025-09-05.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK37"/>
+  <dimension ref="A1:AK38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.46</v>
+        <v>2.55</v>
       </c>
       <c r="M4" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N4" t="n">
-        <v>2.46</v>
+        <v>2.55</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,7 +966,7 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Z4" t="n">
         <v>1.8</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1194,52 +1194,52 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1710,52 +1710,52 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1955,65 +1955,65 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2649,10 +2649,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2778,10 +2778,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4.8</v>
+        <v>2.67</v>
       </c>
       <c r="M20" t="n">
-        <v>3.84</v>
+        <v>3.02</v>
       </c>
       <c r="N20" t="n">
-        <v>1.54</v>
+        <v>2.42</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.67</v>
+        <v>4.8</v>
       </c>
       <c r="M24" t="n">
-        <v>3.02</v>
+        <v>3.84</v>
       </c>
       <c r="N24" t="n">
-        <v>2.42</v>
+        <v>1.54</v>
       </c>
       <c r="O24" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3982,12 +3982,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.35</v>
+        <v>2.02</v>
       </c>
       <c r="M28" t="n">
-        <v>3.3</v>
+        <v>2.99</v>
       </c>
       <c r="N28" t="n">
-        <v>2.8</v>
+        <v>3.45</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.9</v>
+        <v>2.12</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45905.79166666666</v>
+        <v>45905.70833333334</v>
       </c>
     </row>
     <row r="29">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,49 +4281,49 @@
         </is>
       </c>
       <c r="L30" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
         <v>1.9</v>
       </c>
-      <c r="M30" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="N30" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="X30" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>2.38</v>
-      </c>
       <c r="Z30" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4369,12 +4369,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4443,16 +4443,16 @@
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45905.83333333334</v>
+        <v>45905.79166666666</v>
       </c>
     </row>
     <row r="32">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4572,10 +4572,10 @@
         <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
         <v>0</v>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4701,10 +4701,10 @@
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y33" t="n">
         <v>0</v>
@@ -4747,7 +4747,7 @@
         <v>0</v>
       </c>
       <c r="AK33" s="3" t="n">
-        <v>45905.85416666666</v>
+        <v>45905.83333333334</v>
       </c>
     </row>
     <row r="34">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>45905.875</v>
+        <v>45905.85416666666</v>
       </c>
     </row>
     <row r="35">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.52</v>
+        <v>3.1</v>
       </c>
       <c r="M35" t="n">
-        <v>3.37</v>
+        <v>3.25</v>
       </c>
       <c r="N35" t="n">
-        <v>6</v>
+        <v>2.25</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5005,7 +5005,7 @@
         <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
-        <v>45905.89583333334</v>
+        <v>45905.875</v>
       </c>
     </row>
     <row r="36">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="M36" t="n">
-        <v>3.8</v>
+        <v>3.37</v>
       </c>
       <c r="N36" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45905.97916666666</v>
+        <v>45905.89583333334</v>
       </c>
     </row>
     <row r="37">
@@ -5263,6 +5263,135 @@
         <v>0</v>
       </c>
       <c r="AK37" s="3" t="n">
+        <v>45905.97916666666</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>45905</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Phoenix Rising</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Las Vegas Lights</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="M38" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N38" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" s="3" t="n">
         <v>45905.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-09-05.xlsx
+++ b/jogos_2025-09-05.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.93</v>
+        <v>2.55</v>
       </c>
       <c r="M3" t="n">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="N3" t="n">
-        <v>2.18</v>
+        <v>2.55</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Y3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z3" t="n">
         <v>1.8</v>
       </c>
-      <c r="Z3" t="n">
-        <v>1.89</v>
-      </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.55</v>
+        <v>2.93</v>
       </c>
       <c r="M4" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="N4" t="n">
-        <v>2.55</v>
+        <v>2.18</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1581,52 +1581,52 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,28 +1701,28 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O10" t="n">
-        <v>2.62</v>
+        <v>2.87</v>
       </c>
       <c r="P10" t="n">
         <v>2.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.61</v>
+        <v>3.9</v>
       </c>
       <c r="R10" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S10" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="T10" t="n">
         <v>3</v>
@@ -1734,28 +1734,28 @@
         <v>1.05</v>
       </c>
       <c r="W10" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="X10" t="n">
         <v>2.8</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AA10" t="n">
         <v>3.9</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AC10" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2226,34 +2226,34 @@
         <v>3.89</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y14" t="n">
         <v>1.98</v>
@@ -2262,16 +2262,16 @@
         <v>1.77</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>6.71</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>7.32</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.58</v>
+        <v>3.3</v>
       </c>
       <c r="M18" t="n">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="N18" t="n">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.2</v>
+        <v>5.96</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,16 +2901,16 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.67</v>
+        <v>3.66</v>
       </c>
       <c r="M20" t="n">
-        <v>3.02</v>
+        <v>3.55</v>
       </c>
       <c r="N20" t="n">
-        <v>2.42</v>
+        <v>1.77</v>
       </c>
       <c r="O20" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="P20" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="Q20" t="n">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="R20" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="S20" t="n">
-        <v>2.8</v>
+        <v>3.07</v>
       </c>
       <c r="T20" t="n">
-        <v>2.76</v>
+        <v>2.65</v>
       </c>
       <c r="U20" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="V20" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W20" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="X20" t="n">
-        <v>3.22</v>
+        <v>3.42</v>
       </c>
       <c r="Y20" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Z20" t="n">
         <v>1.89</v>
       </c>
-      <c r="Z20" t="n">
-        <v>1.81</v>
-      </c>
       <c r="AA20" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AD20" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.41</v>
+        <v>1.18</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.66</v>
+        <v>2.89</v>
       </c>
       <c r="M21" t="n">
-        <v>3.55</v>
+        <v>3.18</v>
       </c>
       <c r="N21" t="n">
-        <v>1.77</v>
+        <v>2.18</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.48</v>
+        <v>2.67</v>
       </c>
       <c r="M22" t="n">
-        <v>3.94</v>
+        <v>3.02</v>
       </c>
       <c r="N22" t="n">
-        <v>5.2</v>
+        <v>2.42</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.6</v>
+        <v>1.89</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.2</v>
+        <v>1.81</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.89</v>
+        <v>1.48</v>
       </c>
       <c r="M23" t="n">
-        <v>3.18</v>
+        <v>3.94</v>
       </c>
       <c r="N23" t="n">
-        <v>2.18</v>
+        <v>5.2</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>5.67</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3516,34 +3516,34 @@
         <v>1.54</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Y24" t="n">
         <v>1.65</v>
@@ -3552,16 +3552,16 @@
         <v>2.1</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4185,16 +4185,16 @@
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,49 +4410,49 @@
         </is>
       </c>
       <c r="L31" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="M31" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
         <v>1.9</v>
       </c>
-      <c r="M31" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="N31" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="X31" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>2.35</v>
-      </c>
       <c r="Z31" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4572,10 +4572,10 @@
         <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4701,10 +4701,10 @@
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>

--- a/jogos_2025-09-05.xlsx
+++ b/jogos_2025-09-05.xlsx
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.3</v>
+        <v>2.62</v>
       </c>
       <c r="P6" t="n">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.6</v>
+        <v>4.61</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="S6" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="T6" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="U6" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="V6" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="W6" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="X6" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.5</v>
+        <v>2.17</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.45</v>
+        <v>1.78</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,28 +1572,28 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O9" t="n">
-        <v>2.62</v>
+        <v>2.87</v>
       </c>
       <c r="P9" t="n">
         <v>2.05</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.61</v>
+        <v>3.9</v>
       </c>
       <c r="R9" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S9" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="T9" t="n">
         <v>3</v>
@@ -1605,28 +1605,28 @@
         <v>1.05</v>
       </c>
       <c r="W9" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="X9" t="n">
         <v>2.8</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AA9" t="n">
         <v>3.9</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AC9" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2229,7 +2229,7 @@
         <v>2.52</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="Q14" t="n">
         <v>4.7</v>
@@ -2241,7 +2241,7 @@
         <v>2.71</v>
       </c>
       <c r="T14" t="n">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="U14" t="n">
         <v>1.34</v>
@@ -2250,7 +2250,7 @@
         <v>1.02</v>
       </c>
       <c r="W14" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X14" t="n">
         <v>3.2</v>
@@ -2262,7 +2262,7 @@
         <v>1.77</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.58</v>
+        <v>3.55</v>
       </c>
       <c r="AB14" t="n">
         <v>1.25</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.89</v>
+        <v>2.67</v>
       </c>
       <c r="M21" t="n">
-        <v>3.18</v>
+        <v>3.02</v>
       </c>
       <c r="N21" t="n">
-        <v>2.18</v>
+        <v>2.42</v>
       </c>
       <c r="O21" t="n">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="P21" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="S21" t="n">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="T21" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="U21" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="V21" t="n">
         <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="X21" t="n">
-        <v>3.59</v>
+        <v>3.22</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.14</v>
+        <v>3.22</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.56</v>
+        <v>1.28</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.67</v>
+        <v>4.8</v>
       </c>
       <c r="M22" t="n">
-        <v>3.02</v>
+        <v>3.84</v>
       </c>
       <c r="N22" t="n">
-        <v>2.42</v>
+        <v>1.54</v>
       </c>
       <c r="O22" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="P22" t="n">
-        <v>2.08</v>
+        <v>2.46</v>
       </c>
       <c r="Q22" t="n">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="R22" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="S22" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="T22" t="n">
-        <v>2.76</v>
+        <v>2.46</v>
       </c>
       <c r="U22" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="V22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W22" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="X22" t="n">
-        <v>3.22</v>
+        <v>4.15</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.22</v>
+        <v>2.65</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AD22" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.41</v>
+        <v>1.11</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4.8</v>
+        <v>2.89</v>
       </c>
       <c r="M24" t="n">
-        <v>3.84</v>
+        <v>3.18</v>
       </c>
       <c r="N24" t="n">
-        <v>1.54</v>
+        <v>2.18</v>
       </c>
       <c r="O24" t="n">
-        <v>5</v>
+        <v>3.58</v>
       </c>
       <c r="P24" t="n">
-        <v>2.46</v>
+        <v>2.05</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="R24" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="S24" t="n">
-        <v>3.2</v>
+        <v>2.93</v>
       </c>
       <c r="T24" t="n">
-        <v>2.46</v>
+        <v>2.79</v>
       </c>
       <c r="U24" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="V24" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="X24" t="n">
-        <v>4.15</v>
+        <v>3.59</v>
       </c>
       <c r="Y24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC24" t="n">
         <v>1.65</v>
       </c>
-      <c r="Z24" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.74</v>
-      </c>
       <c r="AD24" t="n">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.18</v>
+        <v>1.56</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -4023,31 +4023,31 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="M28" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="N28" t="n">
-        <v>3.45</v>
+        <v>3.37</v>
       </c>
       <c r="O28" t="n">
-        <v>2.73</v>
+        <v>2.93</v>
       </c>
       <c r="P28" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.38</v>
+        <v>4.22</v>
       </c>
       <c r="R28" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S28" t="n">
         <v>2.53</v>
       </c>
       <c r="T28" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="U28" t="n">
         <v>1.3</v>
@@ -4056,22 +4056,22 @@
         <v>1.03</v>
       </c>
       <c r="W28" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="X28" t="n">
-        <v>2.72</v>
+        <v>2.63</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.12</v>
+        <v>2.35</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="AA28" t="n">
-        <v>4.15</v>
+        <v>4.4</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AC28" t="n">
         <v>1.96</v>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4185,16 +4185,16 @@
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4314,16 +4314,16 @@
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>

--- a/jogos_2025-09-05.xlsx
+++ b/jogos_2025-09-05.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.55</v>
+        <v>2.93</v>
       </c>
       <c r="M3" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="N3" t="n">
-        <v>2.55</v>
+        <v>2.18</v>
       </c>
       <c r="O3" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.93</v>
+        <v>2.55</v>
       </c>
       <c r="M4" t="n">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="N4" t="n">
-        <v>2.18</v>
+        <v>2.55</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Y4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z4" t="n">
         <v>1.8</v>
       </c>
-      <c r="Z4" t="n">
-        <v>1.89</v>
-      </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1194,52 +1194,52 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1710,52 +1710,52 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="M12" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="N12" t="n">
-        <v>2.75</v>
+        <v>3.55</v>
       </c>
       <c r="O12" t="n">
-        <v>3.3</v>
+        <v>2.87</v>
       </c>
       <c r="P12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC12" t="n">
         <v>1.92</v>
       </c>
-      <c r="Q12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.12</v>
-      </c>
       <c r="AD12" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="N17" t="n">
+        <v>6</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="R17" t="n">
         <v>1.8</v>
       </c>
-      <c r="M17" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="N17" t="n">
-        <v>6.71</v>
-      </c>
-      <c r="O17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>7.32</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.76</v>
-      </c>
       <c r="S17" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="T17" t="n">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="U17" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="V17" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="W17" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="X17" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AA17" t="n">
-        <v>5.95</v>
+        <v>6.25</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.37</v>
+        <v>1.1</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.3</v>
+        <v>1.6</v>
       </c>
       <c r="M18" t="n">
-        <v>2.7</v>
+        <v>4.05</v>
       </c>
       <c r="N18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z18" t="n">
         <v>2.2</v>
       </c>
-      <c r="O18" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AA18" t="n">
-        <v>5.96</v>
+        <v>2.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O19" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W19" t="n">
         <v>1.6</v>
       </c>
-      <c r="M19" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="N19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.58</v>
+        <v>2.94</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.2</v>
+        <v>1.36</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.2</v>
+        <v>5.96</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.66</v>
+        <v>1.48</v>
       </c>
       <c r="M20" t="n">
-        <v>3.55</v>
+        <v>3.94</v>
       </c>
       <c r="N20" t="n">
-        <v>1.77</v>
+        <v>5.2</v>
       </c>
       <c r="O20" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="P20" t="n">
-        <v>2.14</v>
+        <v>2.27</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.33</v>
+        <v>5.67</v>
       </c>
       <c r="R20" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="S20" t="n">
-        <v>3.07</v>
+        <v>3.3</v>
       </c>
       <c r="T20" t="n">
-        <v>2.65</v>
+        <v>2.41</v>
       </c>
       <c r="U20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X20" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AB20" t="n">
         <v>1.42</v>
       </c>
-      <c r="V20" t="n">
-        <v>1</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X20" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AC20" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.18</v>
+        <v>2.42</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.67</v>
+        <v>4.8</v>
       </c>
       <c r="M21" t="n">
-        <v>3.02</v>
+        <v>3.84</v>
       </c>
       <c r="N21" t="n">
-        <v>2.42</v>
+        <v>1.54</v>
       </c>
       <c r="O21" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="P21" t="n">
-        <v>2.08</v>
+        <v>2.46</v>
       </c>
       <c r="Q21" t="n">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="R21" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="S21" t="n">
-        <v>2.8</v>
+        <v>3.14</v>
       </c>
       <c r="T21" t="n">
-        <v>2.76</v>
+        <v>2.46</v>
       </c>
       <c r="U21" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W21" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="X21" t="n">
-        <v>3.22</v>
+        <v>4.15</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.22</v>
+        <v>2.65</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.27</v>
+        <v>1.39</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AD21" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.41</v>
+        <v>1.11</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4.8</v>
+        <v>2.67</v>
       </c>
       <c r="M22" t="n">
-        <v>3.84</v>
+        <v>3.02</v>
       </c>
       <c r="N22" t="n">
-        <v>1.54</v>
+        <v>2.42</v>
       </c>
       <c r="O22" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="P22" t="n">
-        <v>2.46</v>
+        <v>2.08</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="R22" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="S22" t="n">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="T22" t="n">
-        <v>2.46</v>
+        <v>2.76</v>
       </c>
       <c r="U22" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="V22" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="X22" t="n">
-        <v>4.15</v>
+        <v>3.22</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.65</v>
+        <v>3.22</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.11</v>
+        <v>1.41</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.48</v>
+        <v>2.89</v>
       </c>
       <c r="M23" t="n">
-        <v>3.94</v>
+        <v>3.18</v>
       </c>
       <c r="N23" t="n">
-        <v>5.2</v>
+        <v>2.18</v>
       </c>
       <c r="O23" t="n">
-        <v>2</v>
+        <v>3.58</v>
       </c>
       <c r="P23" t="n">
-        <v>2.27</v>
+        <v>2.05</v>
       </c>
       <c r="Q23" t="n">
-        <v>5.67</v>
+        <v>2.88</v>
       </c>
       <c r="R23" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="S23" t="n">
-        <v>3.3</v>
+        <v>2.93</v>
       </c>
       <c r="T23" t="n">
-        <v>2.41</v>
+        <v>2.78</v>
       </c>
       <c r="U23" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="V23" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X23" t="n">
-        <v>4.3</v>
+        <v>3.42</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.49</v>
+        <v>3.13</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.84</v>
+        <v>1.66</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.9</v>
+        <v>2.07</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.17</v>
+        <v>1.56</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.42</v>
+        <v>1.36</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,22 +3507,22 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.89</v>
+        <v>3.66</v>
       </c>
       <c r="M24" t="n">
-        <v>3.18</v>
+        <v>3.55</v>
       </c>
       <c r="N24" t="n">
-        <v>2.18</v>
+        <v>1.77</v>
       </c>
       <c r="O24" t="n">
-        <v>3.58</v>
+        <v>4.5</v>
       </c>
       <c r="P24" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.88</v>
+        <v>2.33</v>
       </c>
       <c r="R24" t="n">
         <v>1.35</v>
@@ -3531,37 +3531,37 @@
         <v>2.93</v>
       </c>
       <c r="T24" t="n">
-        <v>2.79</v>
+        <v>2.65</v>
       </c>
       <c r="U24" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="V24" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W24" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="X24" t="n">
-        <v>3.59</v>
+        <v>3.6</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.56</v>
+        <v>1.24</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="M28" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N28" t="n">
-        <v>3.37</v>
+        <v>3.6</v>
       </c>
       <c r="O28" t="n">
         <v>2.93</v>
@@ -4062,10 +4062,10 @@
         <v>2.63</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.35</v>
+        <v>2.12</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="AA28" t="n">
         <v>4.4</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4185,16 +4185,16 @@
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,49 +4281,49 @@
         </is>
       </c>
       <c r="L30" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
         <v>1.9</v>
       </c>
-      <c r="M30" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="N30" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="X30" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>2.35</v>
-      </c>
       <c r="Z30" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.35</v>
+        <v>1.86</v>
       </c>
       <c r="M31" t="n">
-        <v>3.3</v>
+        <v>2.91</v>
       </c>
       <c r="N31" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4443,16 +4443,16 @@
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.75</v>
+        <v>2.43</v>
       </c>
       <c r="M32" t="n">
-        <v>2.9</v>
+        <v>2.59</v>
       </c>
       <c r="N32" t="n">
-        <v>2.65</v>
+        <v>3.11</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4572,10 +4572,10 @@
         <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.58</v>
+        <v>1.79</v>
       </c>
       <c r="X32" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="Y32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4701,10 +4701,10 @@
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Y33" t="n">
         <v>0</v>
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>

--- a/jogos_2025-09-05.xlsx
+++ b/jogos_2025-09-05.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.93</v>
+        <v>2.55</v>
       </c>
       <c r="M3" t="n">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="N3" t="n">
-        <v>2.18</v>
+        <v>2.55</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Y3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z3" t="n">
         <v>1.8</v>
       </c>
-      <c r="Z3" t="n">
-        <v>1.89</v>
-      </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.55</v>
+        <v>2.93</v>
       </c>
       <c r="M4" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="N4" t="n">
-        <v>2.55</v>
+        <v>2.18</v>
       </c>
       <c r="O4" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1052,65 +1052,65 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1710,52 +1710,52 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1839,52 +1839,52 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="M12" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="N12" t="n">
-        <v>3.55</v>
+        <v>2.75</v>
       </c>
       <c r="O12" t="n">
-        <v>2.87</v>
+        <v>3.56</v>
       </c>
       <c r="P12" t="n">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="R12" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="S12" t="n">
-        <v>2.65</v>
+        <v>2.33</v>
       </c>
       <c r="T12" t="n">
-        <v>3</v>
+        <v>3.56</v>
       </c>
       <c r="U12" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="V12" t="n">
         <v>1.05</v>
       </c>
       <c r="W12" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="X12" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.1</v>
+        <v>2.54</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.9</v>
+        <v>4.91</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.58</v>
+        <v>1.41</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2226,25 +2226,25 @@
         <v>3.89</v>
       </c>
       <c r="O14" t="n">
-        <v>2.52</v>
+        <v>2.31</v>
       </c>
       <c r="P14" t="n">
-        <v>2.23</v>
+        <v>2.04</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.7</v>
+        <v>4.06</v>
       </c>
       <c r="R14" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S14" t="n">
-        <v>2.71</v>
+        <v>2.9</v>
       </c>
       <c r="T14" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="U14" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="V14" t="n">
         <v>1.02</v>
@@ -2253,7 +2253,7 @@
         <v>1.32</v>
       </c>
       <c r="X14" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="Y14" t="n">
         <v>1.98</v>
@@ -2262,16 +2262,16 @@
         <v>1.77</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2613,28 +2613,28 @@
         <v>6</v>
       </c>
       <c r="O17" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="P17" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="Q17" t="n">
-        <v>7.2</v>
+        <v>7.43</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="S17" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="T17" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="U17" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W17" t="n">
         <v>1.75</v>
@@ -2643,38 +2643,38 @@
         <v>1.95</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.08</v>
+        <v>3.6</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AA17" t="n">
-        <v>6.25</v>
+        <v>8</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.71</v>
+        <v>2.84</v>
       </c>
       <c r="AD17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
         <v>1.4</v>
       </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AH17" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W18" t="n">
         <v>1.6</v>
       </c>
-      <c r="M18" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="N18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.58</v>
+        <v>2.78</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.2</v>
+        <v>1.34</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.2</v>
+        <v>6.1</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.6</v>
+        <v>1.08</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.39</v>
+        <v>1.6</v>
       </c>
       <c r="M19" t="n">
-        <v>2.7</v>
+        <v>4.05</v>
       </c>
       <c r="N19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z19" t="n">
         <v>2.2</v>
       </c>
-      <c r="O19" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W19" t="n">
+      <c r="AA19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB19" t="n">
         <v>1.6</v>
       </c>
-      <c r="X19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>5.96</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AC19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.48</v>
+        <v>2.67</v>
       </c>
       <c r="M20" t="n">
-        <v>3.94</v>
+        <v>3.02</v>
       </c>
       <c r="N20" t="n">
-        <v>5.2</v>
+        <v>2.42</v>
       </c>
       <c r="O20" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="P20" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.67</v>
+        <v>3.12</v>
       </c>
       <c r="R20" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="S20" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="T20" t="n">
-        <v>2.41</v>
+        <v>2.76</v>
       </c>
       <c r="U20" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="V20" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="X20" t="n">
-        <v>4.3</v>
+        <v>3.22</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.6</v>
+        <v>1.89</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.2</v>
+        <v>1.81</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.49</v>
+        <v>3.22</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="AC20" t="n">
         <v>1.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.42</v>
+        <v>1.41</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>4.8</v>
+        <v>1.48</v>
       </c>
       <c r="M21" t="n">
-        <v>3.84</v>
+        <v>3.94</v>
       </c>
       <c r="N21" t="n">
-        <v>1.54</v>
+        <v>5.2</v>
       </c>
       <c r="O21" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P21" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.05</v>
+        <v>5.83</v>
       </c>
       <c r="R21" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="S21" t="n">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="T21" t="n">
-        <v>2.46</v>
+        <v>2.41</v>
       </c>
       <c r="U21" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="V21" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X21" t="n">
-        <v>4.15</v>
+        <v>4.08</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.65</v>
+        <v>2.49</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.11</v>
+        <v>2.4</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.67</v>
+        <v>3.66</v>
       </c>
       <c r="M22" t="n">
-        <v>3.02</v>
+        <v>3.55</v>
       </c>
       <c r="N22" t="n">
-        <v>2.42</v>
+        <v>1.77</v>
       </c>
       <c r="O22" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="P22" t="n">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="Q22" t="n">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="R22" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="S22" t="n">
-        <v>2.99</v>
+        <v>2.93</v>
       </c>
       <c r="T22" t="n">
-        <v>2.76</v>
+        <v>2.65</v>
       </c>
       <c r="U22" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="V22" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W22" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="X22" t="n">
-        <v>3.22</v>
+        <v>3.42</v>
       </c>
       <c r="Y22" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Z22" t="n">
         <v>1.89</v>
       </c>
-      <c r="Z22" t="n">
-        <v>1.81</v>
-      </c>
       <c r="AA22" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AD22" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.41</v>
+        <v>1.18</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3387,13 +3387,13 @@
         <v>2.18</v>
       </c>
       <c r="O23" t="n">
-        <v>3.58</v>
+        <v>3.67</v>
       </c>
       <c r="P23" t="n">
         <v>2.05</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="R23" t="n">
         <v>1.35</v>
@@ -3423,7 +3423,7 @@
         <v>1.85</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.13</v>
+        <v>3.04</v>
       </c>
       <c r="AB23" t="n">
         <v>1.29</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.56</v>
+        <v>1.27</v>
       </c>
       <c r="AH23" t="n">
         <v>1.36</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.66</v>
+        <v>4.8</v>
       </c>
       <c r="M24" t="n">
-        <v>3.55</v>
+        <v>3.84</v>
       </c>
       <c r="N24" t="n">
-        <v>1.77</v>
+        <v>1.54</v>
       </c>
       <c r="O24" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="P24" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.33</v>
+        <v>2.05</v>
       </c>
       <c r="R24" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="S24" t="n">
-        <v>2.93</v>
+        <v>3.2</v>
       </c>
       <c r="T24" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X24" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA24" t="n">
         <v>2.65</v>
       </c>
-      <c r="U24" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X24" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>3.25</v>
-      </c>
       <c r="AB24" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3651,7 +3651,7 @@
         <v>2.28</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.2</v>
+        <v>3.44</v>
       </c>
       <c r="R25" t="n">
         <v>1.27</v>
@@ -3669,7 +3669,7 @@
         <v>1.02</v>
       </c>
       <c r="W25" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="X25" t="n">
         <v>4.4</v>
@@ -3681,7 +3681,7 @@
         <v>2.2</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="AB25" t="n">
         <v>1.53</v>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -4047,7 +4047,7 @@
         <v>2.53</v>
       </c>
       <c r="T28" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U28" t="n">
         <v>1.3</v>
@@ -4068,16 +4068,16 @@
         <v>1.64</v>
       </c>
       <c r="AA28" t="n">
-        <v>4.4</v>
+        <v>4.43</v>
       </c>
       <c r="AB28" t="n">
         <v>1.2</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.96</v>
+        <v>2.07</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH28" t="n">
         <v>1.66</v>
@@ -4161,28 +4161,28 @@
         <v>3.86</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W29" t="n">
         <v>1.52</v>
@@ -4197,16 +4197,16 @@
         <v>1.53</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.35</v>
+        <v>1.86</v>
       </c>
       <c r="M30" t="n">
-        <v>3.3</v>
+        <v>2.91</v>
       </c>
       <c r="N30" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.9</v>
+        <v>2.88</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.8</v>
+        <v>1.32</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.86</v>
+        <v>2.35</v>
       </c>
       <c r="M31" t="n">
-        <v>2.91</v>
+        <v>3.3</v>
       </c>
       <c r="N31" t="n">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W31" t="n">
-        <v>1.65</v>
+        <v>1.26</v>
       </c>
       <c r="X31" t="n">
-        <v>2.1</v>
+        <v>3.22</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.43</v>
+        <v>3</v>
       </c>
       <c r="M32" t="n">
-        <v>2.59</v>
+        <v>2.51</v>
       </c>
       <c r="N32" t="n">
-        <v>3.11</v>
+        <v>2.58</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W32" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="X32" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3</v>
+        <v>2.43</v>
       </c>
       <c r="M33" t="n">
-        <v>2.51</v>
+        <v>2.59</v>
       </c>
       <c r="N33" t="n">
-        <v>2.58</v>
+        <v>3.11</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W33" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="X33" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4935,34 +4935,34 @@
         <v>2.25</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Y35" t="n">
         <v>2</v>
@@ -4971,16 +4971,16 @@
         <v>1.72</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5064,34 +5064,34 @@
         <v>6</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>6.48</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Y36" t="n">
         <v>2.4</v>
@@ -5100,16 +5100,16 @@
         <v>1.5</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5322,34 +5322,34 @@
         <v>4.7</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y38" t="n">
         <v>1.8</v>
@@ -5358,16 +5358,16 @@
         <v>1.9</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>

--- a/jogos_2025-09-05.xlsx
+++ b/jogos_2025-09-05.xlsx
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>4.91</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.91</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.74</v>
+        <v>3.39</v>
       </c>
       <c r="M17" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="N17" t="n">
-        <v>6</v>
+        <v>2.2</v>
       </c>
       <c r="O17" t="n">
-        <v>2.72</v>
+        <v>4.6</v>
       </c>
       <c r="P17" t="n">
-        <v>1.66</v>
+        <v>1.87</v>
       </c>
       <c r="Q17" t="n">
-        <v>7.43</v>
+        <v>2.95</v>
       </c>
       <c r="R17" t="n">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="S17" t="n">
-        <v>1.91</v>
+        <v>2.11</v>
       </c>
       <c r="T17" t="n">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="U17" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="V17" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="W17" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="X17" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.6</v>
+        <v>2.78</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AA17" t="n">
-        <v>8</v>
+        <v>6.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.84</v>
+        <v>2.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.36</v>
+        <v>1.54</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.82</v>
+        <v>1.23</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.39</v>
+        <v>1.6</v>
       </c>
       <c r="M18" t="n">
-        <v>2.7</v>
+        <v>4.05</v>
       </c>
       <c r="N18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z18" t="n">
         <v>2.2</v>
       </c>
-      <c r="O18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W18" t="n">
+      <c r="AA18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB18" t="n">
         <v>1.6</v>
       </c>
-      <c r="X18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AC18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="M19" t="n">
-        <v>4.05</v>
+        <v>2.62</v>
       </c>
       <c r="N19" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>7.43</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.58</v>
+        <v>3.6</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.2</v>
+        <v>1.25</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.2</v>
+        <v>8</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>1.05</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.67</v>
+        <v>1.48</v>
       </c>
       <c r="M20" t="n">
-        <v>3.02</v>
+        <v>3.94</v>
       </c>
       <c r="N20" t="n">
-        <v>2.42</v>
+        <v>5.2</v>
       </c>
       <c r="O20" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="P20" t="n">
-        <v>2.08</v>
+        <v>2.47</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.12</v>
+        <v>5.83</v>
       </c>
       <c r="R20" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="S20" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="T20" t="n">
-        <v>2.76</v>
+        <v>2.41</v>
       </c>
       <c r="U20" t="n">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="V20" t="n">
         <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="X20" t="n">
-        <v>3.22</v>
+        <v>4.08</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.89</v>
+        <v>1.6</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.81</v>
+        <v>2.2</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.22</v>
+        <v>2.49</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AC20" t="n">
         <v>1.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.41</v>
+        <v>2.4</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.48</v>
+        <v>3.66</v>
       </c>
       <c r="M21" t="n">
-        <v>3.94</v>
+        <v>3.55</v>
       </c>
       <c r="N21" t="n">
-        <v>5.2</v>
+        <v>1.77</v>
       </c>
       <c r="O21" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="P21" t="n">
-        <v>2.47</v>
+        <v>2.28</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.83</v>
+        <v>2.33</v>
       </c>
       <c r="R21" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X21" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB21" t="n">
         <v>1.28</v>
       </c>
-      <c r="S21" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X21" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AC21" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.4</v>
+        <v>1.18</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,22 +3249,22 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.66</v>
+        <v>2.89</v>
       </c>
       <c r="M22" t="n">
-        <v>3.55</v>
+        <v>3.18</v>
       </c>
       <c r="N22" t="n">
-        <v>1.77</v>
+        <v>2.18</v>
       </c>
       <c r="O22" t="n">
-        <v>4.5</v>
+        <v>3.67</v>
       </c>
       <c r="P22" t="n">
-        <v>2.28</v>
+        <v>2.05</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.33</v>
+        <v>2.84</v>
       </c>
       <c r="R22" t="n">
         <v>1.35</v>
@@ -3273,13 +3273,13 @@
         <v>2.93</v>
       </c>
       <c r="T22" t="n">
-        <v>2.65</v>
+        <v>2.78</v>
       </c>
       <c r="U22" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="V22" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W22" t="n">
         <v>1.23</v>
@@ -3288,22 +3288,22 @@
         <v>3.42</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.94</v>
+        <v>2.07</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.89</v>
+        <v>2.67</v>
       </c>
       <c r="M23" t="n">
-        <v>3.18</v>
+        <v>3.02</v>
       </c>
       <c r="N23" t="n">
-        <v>2.18</v>
+        <v>2.42</v>
       </c>
       <c r="O23" t="n">
-        <v>3.67</v>
+        <v>3.2</v>
       </c>
       <c r="P23" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.84</v>
+        <v>3.12</v>
       </c>
       <c r="R23" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="S23" t="n">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="T23" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="U23" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="V23" t="n">
         <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="X23" t="n">
-        <v>3.42</v>
+        <v>3.22</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.04</v>
+        <v>3.22</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="M29" t="n">
-        <v>2.98</v>
+        <v>2.91</v>
       </c>
       <c r="N29" t="n">
-        <v>3.86</v>
+        <v>4.2</v>
       </c>
       <c r="O29" t="n">
-        <v>2.75</v>
+        <v>2.61</v>
       </c>
       <c r="P29" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.76</v>
+        <v>5.7</v>
       </c>
       <c r="R29" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="S29" t="n">
-        <v>2.42</v>
+        <v>2.16</v>
       </c>
       <c r="T29" t="n">
-        <v>3.34</v>
+        <v>4.15</v>
       </c>
       <c r="U29" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="V29" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="W29" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="X29" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.35</v>
+        <v>2.88</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.53</v>
+        <v>1.32</v>
       </c>
       <c r="AA29" t="n">
-        <v>4.64</v>
+        <v>6.05</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.04</v>
+        <v>2.51</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.71</v>
+        <v>1.46</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.86</v>
+        <v>2.35</v>
       </c>
       <c r="M30" t="n">
-        <v>2.91</v>
+        <v>3.3</v>
       </c>
       <c r="N30" t="n">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="O30" t="n">
-        <v>2.61</v>
+        <v>2.9</v>
       </c>
       <c r="P30" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X30" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z30" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q30" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="T30" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="X30" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AA30" t="n">
-        <v>6.05</v>
+        <v>3.25</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.06</v>
+        <v>1.28</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.51</v>
+        <v>1.69</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.46</v>
+        <v>2.03</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M31" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="N31" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="O31" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X31" t="n">
         <v>2.35</v>
       </c>
-      <c r="M31" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N31" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O31" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="P31" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="X31" t="n">
-        <v>3.22</v>
-      </c>
       <c r="Y31" t="n">
-        <v>1.9</v>
+        <v>2.35</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.25</v>
+        <v>4.64</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.69</v>
+        <v>2.04</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.03</v>
+        <v>1.71</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3</v>
+        <v>2.43</v>
       </c>
       <c r="M32" t="n">
-        <v>2.51</v>
+        <v>2.59</v>
       </c>
       <c r="N32" t="n">
-        <v>2.58</v>
+        <v>3.11</v>
       </c>
       <c r="O32" t="n">
-        <v>4.43</v>
+        <v>3.26</v>
       </c>
       <c r="P32" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="R32" t="n">
         <v>1.76</v>
       </c>
-      <c r="Q32" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.74</v>
-      </c>
       <c r="S32" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="T32" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="U32" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="V32" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="W32" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="X32" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="Y32" t="n">
-        <v>3.08</v>
+        <v>3.34</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AA32" t="n">
-        <v>6.3</v>
+        <v>7</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.42</v>
+        <v>2.7</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.47</v>
+        <v>1.26</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.28</v>
+        <v>1.52</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.43</v>
+        <v>3</v>
       </c>
       <c r="M33" t="n">
-        <v>2.59</v>
+        <v>2.51</v>
       </c>
       <c r="N33" t="n">
-        <v>3.11</v>
+        <v>2.58</v>
       </c>
       <c r="O33" t="n">
-        <v>3.26</v>
+        <v>4.43</v>
       </c>
       <c r="P33" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.88</v>
+        <v>3.53</v>
       </c>
       <c r="R33" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="S33" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="T33" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="U33" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="V33" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="W33" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="X33" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="Y33" t="n">
-        <v>3.34</v>
+        <v>3.08</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AA33" t="n">
-        <v>7</v>
+        <v>6.3</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.7</v>
+        <v>2.42</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.26</v>
+        <v>1.47</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.52</v>
+        <v>1.28</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>

--- a/jogos_2025-09-05.xlsx
+++ b/jogos_2025-09-05.xlsx
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1323,52 +1323,52 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>4.91</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.91</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O11" t="n">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="P11" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.64</v>
+        <v>4.3</v>
       </c>
       <c r="R11" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S11" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="T11" t="n">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="U11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W11" t="n">
         <v>1.32</v>
       </c>
-      <c r="V11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.35</v>
-      </c>
       <c r="X11" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.96</v>
+        <v>3.86</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>1.28</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.39</v>
+        <v>1.74</v>
       </c>
       <c r="M17" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="N17" t="n">
-        <v>2.2</v>
+        <v>6</v>
       </c>
       <c r="O17" t="n">
-        <v>4.6</v>
+        <v>2.72</v>
       </c>
       <c r="P17" t="n">
-        <v>1.87</v>
+        <v>1.66</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.95</v>
+        <v>7.43</v>
       </c>
       <c r="R17" t="n">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="S17" t="n">
-        <v>2.11</v>
+        <v>1.91</v>
       </c>
       <c r="T17" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="U17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="V17" t="n">
         <v>1.19</v>
       </c>
-      <c r="V17" t="n">
-        <v>1.13</v>
-      </c>
       <c r="W17" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="X17" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.78</v>
+        <v>3.6</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AA17" t="n">
-        <v>6.1</v>
+        <v>8</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.3</v>
+        <v>2.84</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.54</v>
+        <v>1.36</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.23</v>
+        <v>1.82</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W18" t="n">
         <v>1.6</v>
       </c>
-      <c r="M18" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="N18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.58</v>
+        <v>2.78</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.2</v>
+        <v>1.34</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.2</v>
+        <v>6.1</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.6</v>
+        <v>1.08</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="M19" t="n">
-        <v>2.62</v>
+        <v>4.05</v>
       </c>
       <c r="N19" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="O19" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>7.43</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>3.6</v>
+        <v>1.58</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.25</v>
+        <v>2.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>8</v>
+        <v>2.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.05</v>
+        <v>1.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.48</v>
+        <v>4.8</v>
       </c>
       <c r="M20" t="n">
-        <v>3.94</v>
+        <v>3.84</v>
       </c>
       <c r="N20" t="n">
-        <v>5.2</v>
+        <v>1.54</v>
       </c>
       <c r="O20" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P20" t="n">
-        <v>2.47</v>
+        <v>2.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.83</v>
+        <v>2.05</v>
       </c>
       <c r="R20" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S20" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="T20" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="U20" t="n">
         <v>1.49</v>
       </c>
       <c r="V20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W20" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="X20" t="n">
-        <v>4.08</v>
+        <v>3.94</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.49</v>
+        <v>2.65</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.4</v>
+        <v>1.12</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.66</v>
+        <v>2.67</v>
       </c>
       <c r="M21" t="n">
-        <v>3.55</v>
+        <v>3.02</v>
       </c>
       <c r="N21" t="n">
-        <v>1.77</v>
+        <v>2.42</v>
       </c>
       <c r="O21" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="P21" t="n">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.33</v>
+        <v>3.12</v>
       </c>
       <c r="R21" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="S21" t="n">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="T21" t="n">
-        <v>2.65</v>
+        <v>2.76</v>
       </c>
       <c r="U21" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="V21" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="X21" t="n">
-        <v>3.42</v>
+        <v>3.22</v>
       </c>
       <c r="Y21" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Z21" t="n">
         <v>1.81</v>
       </c>
-      <c r="Z21" t="n">
-        <v>1.89</v>
-      </c>
       <c r="AA21" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.89</v>
+        <v>1.48</v>
       </c>
       <c r="M22" t="n">
-        <v>3.18</v>
+        <v>3.94</v>
       </c>
       <c r="N22" t="n">
-        <v>2.18</v>
+        <v>5.2</v>
       </c>
       <c r="O22" t="n">
-        <v>3.67</v>
+        <v>2</v>
       </c>
       <c r="P22" t="n">
-        <v>2.05</v>
+        <v>2.47</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.84</v>
+        <v>5.83</v>
       </c>
       <c r="R22" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="S22" t="n">
-        <v>2.93</v>
+        <v>3.3</v>
       </c>
       <c r="T22" t="n">
-        <v>2.78</v>
+        <v>2.41</v>
       </c>
       <c r="U22" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="V22" t="n">
         <v>1.01</v>
       </c>
       <c r="W22" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="X22" t="n">
-        <v>3.42</v>
+        <v>4.08</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.04</v>
+        <v>2.49</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.07</v>
+        <v>1.98</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.27</v>
+        <v>1.1</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.36</v>
+        <v>2.4</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.67</v>
+        <v>3.66</v>
       </c>
       <c r="M23" t="n">
-        <v>3.02</v>
+        <v>3.55</v>
       </c>
       <c r="N23" t="n">
-        <v>2.42</v>
+        <v>1.77</v>
       </c>
       <c r="O23" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="P23" t="n">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.12</v>
+        <v>2.33</v>
       </c>
       <c r="R23" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="S23" t="n">
-        <v>2.8</v>
+        <v>2.93</v>
       </c>
       <c r="T23" t="n">
-        <v>2.76</v>
+        <v>2.65</v>
       </c>
       <c r="U23" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="V23" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W23" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="X23" t="n">
-        <v>3.22</v>
+        <v>3.42</v>
       </c>
       <c r="Y23" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Z23" t="n">
         <v>1.89</v>
       </c>
-      <c r="Z23" t="n">
-        <v>1.81</v>
-      </c>
       <c r="AA23" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AD23" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.41</v>
+        <v>1.18</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4.8</v>
+        <v>2.89</v>
       </c>
       <c r="M24" t="n">
-        <v>3.84</v>
+        <v>3.18</v>
       </c>
       <c r="N24" t="n">
-        <v>1.54</v>
+        <v>2.18</v>
       </c>
       <c r="O24" t="n">
-        <v>5</v>
+        <v>3.67</v>
       </c>
       <c r="P24" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.05</v>
+        <v>2.84</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="S24" t="n">
-        <v>3.2</v>
+        <v>2.93</v>
       </c>
       <c r="T24" t="n">
-        <v>2.44</v>
+        <v>2.78</v>
       </c>
       <c r="U24" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="V24" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="X24" t="n">
-        <v>3.94</v>
+        <v>3.42</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.65</v>
+        <v>3.04</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AD24" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.12</v>
+        <v>1.36</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>

--- a/jogos_2025-09-05.xlsx
+++ b/jogos_2025-09-05.xlsx
@@ -834,7 +834,7 @@
         <v>1.26</v>
       </c>
       <c r="X3" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="Y3" t="n">
         <v>1.9</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -1323,52 +1323,52 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.64</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1455,7 +1455,7 @@
         <v>3.56</v>
       </c>
       <c r="P8" t="n">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="Q8" t="n">
         <v>3.45</v>
@@ -1482,7 +1482,7 @@
         <v>2.45</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="Z8" t="n">
         <v>1.43</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1710,52 +1710,52 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2232,10 +2232,10 @@
         <v>2.04</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.06</v>
+        <v>4.55</v>
       </c>
       <c r="R14" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S14" t="n">
         <v>2.9</v>
@@ -2244,16 +2244,16 @@
         <v>2.8</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="V14" t="n">
         <v>1.02</v>
       </c>
       <c r="W14" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="X14" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="Y14" t="n">
         <v>1.98</v>
@@ -2262,16 +2262,16 @@
         <v>1.77</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AH14" t="n">
         <v>1.88</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>4.94</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2613,19 +2613,19 @@
         <v>6</v>
       </c>
       <c r="O17" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="P17" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q17" t="n">
-        <v>7.43</v>
+        <v>7.27</v>
       </c>
       <c r="R17" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="S17" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="T17" t="n">
         <v>4.5</v>
@@ -2643,10 +2643,10 @@
         <v>1.95</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AA17" t="n">
         <v>8</v>
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AH17" t="n">
         <v>1.82</v>
@@ -2742,19 +2742,19 @@
         <v>2.2</v>
       </c>
       <c r="O18" t="n">
-        <v>4.6</v>
+        <v>4.76</v>
       </c>
       <c r="P18" t="n">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.95</v>
+        <v>3.06</v>
       </c>
       <c r="R18" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="S18" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="T18" t="n">
         <v>3.85</v>
@@ -2763,7 +2763,7 @@
         <v>1.19</v>
       </c>
       <c r="V18" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="W18" t="n">
         <v>1.6</v>
@@ -2772,13 +2772,13 @@
         <v>2.2</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AA18" t="n">
-        <v>6.1</v>
+        <v>5.5</v>
       </c>
       <c r="AB18" t="n">
         <v>1.08</v>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,62 +2991,62 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4.8</v>
+        <v>2.89</v>
       </c>
       <c r="M20" t="n">
-        <v>3.84</v>
+        <v>3.18</v>
       </c>
       <c r="N20" t="n">
-        <v>1.54</v>
+        <v>2.18</v>
       </c>
       <c r="O20" t="n">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="P20" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.05</v>
+        <v>2.8</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="S20" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="T20" t="n">
-        <v>2.44</v>
+        <v>2.62</v>
       </c>
       <c r="U20" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="V20" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="X20" t="n">
-        <v>3.94</v>
+        <v>3.6</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="Z20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD20" t="n">
         <v>2.1</v>
       </c>
-      <c r="AA20" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>2</v>
-      </c>
       <c r="AE20" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.12</v>
+        <v>1.36</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3132,7 +3132,7 @@
         <v>3.2</v>
       </c>
       <c r="P21" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q21" t="n">
         <v>3.12</v>
@@ -3144,7 +3144,7 @@
         <v>2.8</v>
       </c>
       <c r="T21" t="n">
-        <v>2.76</v>
+        <v>2.85</v>
       </c>
       <c r="U21" t="n">
         <v>1.38</v>
@@ -3153,7 +3153,7 @@
         <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="X21" t="n">
         <v>3.22</v>
@@ -3165,7 +3165,7 @@
         <v>1.81</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.22</v>
+        <v>3.14</v>
       </c>
       <c r="AB21" t="n">
         <v>1.27</v>
@@ -3187,7 +3187,7 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH21" t="n">
         <v>1.41</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,77 +3249,77 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.48</v>
+        <v>4.8</v>
       </c>
       <c r="M22" t="n">
-        <v>3.94</v>
+        <v>3.84</v>
       </c>
       <c r="N22" t="n">
-        <v>5.2</v>
+        <v>1.54</v>
       </c>
       <c r="O22" t="n">
+        <v>5</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X22" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD22" t="n">
         <v>2</v>
       </c>
-      <c r="P22" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>5.83</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W22" t="n">
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
         <v>1.22</v>
       </c>
-      <c r="X22" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AH22" t="n">
-        <v>2.4</v>
+        <v>1.15</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3390,22 +3390,22 @@
         <v>4.5</v>
       </c>
       <c r="P23" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="R23" t="n">
         <v>1.35</v>
       </c>
       <c r="S23" t="n">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="T23" t="n">
         <v>2.65</v>
       </c>
       <c r="U23" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="V23" t="n">
         <v>1</v>
@@ -3414,7 +3414,7 @@
         <v>1.23</v>
       </c>
       <c r="X23" t="n">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="Y23" t="n">
         <v>1.81</v>
@@ -3429,10 +3429,10 @@
         <v>1.28</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.89</v>
+        <v>1.48</v>
       </c>
       <c r="M24" t="n">
-        <v>3.18</v>
+        <v>3.94</v>
       </c>
       <c r="N24" t="n">
-        <v>2.18</v>
+        <v>5.2</v>
       </c>
       <c r="O24" t="n">
-        <v>3.67</v>
+        <v>2</v>
       </c>
       <c r="P24" t="n">
-        <v>2.05</v>
+        <v>2.47</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.84</v>
+        <v>5.83</v>
       </c>
       <c r="R24" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="S24" t="n">
-        <v>2.93</v>
+        <v>3.4</v>
       </c>
       <c r="T24" t="n">
-        <v>2.78</v>
+        <v>2.46</v>
       </c>
       <c r="U24" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="V24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W24" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="X24" t="n">
-        <v>3.42</v>
+        <v>4.1</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.04</v>
+        <v>2.59</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.36</v>
+        <v>2.4</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3645,25 +3645,25 @@
         <v>3.09</v>
       </c>
       <c r="O25" t="n">
-        <v>2.81</v>
+        <v>2.87</v>
       </c>
       <c r="P25" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.44</v>
+        <v>3.25</v>
       </c>
       <c r="R25" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="S25" t="n">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="T25" t="n">
         <v>2.38</v>
       </c>
       <c r="U25" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="V25" t="n">
         <v>1.02</v>
@@ -3681,16 +3681,16 @@
         <v>2.2</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="AB25" t="n">
         <v>1.53</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -4032,22 +4032,22 @@
         <v>3.6</v>
       </c>
       <c r="O28" t="n">
-        <v>2.93</v>
+        <v>2.97</v>
       </c>
       <c r="P28" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.22</v>
+        <v>4.28</v>
       </c>
       <c r="R28" t="n">
         <v>1.45</v>
       </c>
       <c r="S28" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="T28" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="U28" t="n">
         <v>1.3</v>
@@ -4056,10 +4056,10 @@
         <v>1.03</v>
       </c>
       <c r="W28" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="X28" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="Y28" t="n">
         <v>2.12</v>
@@ -4071,13 +4071,13 @@
         <v>4.43</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.07</v>
+        <v>1.98</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>1.8</v>
       </c>
       <c r="Q29" t="n">
-        <v>5.7</v>
+        <v>5.98</v>
       </c>
       <c r="R29" t="n">
         <v>1.65</v>
@@ -4191,13 +4191,13 @@
         <v>2.1</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AA29" t="n">
-        <v>6.05</v>
+        <v>6.09</v>
       </c>
       <c r="AB29" t="n">
         <v>1.06</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M30" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="O30" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X30" t="n">
         <v>2.35</v>
       </c>
-      <c r="M30" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N30" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O30" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="X30" t="n">
-        <v>3.22</v>
-      </c>
       <c r="Y30" t="n">
-        <v>1.9</v>
+        <v>2.35</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.25</v>
+        <v>4.7</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.69</v>
+        <v>2.04</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.03</v>
+        <v>1.71</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,77 +4410,77 @@
         </is>
       </c>
       <c r="L31" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="M31" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O31" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X31" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="Y31" t="n">
         <v>1.9</v>
       </c>
-      <c r="M31" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="N31" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="O31" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P31" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>4.76</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="T31" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="U31" t="n">
+      <c r="Z31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB31" t="n">
         <v>1.28</v>
       </c>
-      <c r="V31" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="X31" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z31" t="n">
+      <c r="AC31" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH31" t="n">
         <v>1.53</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.62</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.43</v>
+        <v>3</v>
       </c>
       <c r="M32" t="n">
-        <v>2.59</v>
+        <v>2.51</v>
       </c>
       <c r="N32" t="n">
-        <v>3.11</v>
+        <v>2.58</v>
       </c>
       <c r="O32" t="n">
-        <v>3.26</v>
+        <v>3.95</v>
       </c>
       <c r="P32" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.88</v>
+        <v>3.52</v>
       </c>
       <c r="R32" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="S32" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="T32" t="n">
-        <v>4.7</v>
+        <v>4.33</v>
       </c>
       <c r="U32" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="V32" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="W32" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="X32" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="Y32" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AA32" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.7</v>
+        <v>2.42</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3</v>
+        <v>2.43</v>
       </c>
       <c r="M33" t="n">
-        <v>2.51</v>
+        <v>2.59</v>
       </c>
       <c r="N33" t="n">
-        <v>2.58</v>
+        <v>3.11</v>
       </c>
       <c r="O33" t="n">
-        <v>4.43</v>
+        <v>3.26</v>
       </c>
       <c r="P33" t="n">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.53</v>
+        <v>4.88</v>
       </c>
       <c r="R33" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="S33" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="T33" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="U33" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="V33" t="n">
         <v>1.16</v>
       </c>
-      <c r="V33" t="n">
-        <v>1.12</v>
-      </c>
       <c r="W33" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="X33" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="Y33" t="n">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="Z33" t="n">
         <v>1.28</v>
       </c>
       <c r="AA33" t="n">
-        <v>6.3</v>
+        <v>7</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.42</v>
+        <v>2.7</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.28</v>
+        <v>1.52</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4941,7 +4941,7 @@
         <v>2.01</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="R35" t="n">
         <v>1.43</v>
@@ -5064,34 +5064,34 @@
         <v>6</v>
       </c>
       <c r="O36" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="P36" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="Q36" t="n">
-        <v>6.48</v>
+        <v>6.49</v>
       </c>
       <c r="R36" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S36" t="n">
-        <v>2.42</v>
+        <v>2.39</v>
       </c>
       <c r="T36" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="U36" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="V36" t="n">
         <v>1.05</v>
       </c>
       <c r="W36" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="X36" t="n">
-        <v>2.47</v>
+        <v>2.43</v>
       </c>
       <c r="Y36" t="n">
         <v>2.4</v>
@@ -5100,16 +5100,16 @@
         <v>1.5</v>
       </c>
       <c r="AA36" t="n">
-        <v>4.4</v>
+        <v>4.55</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>1.28</v>
       </c>
       <c r="AH36" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5325,10 +5325,10 @@
         <v>2.26</v>
       </c>
       <c r="P38" t="n">
-        <v>2.32</v>
+        <v>2.21</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.6</v>
+        <v>4.71</v>
       </c>
       <c r="R38" t="n">
         <v>1.33</v>
@@ -5346,10 +5346,10 @@
         <v>1.01</v>
       </c>
       <c r="W38" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X38" t="n">
-        <v>3.5</v>
+        <v>3.69</v>
       </c>
       <c r="Y38" t="n">
         <v>1.8</v>
@@ -5358,16 +5358,16 @@
         <v>1.9</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.83</v>
+        <v>3.02</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AC38" t="n">
         <v>1.72</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>

--- a/jogos_2025-09-05.xlsx
+++ b/jogos_2025-09-05.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.55</v>
+        <v>2.93</v>
       </c>
       <c r="M3" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="N3" t="n">
-        <v>2.55</v>
+        <v>2.18</v>
       </c>
       <c r="O3" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.93</v>
+        <v>2.55</v>
       </c>
       <c r="M4" t="n">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="N4" t="n">
-        <v>2.18</v>
+        <v>2.55</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z4" t="n">
         <v>1.8</v>
       </c>
-      <c r="Z4" t="n">
-        <v>1.89</v>
-      </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>4.91</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.56</v>
+        <v>2.6</v>
       </c>
       <c r="P8" t="n">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.45</v>
+        <v>4.64</v>
       </c>
       <c r="R8" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="S8" t="n">
-        <v>2.33</v>
+        <v>2.52</v>
       </c>
       <c r="T8" t="n">
-        <v>3.56</v>
+        <v>3.25</v>
       </c>
       <c r="U8" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="V8" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W8" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="X8" t="n">
-        <v>2.45</v>
+        <v>2.74</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.46</v>
+        <v>2.15</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.91</v>
+        <v>3.96</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.41</v>
+        <v>1.73</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1710,52 +1710,52 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.64</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="M17" t="n">
-        <v>2.62</v>
+        <v>4.05</v>
       </c>
       <c r="N17" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="O17" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>7.27</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.3</v>
+        <v>1.58</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.28</v>
+        <v>2.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>8</v>
+        <v>2.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.05</v>
+        <v>1.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,62 +2733,62 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.39</v>
+        <v>1.74</v>
       </c>
       <c r="M18" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="N18" t="n">
-        <v>2.2</v>
+        <v>6</v>
       </c>
       <c r="O18" t="n">
-        <v>4.76</v>
+        <v>2.71</v>
       </c>
       <c r="P18" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.06</v>
+        <v>7.27</v>
       </c>
       <c r="R18" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="S18" t="n">
-        <v>2.12</v>
+        <v>1.92</v>
       </c>
       <c r="T18" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="U18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="V18" t="n">
         <v>1.19</v>
       </c>
-      <c r="V18" t="n">
-        <v>1.1</v>
-      </c>
       <c r="W18" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="X18" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="Z18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AD18" t="n">
         <v>1.36</v>
       </c>
-      <c r="AA18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.54</v>
-      </c>
       <c r="AE18" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.24</v>
+        <v>1.82</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O19" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W19" t="n">
         <v>1.6</v>
       </c>
-      <c r="M19" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="N19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.58</v>
+        <v>2.9</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.2</v>
+        <v>1.36</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.2</v>
+        <v>5.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>1.08</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.89</v>
+        <v>1.48</v>
       </c>
       <c r="M20" t="n">
-        <v>3.18</v>
+        <v>3.94</v>
       </c>
       <c r="N20" t="n">
-        <v>2.18</v>
+        <v>5.2</v>
       </c>
       <c r="O20" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="P20" t="n">
-        <v>2.05</v>
+        <v>2.47</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.8</v>
+        <v>5.83</v>
       </c>
       <c r="R20" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="T20" t="n">
-        <v>2.62</v>
+        <v>2.46</v>
       </c>
       <c r="U20" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="V20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W20" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="X20" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.04</v>
+        <v>2.59</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.36</v>
+        <v>2.4</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,58 +3120,58 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.67</v>
+        <v>4.8</v>
       </c>
       <c r="M21" t="n">
-        <v>3.02</v>
+        <v>3.84</v>
       </c>
       <c r="N21" t="n">
-        <v>2.42</v>
+        <v>1.54</v>
       </c>
       <c r="O21" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="P21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X21" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z21" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q21" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="X21" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1.81</v>
-      </c>
       <c r="AA21" t="n">
-        <v>3.14</v>
+        <v>2.65</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.27</v>
+        <v>1.39</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AD21" t="n">
         <v>2</v>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.41</v>
+        <v>1.15</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,58 +3249,58 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4.8</v>
+        <v>2.67</v>
       </c>
       <c r="M22" t="n">
-        <v>3.84</v>
+        <v>3.02</v>
       </c>
       <c r="N22" t="n">
-        <v>1.54</v>
+        <v>2.42</v>
       </c>
       <c r="O22" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="P22" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.05</v>
+        <v>3.12</v>
       </c>
       <c r="R22" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="S22" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="T22" t="n">
-        <v>2.38</v>
+        <v>2.85</v>
       </c>
       <c r="U22" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="V22" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W22" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="X22" t="n">
-        <v>3.88</v>
+        <v>3.22</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.65</v>
+        <v>3.14</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AD22" t="n">
         <v>2</v>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.15</v>
+        <v>1.41</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,22 +3378,22 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.66</v>
+        <v>2.89</v>
       </c>
       <c r="M23" t="n">
-        <v>3.55</v>
+        <v>3.18</v>
       </c>
       <c r="N23" t="n">
-        <v>1.77</v>
+        <v>2.18</v>
       </c>
       <c r="O23" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="P23" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.38</v>
+        <v>2.8</v>
       </c>
       <c r="R23" t="n">
         <v>1.35</v>
@@ -3402,37 +3402,37 @@
         <v>3</v>
       </c>
       <c r="T23" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="U23" t="n">
         <v>1.44</v>
       </c>
       <c r="V23" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="X23" t="n">
         <v>3.6</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,77 +3507,77 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.48</v>
+        <v>3.66</v>
       </c>
       <c r="M24" t="n">
-        <v>3.94</v>
+        <v>3.55</v>
       </c>
       <c r="N24" t="n">
-        <v>5.2</v>
+        <v>1.77</v>
       </c>
       <c r="O24" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="P24" t="n">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="Q24" t="n">
-        <v>5.83</v>
+        <v>2.38</v>
       </c>
       <c r="R24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
         <v>1.3</v>
       </c>
-      <c r="S24" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X24" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AH24" t="n">
-        <v>2.4</v>
+        <v>1.22</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.86</v>
+        <v>2.35</v>
       </c>
       <c r="M29" t="n">
-        <v>2.91</v>
+        <v>3.3</v>
       </c>
       <c r="N29" t="n">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="O29" t="n">
-        <v>2.61</v>
+        <v>2.87</v>
       </c>
       <c r="P29" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X29" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z29" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q29" t="n">
-        <v>5.98</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="T29" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="X29" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AA29" t="n">
-        <v>6.09</v>
+        <v>3.25</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.06</v>
+        <v>1.28</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.51</v>
+        <v>1.69</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.46</v>
+        <v>2.03</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.35</v>
+        <v>1.86</v>
       </c>
       <c r="M31" t="n">
-        <v>3.3</v>
+        <v>2.91</v>
       </c>
       <c r="N31" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="O31" t="n">
-        <v>2.87</v>
+        <v>2.61</v>
       </c>
       <c r="P31" t="n">
-        <v>2.21</v>
+        <v>1.8</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.4</v>
+        <v>5.98</v>
       </c>
       <c r="R31" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="T31" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Z31" t="n">
         <v>1.36</v>
       </c>
-      <c r="S31" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="X31" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AA31" t="n">
-        <v>3.25</v>
+        <v>6.09</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.28</v>
+        <v>1.06</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.69</v>
+        <v>2.51</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.03</v>
+        <v>1.46</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3</v>
+        <v>2.43</v>
       </c>
       <c r="M32" t="n">
-        <v>2.51</v>
+        <v>2.59</v>
       </c>
       <c r="N32" t="n">
-        <v>2.58</v>
+        <v>3.11</v>
       </c>
       <c r="O32" t="n">
-        <v>3.95</v>
+        <v>3.26</v>
       </c>
       <c r="P32" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.52</v>
+        <v>4.88</v>
       </c>
       <c r="R32" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="S32" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="T32" t="n">
-        <v>4.33</v>
+        <v>4.7</v>
       </c>
       <c r="U32" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="V32" t="n">
         <v>1.16</v>
       </c>
-      <c r="V32" t="n">
-        <v>1.12</v>
-      </c>
       <c r="W32" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="X32" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="Y32" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AA32" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.42</v>
+        <v>2.7</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.43</v>
+        <v>3</v>
       </c>
       <c r="M33" t="n">
-        <v>2.59</v>
+        <v>2.51</v>
       </c>
       <c r="N33" t="n">
-        <v>3.11</v>
+        <v>2.58</v>
       </c>
       <c r="O33" t="n">
-        <v>3.26</v>
+        <v>3.95</v>
       </c>
       <c r="P33" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.88</v>
+        <v>3.52</v>
       </c>
       <c r="R33" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="S33" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="T33" t="n">
-        <v>4.7</v>
+        <v>4.33</v>
       </c>
       <c r="U33" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="V33" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="W33" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="X33" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="Y33" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AA33" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.7</v>
+        <v>2.42</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>

--- a/jogos_2025-09-05.xlsx
+++ b/jogos_2025-09-05.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.93</v>
+        <v>2.54</v>
       </c>
       <c r="M3" t="n">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="N3" t="n">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.55</v>
+        <v>2.93</v>
       </c>
       <c r="M4" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="N4" t="n">
-        <v>2.55</v>
+        <v>2.18</v>
       </c>
       <c r="O4" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="M5" t="n">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="N5" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="O5" t="n">
-        <v>3.56</v>
+        <v>3.4</v>
       </c>
       <c r="P5" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="R5" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="S5" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="T5" t="n">
-        <v>3.56</v>
+        <v>3.4</v>
       </c>
       <c r="U5" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="V5" t="n">
         <v>1.05</v>
       </c>
       <c r="W5" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="X5" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AA5" t="n">
         <v>4.91</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>1.33</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1458,19 +1458,19 @@
         <v>1.98</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.64</v>
+        <v>4.69</v>
       </c>
       <c r="R8" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S8" t="n">
         <v>2.52</v>
       </c>
       <c r="T8" t="n">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="U8" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="V8" t="n">
         <v>1.03</v>
@@ -1485,19 +1485,19 @@
         <v>2.15</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.96</v>
+        <v>4.01</v>
       </c>
       <c r="AB8" t="n">
         <v>1.19</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>1.28</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2217,37 +2217,37 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="M14" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>3.89</v>
+        <v>3.8</v>
       </c>
       <c r="O14" t="n">
-        <v>2.31</v>
+        <v>2.56</v>
       </c>
       <c r="P14" t="n">
         <v>2.04</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.55</v>
+        <v>4.06</v>
       </c>
       <c r="R14" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S14" t="n">
         <v>2.9</v>
       </c>
       <c r="T14" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="U14" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="V14" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W14" t="n">
         <v>1.28</v>
@@ -2256,22 +2256,22 @@
         <v>3.2</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AA14" t="n">
         <v>3.55</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>4.94</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="M17" t="n">
-        <v>4.05</v>
+        <v>2.62</v>
       </c>
       <c r="N17" t="n">
-        <v>4.8</v>
+        <v>6.46</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>7.22</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.58</v>
+        <v>3.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.2</v>
+        <v>1.26</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.2</v>
+        <v>8</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.6</v>
+        <v>1.05</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.74</v>
+        <v>3.65</v>
       </c>
       <c r="M18" t="n">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="N18" t="n">
-        <v>6</v>
+        <v>2.25</v>
       </c>
       <c r="O18" t="n">
-        <v>2.71</v>
+        <v>4.76</v>
       </c>
       <c r="P18" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="Q18" t="n">
-        <v>7.27</v>
+        <v>3.06</v>
       </c>
       <c r="R18" t="n">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="S18" t="n">
-        <v>1.92</v>
+        <v>2.11</v>
       </c>
       <c r="T18" t="n">
-        <v>4.5</v>
+        <v>3.98</v>
       </c>
       <c r="U18" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="V18" t="n">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="W18" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="X18" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="Y18" t="n">
-        <v>3.3</v>
+        <v>2.98</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AA18" t="n">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.84</v>
+        <v>2.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.36</v>
+        <v>1.54</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.82</v>
+        <v>1.24</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.39</v>
+        <v>1.6</v>
       </c>
       <c r="M19" t="n">
-        <v>2.7</v>
+        <v>4.05</v>
       </c>
       <c r="N19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z19" t="n">
         <v>2.2</v>
       </c>
-      <c r="O19" t="n">
-        <v>4.76</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W19" t="n">
+      <c r="AA19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB19" t="n">
         <v>1.6</v>
       </c>
-      <c r="X19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AC19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.48</v>
+        <v>4</v>
       </c>
       <c r="M20" t="n">
-        <v>3.94</v>
+        <v>3.5</v>
       </c>
       <c r="N20" t="n">
-        <v>5.2</v>
+        <v>1.7</v>
       </c>
       <c r="O20" t="n">
-        <v>2</v>
+        <v>4.65</v>
       </c>
       <c r="P20" t="n">
-        <v>2.47</v>
+        <v>2.12</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.83</v>
+        <v>2.34</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="S20" t="n">
-        <v>3.4</v>
+        <v>2.89</v>
       </c>
       <c r="T20" t="n">
-        <v>2.46</v>
+        <v>2.76</v>
       </c>
       <c r="U20" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="V20" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="W20" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="X20" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.6</v>
+        <v>1.89</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.2</v>
+        <v>1.89</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.59</v>
+        <v>3.25</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>4.8</v>
+        <v>1.5</v>
       </c>
       <c r="M21" t="n">
-        <v>3.84</v>
+        <v>4.16</v>
       </c>
       <c r="N21" t="n">
-        <v>1.54</v>
+        <v>5.5</v>
       </c>
       <c r="O21" t="n">
-        <v>5</v>
+        <v>2.06</v>
       </c>
       <c r="P21" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.05</v>
+        <v>4.7</v>
       </c>
       <c r="R21" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S21" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="T21" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="U21" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="V21" t="n">
         <v>1.04</v>
       </c>
       <c r="W21" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X21" t="n">
-        <v>3.88</v>
+        <v>4.4</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.65</v>
+        <v>2.43</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AD21" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.15</v>
+        <v>2.28</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3249,25 +3249,25 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="M22" t="n">
-        <v>3.02</v>
+        <v>3.2</v>
       </c>
       <c r="N22" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="O22" t="n">
-        <v>3.2</v>
+        <v>3.36</v>
       </c>
       <c r="P22" t="n">
         <v>2.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.12</v>
+        <v>3.05</v>
       </c>
       <c r="R22" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S22" t="n">
         <v>2.8</v>
@@ -3279,22 +3279,22 @@
         <v>1.38</v>
       </c>
       <c r="V22" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W22" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="X22" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA22" t="n">
         <v>3.22</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>3.14</v>
       </c>
       <c r="AB22" t="n">
         <v>1.27</v>
@@ -3303,7 +3303,7 @@
         <v>1.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.89</v>
+        <v>4.8</v>
       </c>
       <c r="M23" t="n">
-        <v>3.18</v>
+        <v>4</v>
       </c>
       <c r="N23" t="n">
-        <v>2.18</v>
+        <v>1.53</v>
       </c>
       <c r="O23" t="n">
-        <v>3.3</v>
+        <v>5.3</v>
       </c>
       <c r="P23" t="n">
-        <v>2.05</v>
+        <v>2.31</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.8</v>
+        <v>1.98</v>
       </c>
       <c r="R23" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="T23" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="U23" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="V23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W23" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="X23" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.85</v>
+        <v>2.09</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.04</v>
+        <v>2.65</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.36</v>
+        <v>1.12</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.66</v>
+        <v>2.9</v>
       </c>
       <c r="M24" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="N24" t="n">
-        <v>1.77</v>
+        <v>2.2</v>
       </c>
       <c r="O24" t="n">
-        <v>4.5</v>
+        <v>3.28</v>
       </c>
       <c r="P24" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.38</v>
+        <v>2.83</v>
       </c>
       <c r="R24" t="n">
         <v>1.35</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T24" t="n">
-        <v>2.65</v>
+        <v>2.72</v>
       </c>
       <c r="U24" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V24" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W24" t="n">
         <v>1.23</v>
       </c>
       <c r="X24" t="n">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AC24" t="n">
         <v>1.75</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4152,77 +4152,77 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="M29" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N29" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="O29" t="n">
-        <v>2.87</v>
+        <v>2.83</v>
       </c>
       <c r="P29" t="n">
-        <v>2.21</v>
+        <v>2.09</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.4</v>
+        <v>3.66</v>
       </c>
       <c r="R29" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S29" t="n">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="T29" t="n">
-        <v>2.72</v>
+        <v>2.65</v>
       </c>
       <c r="U29" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V29" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="X29" t="n">
-        <v>3.22</v>
+        <v>3.28</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.25</v>
+        <v>3.03</v>
       </c>
       <c r="AB29" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
         <v>1.28</v>
       </c>
-      <c r="AC29" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH29" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4281,25 +4281,25 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="M30" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="N30" t="n">
-        <v>3.86</v>
+        <v>3.45</v>
       </c>
       <c r="O30" t="n">
-        <v>2.76</v>
+        <v>2.73</v>
       </c>
       <c r="P30" t="n">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.5</v>
+        <v>4.77</v>
       </c>
       <c r="R30" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S30" t="n">
         <v>2.5</v>
@@ -4314,28 +4314,28 @@
         <v>1.05</v>
       </c>
       <c r="W30" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="X30" t="n">
-        <v>2.35</v>
+        <v>2.58</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AA30" t="n">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>1.34</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="M31" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="N31" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="O31" t="n">
         <v>2.61</v>
@@ -4425,10 +4425,10 @@
         <v>1.8</v>
       </c>
       <c r="Q31" t="n">
-        <v>5.98</v>
+        <v>5.7</v>
       </c>
       <c r="R31" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="S31" t="n">
         <v>2.16</v>
@@ -4443,16 +4443,16 @@
         <v>1.08</v>
       </c>
       <c r="W31" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X31" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AA31" t="n">
         <v>6.09</v>
@@ -4539,16 +4539,16 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.43</v>
+        <v>2.37</v>
       </c>
       <c r="M32" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="N32" t="n">
-        <v>3.11</v>
+        <v>3.55</v>
       </c>
       <c r="O32" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="P32" t="n">
         <v>1.69</v>
@@ -4557,31 +4557,31 @@
         <v>4.88</v>
       </c>
       <c r="R32" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="S32" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="T32" t="n">
         <v>4.7</v>
       </c>
       <c r="U32" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="V32" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W32" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="X32" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Y32" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AA32" t="n">
         <v>7</v>
@@ -4590,10 +4590,10 @@
         <v>1.03</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AH32" t="n">
         <v>1.52</v>
@@ -4668,55 +4668,55 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="M33" t="n">
-        <v>2.51</v>
+        <v>2.6</v>
       </c>
       <c r="N33" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="O33" t="n">
-        <v>3.95</v>
+        <v>4.23</v>
       </c>
       <c r="P33" t="n">
         <v>1.71</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="R33" t="n">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="S33" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="T33" t="n">
         <v>4.33</v>
       </c>
       <c r="U33" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="V33" t="n">
         <v>1.16</v>
       </c>
-      <c r="V33" t="n">
-        <v>1.12</v>
-      </c>
       <c r="W33" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="X33" t="n">
-        <v>1.96</v>
+        <v>2.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AA33" t="n">
         <v>6.4</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AC33" t="n">
         <v>2.42</v>
@@ -4738,7 +4738,7 @@
         <v>1.42</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.7</v>
+        <v>2.51</v>
       </c>
       <c r="M34" t="n">
-        <v>3.45</v>
+        <v>3.28</v>
       </c>
       <c r="N34" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="M35" t="n">
-        <v>3.25</v>
+        <v>3.13</v>
       </c>
       <c r="N35" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="O35" t="n">
         <v>4.32</v>
@@ -4962,13 +4962,13 @@
         <v>1.33</v>
       </c>
       <c r="X35" t="n">
-        <v>2.81</v>
+        <v>2.89</v>
       </c>
       <c r="Y35" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AA35" t="n">
         <v>3.72</v>
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="M36" t="n">
-        <v>3.37</v>
+        <v>3.55</v>
       </c>
       <c r="N36" t="n">
-        <v>6</v>
+        <v>5.68</v>
       </c>
       <c r="O36" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="P36" t="n">
         <v>2.06</v>
       </c>
       <c r="Q36" t="n">
-        <v>6.49</v>
+        <v>6.66</v>
       </c>
       <c r="R36" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S36" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X36" t="n">
         <v>2.39</v>
       </c>
-      <c r="T36" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="X36" t="n">
-        <v>2.43</v>
-      </c>
       <c r="Y36" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="Z36" t="n">
         <v>1.5</v>
       </c>
       <c r="AA36" t="n">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.34</v>
+        <v>2.39</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>1.28</v>
       </c>
       <c r="AH36" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="M38" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="N38" t="n">
-        <v>4.7</v>
+        <v>3.85</v>
       </c>
       <c r="O38" t="n">
         <v>2.26</v>
@@ -5337,7 +5337,7 @@
         <v>3.04</v>
       </c>
       <c r="T38" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="U38" t="n">
         <v>1.44</v>
@@ -5346,16 +5346,16 @@
         <v>1.01</v>
       </c>
       <c r="W38" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X38" t="n">
         <v>3.69</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AA38" t="n">
         <v>3.02</v>
@@ -5367,7 +5367,7 @@
         <v>1.72</v>
       </c>
       <c r="AD38" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>

--- a/jogos_2025-09-05.xlsx
+++ b/jogos_2025-09-05.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.54</v>
+        <v>2.93</v>
       </c>
       <c r="M3" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="N3" t="n">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="O3" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z3" t="n">
         <v>1.89</v>
       </c>
-      <c r="Z3" t="n">
-        <v>1.81</v>
-      </c>
       <c r="AA3" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.93</v>
+        <v>2.54</v>
       </c>
       <c r="M4" t="n">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="N4" t="n">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1056,49 +1056,49 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="M5" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="N5" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="O5" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P5" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="R5" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="S5" t="n">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="T5" t="n">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="U5" t="n">
         <v>1.25</v>
       </c>
       <c r="V5" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W5" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="X5" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.42</v>
+        <v>2.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AA5" t="n">
         <v>4.91</v>
@@ -1107,10 +1107,10 @@
         <v>1.12</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -1194,52 +1194,52 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -1452,52 +1452,52 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.69</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
-        <v>3.22</v>
+        <v>3.15</v>
       </c>
       <c r="N11" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O11" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
         <v>2.16</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.68</v>
+        <v>1.56</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2217,58 +2217,58 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="N14" t="n">
-        <v>3.8</v>
+        <v>3.89</v>
       </c>
       <c r="O14" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="P14" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.06</v>
+        <v>4.1</v>
       </c>
       <c r="R14" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S14" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="T14" t="n">
         <v>2.75</v>
       </c>
       <c r="U14" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="V14" t="n">
         <v>1.06</v>
       </c>
       <c r="W14" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="X14" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AA14" t="n">
         <v>3.55</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AD14" t="n">
         <v>1.9</v>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.85</v>
+        <v>3.65</v>
       </c>
       <c r="M17" t="n">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="N17" t="n">
-        <v>6.46</v>
+        <v>2.25</v>
       </c>
       <c r="O17" t="n">
-        <v>2.69</v>
+        <v>4.76</v>
       </c>
       <c r="P17" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="Q17" t="n">
-        <v>7.22</v>
+        <v>3.06</v>
       </c>
       <c r="R17" t="n">
-        <v>1.81</v>
+        <v>1.62</v>
       </c>
       <c r="S17" t="n">
-        <v>1.94</v>
+        <v>2.11</v>
       </c>
       <c r="T17" t="n">
-        <v>4.5</v>
+        <v>3.98</v>
       </c>
       <c r="U17" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="V17" t="n">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="W17" t="n">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="X17" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.5</v>
+        <v>2.98</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="AA17" t="n">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.79</v>
+        <v>2.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.83</v>
+        <v>1.24</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.65</v>
+        <v>1.6</v>
       </c>
       <c r="M18" t="n">
-        <v>2.76</v>
+        <v>4.05</v>
       </c>
       <c r="N18" t="n">
-        <v>2.25</v>
+        <v>4.8</v>
       </c>
       <c r="O18" t="n">
-        <v>4.76</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.98</v>
+        <v>1.58</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.34</v>
+        <v>2.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>5.5</v>
+        <v>2.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.08</v>
+        <v>1.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="M19" t="n">
-        <v>4.05</v>
+        <v>2.62</v>
       </c>
       <c r="N19" t="n">
-        <v>4.8</v>
+        <v>6.46</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>7.22</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.58</v>
+        <v>3.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.2</v>
+        <v>1.26</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.2</v>
+        <v>8</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>1.05</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M20" t="n">
         <v>4</v>
       </c>
-      <c r="M20" t="n">
-        <v>3.5</v>
-      </c>
       <c r="N20" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="O20" t="n">
-        <v>4.65</v>
+        <v>5.3</v>
       </c>
       <c r="P20" t="n">
-        <v>2.12</v>
+        <v>2.31</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.34</v>
+        <v>1.98</v>
       </c>
       <c r="R20" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="S20" t="n">
-        <v>2.89</v>
+        <v>3.14</v>
       </c>
       <c r="T20" t="n">
-        <v>2.76</v>
+        <v>2.44</v>
       </c>
       <c r="U20" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AB20" t="n">
         <v>1.39</v>
       </c>
-      <c r="V20" t="n">
-        <v>1</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="X20" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AC20" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,77 +3120,77 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="M21" t="n">
-        <v>4.16</v>
+        <v>3.5</v>
       </c>
       <c r="N21" t="n">
-        <v>5.5</v>
+        <v>1.7</v>
       </c>
       <c r="O21" t="n">
-        <v>2.06</v>
+        <v>4.65</v>
       </c>
       <c r="P21" t="n">
-        <v>2.36</v>
+        <v>2.12</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.7</v>
+        <v>2.34</v>
       </c>
       <c r="R21" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB21" t="n">
         <v>1.28</v>
       </c>
-      <c r="S21" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W21" t="n">
+      <c r="AC21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH21" t="n">
         <v>1.2</v>
-      </c>
-      <c r="X21" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>2.28</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="M22" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N22" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="O22" t="n">
-        <v>3.36</v>
+        <v>3.28</v>
       </c>
       <c r="P22" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q22" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S22" t="n">
         <v>3.05</v>
       </c>
-      <c r="R22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.8</v>
-      </c>
       <c r="T22" t="n">
-        <v>2.85</v>
+        <v>2.72</v>
       </c>
       <c r="U22" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="V22" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W22" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="X22" t="n">
-        <v>3.14</v>
+        <v>3.42</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.22</v>
+        <v>3.04</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.01</v>
+        <v>2.07</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>4.8</v>
+        <v>1.5</v>
       </c>
       <c r="M23" t="n">
-        <v>4</v>
+        <v>4.16</v>
       </c>
       <c r="N23" t="n">
-        <v>1.53</v>
+        <v>5.5</v>
       </c>
       <c r="O23" t="n">
-        <v>5.3</v>
+        <v>2.06</v>
       </c>
       <c r="P23" t="n">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.98</v>
+        <v>4.7</v>
       </c>
       <c r="R23" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="S23" t="n">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="T23" t="n">
-        <v>2.44</v>
+        <v>2.39</v>
       </c>
       <c r="U23" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="V23" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W23" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X23" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="Y23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC23" t="n">
         <v>1.67</v>
       </c>
-      <c r="Z23" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AD23" t="n">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.12</v>
+        <v>2.28</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="M24" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N24" t="n">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="O24" t="n">
-        <v>3.28</v>
+        <v>3.36</v>
       </c>
       <c r="P24" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.83</v>
+        <v>3.05</v>
       </c>
       <c r="R24" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="T24" t="n">
-        <v>2.72</v>
+        <v>2.85</v>
       </c>
       <c r="U24" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V24" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W24" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="X24" t="n">
-        <v>3.42</v>
+        <v>3.14</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.04</v>
+        <v>3.22</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -4023,16 +4023,16 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="M28" t="n">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="N28" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="O28" t="n">
-        <v>2.81</v>
+        <v>2.97</v>
       </c>
       <c r="P28" t="n">
         <v>1.98</v>
@@ -4041,10 +4041,10 @@
         <v>4.22</v>
       </c>
       <c r="R28" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S28" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="T28" t="n">
         <v>3.28</v>
@@ -4068,16 +4068,16 @@
         <v>1.6</v>
       </c>
       <c r="AA28" t="n">
-        <v>4.43</v>
+        <v>4.42</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AC28" t="n">
         <v>1.98</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>1.3</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="M30" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N30" t="n">
-        <v>3.45</v>
+        <v>4.6</v>
       </c>
       <c r="O30" t="n">
-        <v>2.73</v>
+        <v>2.61</v>
       </c>
       <c r="P30" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.77</v>
+        <v>5.7</v>
       </c>
       <c r="R30" t="n">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="S30" t="n">
-        <v>2.5</v>
+        <v>2.16</v>
       </c>
       <c r="T30" t="n">
-        <v>3.34</v>
+        <v>4.15</v>
       </c>
       <c r="U30" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="V30" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="W30" t="n">
-        <v>1.48</v>
+        <v>1.64</v>
       </c>
       <c r="X30" t="n">
-        <v>2.58</v>
+        <v>2.22</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.4</v>
+        <v>2.97</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.54</v>
+        <v>1.37</v>
       </c>
       <c r="AA30" t="n">
-        <v>4.75</v>
+        <v>6.09</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.07</v>
+        <v>2.51</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.69</v>
+        <v>1.46</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.87</v>
+        <v>2.04</v>
       </c>
       <c r="M31" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N31" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="O31" t="n">
-        <v>2.61</v>
+        <v>2.73</v>
       </c>
       <c r="P31" t="n">
-        <v>1.8</v>
+        <v>2.04</v>
       </c>
       <c r="Q31" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="R31" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="S31" t="n">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="T31" t="n">
-        <v>4.15</v>
+        <v>3.34</v>
       </c>
       <c r="U31" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="V31" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="W31" t="n">
-        <v>1.64</v>
+        <v>1.48</v>
       </c>
       <c r="X31" t="n">
-        <v>2.22</v>
+        <v>2.58</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.97</v>
+        <v>2.4</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="AA31" t="n">
-        <v>6.09</v>
+        <v>4.75</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.51</v>
+        <v>2.02</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -5055,31 +5055,31 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="M36" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="N36" t="n">
-        <v>5.68</v>
+        <v>5</v>
       </c>
       <c r="O36" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="P36" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="Q36" t="n">
-        <v>6.66</v>
+        <v>5.8</v>
       </c>
       <c r="R36" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="S36" t="n">
         <v>2.38</v>
       </c>
       <c r="T36" t="n">
-        <v>3.48</v>
+        <v>3.25</v>
       </c>
       <c r="U36" t="n">
         <v>1.26</v>
@@ -5088,7 +5088,7 @@
         <v>1.1</v>
       </c>
       <c r="W36" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="X36" t="n">
         <v>2.39</v>
@@ -5103,13 +5103,13 @@
         <v>4.5</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.39</v>
+        <v>2.63</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH36" t="n">
-        <v>2.19</v>
+        <v>1.97</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>

--- a/jogos_2025-09-05.xlsx
+++ b/jogos_2025-09-05.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.93</v>
+        <v>2.54</v>
       </c>
       <c r="M3" t="n">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="N3" t="n">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.54</v>
+        <v>2.93</v>
       </c>
       <c r="M4" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="N4" t="n">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="O4" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z4" t="n">
         <v>1.89</v>
       </c>
-      <c r="Z4" t="n">
-        <v>1.81</v>
-      </c>
       <c r="AA4" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.91</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O6" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="P7" t="n">
         <v>2.05</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.37</v>
+        <v>4.2</v>
       </c>
       <c r="R7" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="S7" t="n">
         <v>2.62</v>
       </c>
       <c r="T7" t="n">
-        <v>2.9</v>
+        <v>3.27</v>
       </c>
       <c r="U7" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W7" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="X7" t="n">
-        <v>3.2</v>
+        <v>2.74</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1833,58 +1833,58 @@
         <v>2</v>
       </c>
       <c r="M11" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N11" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="M12" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q12" t="n">
         <v>3.15</v>
       </c>
-      <c r="N12" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.96</v>
+        <v>2.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>4.91</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.65</v>
+        <v>1.6</v>
       </c>
       <c r="M17" t="n">
-        <v>2.76</v>
+        <v>4.05</v>
       </c>
       <c r="N17" t="n">
-        <v>2.25</v>
+        <v>4.8</v>
       </c>
       <c r="O17" t="n">
-        <v>4.76</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.98</v>
+        <v>1.58</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.34</v>
+        <v>2.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>5.5</v>
+        <v>2.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.08</v>
+        <v>1.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.6</v>
+        <v>3.65</v>
       </c>
       <c r="M18" t="n">
-        <v>4.05</v>
+        <v>2.76</v>
       </c>
       <c r="N18" t="n">
-        <v>4.8</v>
+        <v>2.25</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.58</v>
+        <v>2.98</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.2</v>
+        <v>1.34</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.2</v>
+        <v>5.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.6</v>
+        <v>1.08</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="M20" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N20" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="O20" t="n">
-        <v>5.3</v>
+        <v>4.65</v>
       </c>
       <c r="P20" t="n">
-        <v>2.31</v>
+        <v>2.12</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.98</v>
+        <v>2.34</v>
       </c>
       <c r="R20" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="S20" t="n">
-        <v>3.14</v>
+        <v>2.89</v>
       </c>
       <c r="T20" t="n">
-        <v>2.44</v>
+        <v>2.76</v>
       </c>
       <c r="U20" t="n">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="V20" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="W20" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="X20" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.67</v>
+        <v>1.89</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.09</v>
+        <v>1.89</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.65</v>
+        <v>3.25</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="M21" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="N21" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="O21" t="n">
-        <v>4.65</v>
+        <v>3.28</v>
       </c>
       <c r="P21" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.34</v>
+        <v>2.83</v>
       </c>
       <c r="R21" t="n">
         <v>1.35</v>
       </c>
       <c r="S21" t="n">
-        <v>2.89</v>
+        <v>3.05</v>
       </c>
       <c r="T21" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="U21" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="V21" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="X21" t="n">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AC21" t="n">
         <v>1.75</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>1.24</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.9</v>
+        <v>4.8</v>
       </c>
       <c r="M22" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="N22" t="n">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="O22" t="n">
-        <v>3.28</v>
+        <v>5.3</v>
       </c>
       <c r="P22" t="n">
-        <v>2.05</v>
+        <v>2.31</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.83</v>
+        <v>1.98</v>
       </c>
       <c r="R22" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="S22" t="n">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="T22" t="n">
-        <v>2.72</v>
+        <v>2.44</v>
       </c>
       <c r="U22" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="V22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W22" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="X22" t="n">
-        <v>3.42</v>
+        <v>3.9</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.84</v>
+        <v>1.67</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.87</v>
+        <v>2.09</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.04</v>
+        <v>2.65</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.07</v>
+        <v>1.98</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.35</v>
+        <v>1.12</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.5</v>
+        <v>2.65</v>
       </c>
       <c r="M23" t="n">
-        <v>4.16</v>
+        <v>3.2</v>
       </c>
       <c r="N23" t="n">
-        <v>5.5</v>
+        <v>2.44</v>
       </c>
       <c r="O23" t="n">
-        <v>2.06</v>
+        <v>3.36</v>
       </c>
       <c r="P23" t="n">
-        <v>2.36</v>
+        <v>2.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.7</v>
+        <v>3.05</v>
       </c>
       <c r="R23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W23" t="n">
         <v>1.28</v>
       </c>
-      <c r="S23" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.2</v>
-      </c>
       <c r="X23" t="n">
-        <v>4.4</v>
+        <v>3.14</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.43</v>
+        <v>3.22</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.14</v>
+        <v>2.01</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.28</v>
+        <v>1.41</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.65</v>
+        <v>1.5</v>
       </c>
       <c r="M24" t="n">
-        <v>3.2</v>
+        <v>4.16</v>
       </c>
       <c r="N24" t="n">
-        <v>2.44</v>
+        <v>5.5</v>
       </c>
       <c r="O24" t="n">
-        <v>3.36</v>
+        <v>2.06</v>
       </c>
       <c r="P24" t="n">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.05</v>
+        <v>4.7</v>
       </c>
       <c r="R24" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="S24" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="T24" t="n">
-        <v>2.85</v>
+        <v>2.39</v>
       </c>
       <c r="U24" t="n">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="V24" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W24" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="X24" t="n">
-        <v>3.14</v>
+        <v>4.4</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.22</v>
+        <v>2.43</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.01</v>
+        <v>2.14</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.41</v>
+        <v>2.28</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,77 +4152,77 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="M29" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="N29" t="n">
-        <v>2.86</v>
+        <v>3.5</v>
       </c>
       <c r="O29" t="n">
-        <v>2.83</v>
+        <v>2.73</v>
       </c>
       <c r="P29" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.66</v>
+        <v>4.7</v>
       </c>
       <c r="R29" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="S29" t="n">
-        <v>2.84</v>
+        <v>2.4</v>
       </c>
       <c r="T29" t="n">
-        <v>2.65</v>
+        <v>3.34</v>
       </c>
       <c r="U29" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="V29" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W29" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X29" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
         <v>1.25</v>
       </c>
-      <c r="X29" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH29" t="n">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,77 +4410,77 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="M31" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N31" t="n">
-        <v>3.5</v>
+        <v>2.86</v>
       </c>
       <c r="O31" t="n">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="P31" t="n">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.7</v>
+        <v>3.66</v>
       </c>
       <c r="R31" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="S31" t="n">
-        <v>2.4</v>
+        <v>2.84</v>
       </c>
       <c r="T31" t="n">
-        <v>3.34</v>
+        <v>2.65</v>
       </c>
       <c r="U31" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X31" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
         <v>1.28</v>
       </c>
-      <c r="V31" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="X31" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH31" t="n">
-        <v>1.72</v>
+        <v>1.55</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>

--- a/jogos_2025-09-05.xlsx
+++ b/jogos_2025-09-05.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK38"/>
+  <dimension ref="A1:AK39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="M3" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="N3" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="O3" t="n">
         <v>3.22</v>
@@ -831,28 +831,28 @@
         <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="X3" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AD3" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="M4" t="n">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="N4" t="n">
         <v>2.18</v>
@@ -969,7 +969,7 @@
         <v>1.8</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -1323,52 +1323,52 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1439,65 +1439,65 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.88</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
         <v>3.15</v>
       </c>
       <c r="N9" t="n">
-        <v>2.23</v>
+        <v>3.4</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.96</v>
+        <v>2.16</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.68</v>
+        <v>1.56</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1839,34 +1839,34 @@
         <v>3.55</v>
       </c>
       <c r="O11" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="P11" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.37</v>
+        <v>4.2</v>
       </c>
       <c r="R11" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="S11" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="T11" t="n">
-        <v>2.9</v>
+        <v>3.18</v>
       </c>
       <c r="U11" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V11" t="n">
         <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="X11" t="n">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="Y11" t="n">
         <v>2.1</v>
@@ -1875,16 +1875,16 @@
         <v>1.65</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.86</v>
+        <v>3.72</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AC11" t="n">
         <v>1.83</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>1.28</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="M12" t="n">
-        <v>2.95</v>
+        <v>3.15</v>
       </c>
       <c r="N12" t="n">
-        <v>2.75</v>
+        <v>2.23</v>
       </c>
       <c r="O12" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.91</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2229,31 +2229,31 @@
         <v>2.5</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q14" t="n">
         <v>4.1</v>
       </c>
       <c r="R14" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="T14" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="U14" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="V14" t="n">
         <v>1.06</v>
       </c>
       <c r="W14" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="X14" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="Y14" t="n">
         <v>1.98</v>
@@ -2271,7 +2271,7 @@
         <v>1.75</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O17" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W17" t="n">
         <v>1.6</v>
       </c>
-      <c r="M17" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="N17" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.58</v>
+        <v>2.9</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.2</v>
+        <v>1.36</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.2</v>
+        <v>5.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.6</v>
+        <v>1.12</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.65</v>
+        <v>1.6</v>
       </c>
       <c r="M18" t="n">
-        <v>2.76</v>
+        <v>4.05</v>
       </c>
       <c r="N18" t="n">
-        <v>2.25</v>
+        <v>4.8</v>
       </c>
       <c r="O18" t="n">
-        <v>4.76</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.98</v>
+        <v>1.58</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.34</v>
+        <v>2.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>5.5</v>
+        <v>2.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.08</v>
+        <v>1.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2862,28 +2862,28 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="M19" t="n">
         <v>2.62</v>
       </c>
       <c r="N19" t="n">
-        <v>6.46</v>
+        <v>6</v>
       </c>
       <c r="O19" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="P19" t="n">
         <v>1.81</v>
       </c>
       <c r="Q19" t="n">
-        <v>7.22</v>
+        <v>6.75</v>
       </c>
       <c r="R19" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="S19" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="T19" t="n">
         <v>4.5</v>
@@ -2895,44 +2895,44 @@
         <v>1.19</v>
       </c>
       <c r="W19" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="X19" t="n">
         <v>1.95</v>
       </c>
       <c r="Y19" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AA19" t="n">
-        <v>8</v>
+        <v>6.33</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.79</v>
+        <v>3.1</v>
       </c>
       <c r="AD19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
         <v>1.38</v>
       </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.39</v>
-      </c>
       <c r="AH19" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,77 +2991,77 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4</v>
+        <v>2.89</v>
       </c>
       <c r="M20" t="n">
-        <v>3.5</v>
+        <v>3.18</v>
       </c>
       <c r="N20" t="n">
-        <v>1.7</v>
+        <v>2.18</v>
       </c>
       <c r="O20" t="n">
-        <v>4.65</v>
+        <v>3.52</v>
       </c>
       <c r="P20" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.34</v>
+        <v>2.88</v>
       </c>
       <c r="R20" t="n">
         <v>1.35</v>
       </c>
       <c r="S20" t="n">
-        <v>2.89</v>
+        <v>2.93</v>
       </c>
       <c r="T20" t="n">
-        <v>2.76</v>
+        <v>2.65</v>
       </c>
       <c r="U20" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="V20" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="X20" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.25</v>
+        <v>3.13</v>
       </c>
       <c r="AB20" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
         <v>1.28</v>
       </c>
-      <c r="AC20" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AH20" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.9</v>
+        <v>3.66</v>
       </c>
       <c r="M21" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="N21" t="n">
-        <v>2.2</v>
+        <v>1.77</v>
       </c>
       <c r="O21" t="n">
-        <v>3.28</v>
+        <v>3.98</v>
       </c>
       <c r="P21" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.83</v>
+        <v>2.29</v>
       </c>
       <c r="R21" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AA21" t="n">
         <v>3.05</v>
       </c>
-      <c r="T21" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X21" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>3.04</v>
-      </c>
       <c r="AB21" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4.8</v>
+        <v>1.48</v>
       </c>
       <c r="M22" t="n">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="N22" t="n">
-        <v>1.53</v>
+        <v>5.2</v>
       </c>
       <c r="O22" t="n">
-        <v>5.3</v>
+        <v>2</v>
       </c>
       <c r="P22" t="n">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.98</v>
+        <v>5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="S22" t="n">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="T22" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="U22" t="n">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="V22" t="n">
         <v>1.03</v>
       </c>
       <c r="W22" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="X22" t="n">
-        <v>3.9</v>
+        <v>4.22</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.65</v>
+        <v>2.16</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.39</v>
+        <v>1.57</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.12</v>
+        <v>2.07</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="M23" t="n">
-        <v>3.2</v>
+        <v>3.02</v>
       </c>
       <c r="N23" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="O23" t="n">
         <v>3.36</v>
       </c>
       <c r="P23" t="n">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.05</v>
+        <v>3.12</v>
       </c>
       <c r="R23" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T23" t="n">
         <v>2.8</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.85</v>
       </c>
       <c r="U23" t="n">
         <v>1.38</v>
       </c>
       <c r="V23" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="X23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AA23" t="n">
         <v>3.14</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>3.22</v>
       </c>
       <c r="AB23" t="n">
         <v>1.27</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.5</v>
+        <v>4.8</v>
       </c>
       <c r="M24" t="n">
-        <v>4.16</v>
+        <v>3.84</v>
       </c>
       <c r="N24" t="n">
-        <v>5.5</v>
+        <v>1.54</v>
       </c>
       <c r="O24" t="n">
-        <v>2.06</v>
+        <v>4.95</v>
       </c>
       <c r="P24" t="n">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.7</v>
+        <v>2.08</v>
       </c>
       <c r="R24" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S24" t="n">
         <v>3.3</v>
       </c>
       <c r="T24" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="U24" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="V24" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W24" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X24" t="n">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.43</v>
+        <v>2.52</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AC24" t="n">
         <v>1.67</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AH24" t="n">
         <v>1.15</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>2.28</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="M27" t="n">
-        <v>3.09</v>
+        <v>3.2</v>
       </c>
       <c r="N27" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="O27" t="n">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="P27" t="n">
         <v>1.98</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.22</v>
+        <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="S27" t="n">
         <v>2.54</v>
       </c>
       <c r="T27" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="U27" t="n">
         <v>1.29</v>
       </c>
       <c r="V27" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W27" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="X27" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.33</v>
+        <v>2.12</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AA27" t="n">
         <v>4.42</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.98</v>
+        <v>2.11</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="M29" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="N29" t="n">
-        <v>3.5</v>
+        <v>3.86</v>
       </c>
       <c r="O29" t="n">
         <v>2.73</v>
@@ -4182,31 +4182,31 @@
         <v>1.28</v>
       </c>
       <c r="V29" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="W29" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="X29" t="n">
-        <v>2.58</v>
+        <v>2.35</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AA29" t="n">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="AB29" t="n">
         <v>1.14</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AH29" t="n">
         <v>1.72</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.87</v>
+        <v>2.35</v>
       </c>
       <c r="M30" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="N30" t="n">
-        <v>4.6</v>
+        <v>2.8</v>
       </c>
       <c r="O30" t="n">
-        <v>2.61</v>
+        <v>2.8</v>
       </c>
       <c r="P30" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X30" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z30" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q30" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="T30" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="X30" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AA30" t="n">
-        <v>6.09</v>
+        <v>2.81</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.06</v>
+        <v>1.38</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.51</v>
+        <v>1.61</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.46</v>
+        <v>2.21</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.15</v>
+        <v>1.86</v>
       </c>
       <c r="M31" t="n">
-        <v>3.4</v>
+        <v>2.91</v>
       </c>
       <c r="N31" t="n">
-        <v>2.86</v>
+        <v>4.2</v>
       </c>
       <c r="O31" t="n">
-        <v>2.83</v>
+        <v>2.49</v>
       </c>
       <c r="P31" t="n">
-        <v>2.09</v>
+        <v>1.81</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.66</v>
+        <v>6.62</v>
       </c>
       <c r="R31" t="n">
-        <v>1.35</v>
+        <v>1.65</v>
       </c>
       <c r="S31" t="n">
-        <v>2.84</v>
+        <v>2.16</v>
       </c>
       <c r="T31" t="n">
-        <v>2.65</v>
+        <v>4.15</v>
       </c>
       <c r="U31" t="n">
-        <v>1.42</v>
+        <v>1.18</v>
       </c>
       <c r="V31" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="W31" t="n">
-        <v>1.25</v>
+        <v>1.65</v>
       </c>
       <c r="X31" t="n">
-        <v>3.28</v>
+        <v>2.1</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.96</v>
+        <v>2.9</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.86</v>
+        <v>1.36</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.03</v>
+        <v>6.09</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.29</v>
+        <v>1.06</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.67</v>
+        <v>2.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.05</v>
+        <v>1.43</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4539,55 +4539,55 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.37</v>
+        <v>2.43</v>
       </c>
       <c r="M32" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="N32" t="n">
-        <v>3.55</v>
+        <v>3.11</v>
       </c>
       <c r="O32" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="P32" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.88</v>
+        <v>4.71</v>
       </c>
       <c r="R32" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="S32" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="T32" t="n">
         <v>4.7</v>
       </c>
       <c r="U32" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="V32" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="W32" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="X32" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="Y32" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AA32" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AC32" t="n">
         <v>2.6</v>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="M33" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="N33" t="n">
-        <v>2.5</v>
+        <v>6.81</v>
       </c>
       <c r="O33" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4756,12 +4756,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
+        <v>3</v>
+      </c>
+      <c r="M34" t="n">
         <v>2.51</v>
       </c>
-      <c r="M34" t="n">
-        <v>3.28</v>
-      </c>
       <c r="N34" t="n">
-        <v>2.32</v>
+        <v>2.58</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Y34" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>45905.85416666666</v>
+        <v>45905.83333333334</v>
       </c>
     </row>
     <row r="35">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="M35" t="n">
-        <v>3.13</v>
+        <v>3.45</v>
       </c>
       <c r="N35" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="O35" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.17</v>
+        <v>1.95</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AA35" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5005,7 +5005,7 @@
         <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
-        <v>45905.875</v>
+        <v>45905.85416666666</v>
       </c>
     </row>
     <row r="36">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,77 +5055,77 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="M36" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N36" t="n">
-        <v>5</v>
+        <v>2.25</v>
       </c>
       <c r="O36" t="n">
-        <v>2.25</v>
+        <v>3.92</v>
       </c>
       <c r="P36" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="Q36" t="n">
-        <v>5.8</v>
+        <v>2.73</v>
       </c>
       <c r="R36" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="S36" t="n">
-        <v>2.38</v>
+        <v>2.61</v>
       </c>
       <c r="T36" t="n">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="U36" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X36" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
         <v>1.26</v>
       </c>
-      <c r="V36" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="X36" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH36" t="n">
-        <v>1.97</v>
+        <v>1.26</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45905.89583333334</v>
+        <v>45905.875</v>
       </c>
     </row>
     <row r="37">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.35</v>
+        <v>1.52</v>
       </c>
       <c r="M37" t="n">
-        <v>3.5</v>
+        <v>3.37</v>
       </c>
       <c r="N37" t="n">
-        <v>2.7</v>
+        <v>6</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="Z37" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="AK37" s="3" t="n">
-        <v>45905.97916666666</v>
+        <v>45905.89583333334</v>
       </c>
     </row>
     <row r="38">
@@ -5277,121 +5277,250 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
+          <t>Canada Canadian Premier League</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Vancouver FC</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Valour FC</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="M38" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N38" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" s="3" t="n">
+        <v>45905.97916666666</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>45905</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
           <t>USA USL Championship</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>Phoenix Rising</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>Las Vegas Lights</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="inlineStr">
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L38" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="M38" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N38" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O38" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="P38" t="n">
+      <c r="L39" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="M39" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N39" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O39" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="P39" t="n">
         <v>2.21</v>
       </c>
-      <c r="Q38" t="n">
-        <v>4.71</v>
-      </c>
-      <c r="R38" t="n">
+      <c r="Q39" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="R39" t="n">
         <v>1.33</v>
       </c>
-      <c r="S38" t="n">
+      <c r="S39" t="n">
         <v>3.04</v>
       </c>
-      <c r="T38" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U38" t="n">
+      <c r="T39" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="U39" t="n">
         <v>1.44</v>
       </c>
-      <c r="V38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W38" t="n">
+      <c r="V39" t="n">
+        <v>1</v>
+      </c>
+      <c r="W39" t="n">
         <v>1.22</v>
       </c>
-      <c r="X38" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC38" t="n">
+      <c r="X39" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC39" t="n">
         <v>1.72</v>
       </c>
-      <c r="AD38" t="n">
+      <c r="AD39" t="n">
         <v>1.98</v>
       </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AH38" t="n">
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH39" t="n">
         <v>1.95</v>
       </c>
-      <c r="AI38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK38" s="3" t="n">
+      <c r="AI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK39" s="3" t="n">
         <v>45905.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-09-05.xlsx
+++ b/jogos_2025-09-05.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="M3" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="N3" t="n">
-        <v>2.55</v>
+        <v>2.18</v>
       </c>
       <c r="O3" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z3" t="n">
         <v>1.9</v>
       </c>
-      <c r="Z3" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AA3" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="M4" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="N4" t="n">
-        <v>2.18</v>
+        <v>2.55</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z4" t="n">
         <v>1.8</v>
       </c>
-      <c r="Z4" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1194,52 +1194,52 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1310,17 +1310,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1439,65 +1439,65 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,58 +1575,58 @@
         <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N9" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>2.88</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="N11" t="n">
-        <v>3.55</v>
+        <v>2.23</v>
       </c>
       <c r="O11" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.39</v>
+        <v>1.6</v>
       </c>
       <c r="M17" t="n">
-        <v>2.7</v>
+        <v>4.05</v>
       </c>
       <c r="N17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z17" t="n">
         <v>2.2</v>
       </c>
-      <c r="O17" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W17" t="n">
+      <c r="AA17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB17" t="n">
         <v>1.6</v>
       </c>
-      <c r="X17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AC17" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O18" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W18" t="n">
         <v>1.6</v>
       </c>
-      <c r="M18" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="N18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.58</v>
+        <v>2.9</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.2</v>
+        <v>1.36</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.2</v>
+        <v>5.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.6</v>
+        <v>1.12</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,34 +2991,34 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.89</v>
+        <v>2.67</v>
       </c>
       <c r="M20" t="n">
-        <v>3.18</v>
+        <v>3.02</v>
       </c>
       <c r="N20" t="n">
-        <v>2.18</v>
+        <v>2.42</v>
       </c>
       <c r="O20" t="n">
-        <v>3.52</v>
+        <v>3.36</v>
       </c>
       <c r="P20" t="n">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.88</v>
+        <v>3.12</v>
       </c>
       <c r="R20" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="S20" t="n">
-        <v>2.93</v>
+        <v>2.75</v>
       </c>
       <c r="T20" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="U20" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="V20" t="n">
         <v>1.01</v>
@@ -3030,22 +3030,22 @@
         <v>3.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.66</v>
+        <v>2.89</v>
       </c>
       <c r="M21" t="n">
-        <v>3.55</v>
+        <v>3.18</v>
       </c>
       <c r="N21" t="n">
-        <v>1.77</v>
+        <v>2.18</v>
       </c>
       <c r="O21" t="n">
-        <v>3.98</v>
+        <v>3.52</v>
       </c>
       <c r="P21" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.29</v>
+        <v>2.88</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S21" t="n">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="T21" t="n">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="U21" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="V21" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="X21" t="n">
         <v>3.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.05</v>
+        <v>3.13</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.48</v>
+        <v>4.8</v>
       </c>
       <c r="M22" t="n">
-        <v>3.94</v>
+        <v>3.84</v>
       </c>
       <c r="N22" t="n">
-        <v>5.2</v>
+        <v>1.54</v>
       </c>
       <c r="O22" t="n">
-        <v>2</v>
+        <v>4.95</v>
       </c>
       <c r="P22" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="Q22" t="n">
-        <v>5</v>
+        <v>2.08</v>
       </c>
       <c r="R22" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S22" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="T22" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="U22" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="V22" t="n">
         <v>1.03</v>
       </c>
       <c r="W22" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="X22" t="n">
-        <v>4.22</v>
+        <v>4.33</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.16</v>
+        <v>2.52</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.19</v>
+        <v>2.28</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.07</v>
+        <v>1.15</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.67</v>
+        <v>1.48</v>
       </c>
       <c r="M23" t="n">
-        <v>3.02</v>
+        <v>3.94</v>
       </c>
       <c r="N23" t="n">
-        <v>2.42</v>
+        <v>5.2</v>
       </c>
       <c r="O23" t="n">
-        <v>3.36</v>
+        <v>2</v>
       </c>
       <c r="P23" t="n">
-        <v>2.21</v>
+        <v>2.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.12</v>
+        <v>5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="S23" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="T23" t="n">
-        <v>2.8</v>
+        <v>2.48</v>
       </c>
       <c r="U23" t="n">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="V23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W23" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="X23" t="n">
-        <v>3.5</v>
+        <v>4.22</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.89</v>
+        <v>1.6</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.81</v>
+        <v>2.2</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.14</v>
+        <v>2.16</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.27</v>
+        <v>1.57</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.45</v>
+        <v>2.07</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4.8</v>
+        <v>3.66</v>
       </c>
       <c r="M24" t="n">
-        <v>3.84</v>
+        <v>3.55</v>
       </c>
       <c r="N24" t="n">
-        <v>1.54</v>
+        <v>1.77</v>
       </c>
       <c r="O24" t="n">
-        <v>4.95</v>
+        <v>3.98</v>
       </c>
       <c r="P24" t="n">
-        <v>2.46</v>
+        <v>2.15</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.08</v>
+        <v>2.29</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="T24" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="U24" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="V24" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W24" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X24" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.65</v>
+        <v>1.81</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.52</v>
+        <v>3.05</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>2.28</v>
+        <v>1.18</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.35</v>
+        <v>1.86</v>
       </c>
       <c r="M30" t="n">
-        <v>3.3</v>
+        <v>2.91</v>
       </c>
       <c r="N30" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="O30" t="n">
-        <v>2.8</v>
+        <v>2.49</v>
       </c>
       <c r="P30" t="n">
-        <v>2.15</v>
+        <v>1.81</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.5</v>
+        <v>6.62</v>
       </c>
       <c r="R30" t="n">
-        <v>1.34</v>
+        <v>1.65</v>
       </c>
       <c r="S30" t="n">
-        <v>2.98</v>
+        <v>2.16</v>
       </c>
       <c r="T30" t="n">
-        <v>2.55</v>
+        <v>4.15</v>
       </c>
       <c r="U30" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="V30" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="W30" t="n">
-        <v>1.2</v>
+        <v>1.65</v>
       </c>
       <c r="X30" t="n">
-        <v>3.95</v>
+        <v>2.1</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.81</v>
+        <v>6.09</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.38</v>
+        <v>1.06</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.61</v>
+        <v>2.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.21</v>
+        <v>1.43</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.86</v>
+        <v>2.35</v>
       </c>
       <c r="M31" t="n">
-        <v>2.91</v>
+        <v>3.3</v>
       </c>
       <c r="N31" t="n">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="O31" t="n">
-        <v>2.49</v>
+        <v>2.8</v>
       </c>
       <c r="P31" t="n">
-        <v>1.81</v>
+        <v>2.15</v>
       </c>
       <c r="Q31" t="n">
-        <v>6.62</v>
+        <v>3.5</v>
       </c>
       <c r="R31" t="n">
-        <v>1.65</v>
+        <v>1.34</v>
       </c>
       <c r="S31" t="n">
-        <v>2.16</v>
+        <v>2.98</v>
       </c>
       <c r="T31" t="n">
-        <v>4.15</v>
+        <v>2.55</v>
       </c>
       <c r="U31" t="n">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="V31" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="W31" t="n">
-        <v>1.65</v>
+        <v>1.2</v>
       </c>
       <c r="X31" t="n">
-        <v>2.1</v>
+        <v>3.95</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="AA31" t="n">
-        <v>6.09</v>
+        <v>2.81</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.06</v>
+        <v>1.38</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.6</v>
+        <v>1.61</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.43</v>
+        <v>2.21</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>

--- a/jogos_2025-09-05.xlsx
+++ b/jogos_2025-09-05.xlsx
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1052,65 +1052,65 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1194,52 +1194,52 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>2.85</v>
       </c>
       <c r="M7" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="N7" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1439,17 +1439,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,77 +1572,77 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="N9" t="n">
-        <v>3.55</v>
+        <v>2.75</v>
       </c>
       <c r="O9" t="n">
-        <v>2.71</v>
+        <v>3.52</v>
       </c>
       <c r="P9" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.2</v>
+        <v>3.34</v>
       </c>
       <c r="R9" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S9" t="n">
-        <v>2.72</v>
+        <v>2.45</v>
       </c>
       <c r="T9" t="n">
-        <v>3.18</v>
+        <v>3.48</v>
       </c>
       <c r="U9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
         <v>1.33</v>
       </c>
-      <c r="V9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH9" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="M10" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="N10" t="n">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.88</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N11" t="n">
-        <v>2.23</v>
+        <v>3.55</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1968,52 +1968,52 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.39</v>
+        <v>1.74</v>
       </c>
       <c r="M18" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="N18" t="n">
-        <v>2.2</v>
+        <v>6</v>
       </c>
       <c r="O18" t="n">
-        <v>4.55</v>
+        <v>2.67</v>
       </c>
       <c r="P18" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="R18" t="n">
         <v>1.76</v>
       </c>
-      <c r="Q18" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.62</v>
-      </c>
       <c r="S18" t="n">
-        <v>2.14</v>
+        <v>1.91</v>
       </c>
       <c r="T18" t="n">
-        <v>3.98</v>
+        <v>4.5</v>
       </c>
       <c r="U18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="V18" t="n">
         <v>1.19</v>
       </c>
-      <c r="V18" t="n">
+      <c r="W18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="AB18" t="n">
         <v>1.1</v>
       </c>
-      <c r="W18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AC18" t="n">
-        <v>2.35</v>
+        <v>3.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.23</v>
+        <v>1.87</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.74</v>
+        <v>3.39</v>
       </c>
       <c r="M19" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="N19" t="n">
-        <v>6</v>
+        <v>2.2</v>
       </c>
       <c r="O19" t="n">
-        <v>2.67</v>
+        <v>4.55</v>
       </c>
       <c r="P19" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.75</v>
+        <v>3.04</v>
       </c>
       <c r="R19" t="n">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="S19" t="n">
-        <v>1.91</v>
+        <v>2.14</v>
       </c>
       <c r="T19" t="n">
-        <v>4.5</v>
+        <v>3.98</v>
       </c>
       <c r="U19" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="V19" t="n">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="W19" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="X19" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="Y19" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AA19" t="n">
-        <v>6.33</v>
+        <v>5.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.1</v>
+        <v>2.35</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.87</v>
+        <v>1.23</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,34 +2991,34 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.67</v>
+        <v>2.89</v>
       </c>
       <c r="M20" t="n">
-        <v>3.02</v>
+        <v>3.18</v>
       </c>
       <c r="N20" t="n">
-        <v>2.42</v>
+        <v>2.18</v>
       </c>
       <c r="O20" t="n">
-        <v>3.36</v>
+        <v>3.52</v>
       </c>
       <c r="P20" t="n">
-        <v>2.21</v>
+        <v>2.05</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.12</v>
+        <v>2.88</v>
       </c>
       <c r="R20" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="S20" t="n">
-        <v>2.75</v>
+        <v>2.93</v>
       </c>
       <c r="T20" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="U20" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="V20" t="n">
         <v>1.01</v>
@@ -3030,22 +3030,22 @@
         <v>3.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.89</v>
+        <v>1.48</v>
       </c>
       <c r="M21" t="n">
-        <v>3.18</v>
+        <v>3.94</v>
       </c>
       <c r="N21" t="n">
-        <v>2.18</v>
+        <v>5.2</v>
       </c>
       <c r="O21" t="n">
-        <v>3.52</v>
+        <v>2</v>
       </c>
       <c r="P21" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.88</v>
+        <v>5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="S21" t="n">
-        <v>2.93</v>
+        <v>3.4</v>
       </c>
       <c r="T21" t="n">
-        <v>2.65</v>
+        <v>2.48</v>
       </c>
       <c r="U21" t="n">
-        <v>1.42</v>
+        <v>1.62</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W21" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="X21" t="n">
-        <v>3.5</v>
+        <v>4.22</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.13</v>
+        <v>2.16</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.31</v>
+        <v>1.57</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.36</v>
+        <v>2.07</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4.8</v>
+        <v>2.67</v>
       </c>
       <c r="M22" t="n">
-        <v>3.84</v>
+        <v>3.02</v>
       </c>
       <c r="N22" t="n">
-        <v>1.54</v>
+        <v>2.42</v>
       </c>
       <c r="O22" t="n">
-        <v>4.95</v>
+        <v>3.36</v>
       </c>
       <c r="P22" t="n">
-        <v>2.46</v>
+        <v>2.21</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.08</v>
+        <v>3.12</v>
       </c>
       <c r="R22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W22" t="n">
         <v>1.3</v>
       </c>
-      <c r="S22" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.21</v>
-      </c>
       <c r="X22" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.52</v>
+        <v>3.14</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.48</v>
+        <v>1.27</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>2.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.15</v>
+        <v>1.45</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.48</v>
+        <v>4.8</v>
       </c>
       <c r="M23" t="n">
-        <v>3.94</v>
+        <v>3.84</v>
       </c>
       <c r="N23" t="n">
-        <v>5.2</v>
+        <v>1.54</v>
       </c>
       <c r="O23" t="n">
-        <v>2</v>
+        <v>4.95</v>
       </c>
       <c r="P23" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="Q23" t="n">
-        <v>5</v>
+        <v>2.08</v>
       </c>
       <c r="R23" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S23" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="T23" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="U23" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="V23" t="n">
         <v>1.03</v>
       </c>
       <c r="W23" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="X23" t="n">
-        <v>4.22</v>
+        <v>4.33</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.16</v>
+        <v>2.52</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.19</v>
+        <v>2.28</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.07</v>
+        <v>1.15</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="M27" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="N27" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="O27" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="M28" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="N28" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X29" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="Y29" t="n">
         <v>1.9</v>
       </c>
-      <c r="M29" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="N29" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="O29" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T29" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="X29" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>2.35</v>
-      </c>
       <c r="Z29" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AA29" t="n">
-        <v>4.4</v>
+        <v>2.81</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.07</v>
+        <v>1.61</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.63</v>
+        <v>2.21</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,77 +4410,77 @@
         </is>
       </c>
       <c r="L31" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M31" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="N31" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="O31" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X31" t="n">
         <v>2.35</v>
       </c>
-      <c r="M31" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N31" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O31" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P31" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R31" t="n">
+      <c r="Y31" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
         <v>1.34</v>
       </c>
-      <c r="S31" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X31" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AH31" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.43</v>
+        <v>3</v>
       </c>
       <c r="M32" t="n">
-        <v>2.59</v>
+        <v>2.51</v>
       </c>
       <c r="N32" t="n">
-        <v>3.11</v>
+        <v>2.58</v>
       </c>
       <c r="O32" t="n">
-        <v>3.26</v>
+        <v>4.2</v>
       </c>
       <c r="P32" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.71</v>
+        <v>3.32</v>
       </c>
       <c r="R32" t="n">
-        <v>1.77</v>
+        <v>1.63</v>
       </c>
       <c r="S32" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="T32" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="U32" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="V32" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="W32" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="X32" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="Y32" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AA32" t="n">
-        <v>7.4</v>
+        <v>6.3</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         <v>1.39</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.56</v>
+        <v>1.3</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3</v>
+        <v>2.43</v>
       </c>
       <c r="M34" t="n">
-        <v>2.51</v>
+        <v>2.59</v>
       </c>
       <c r="N34" t="n">
-        <v>2.58</v>
+        <v>3.11</v>
       </c>
       <c r="O34" t="n">
-        <v>4.2</v>
+        <v>3.26</v>
       </c>
       <c r="P34" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.32</v>
+        <v>4.71</v>
       </c>
       <c r="R34" t="n">
-        <v>1.63</v>
+        <v>1.77</v>
       </c>
       <c r="S34" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="T34" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="U34" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="V34" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W34" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="X34" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="Y34" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AA34" t="n">
-        <v>6.3</v>
+        <v>7.4</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.42</v>
+        <v>2.6</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>1.39</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.3</v>
+        <v>1.56</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>

--- a/jogos_2025-09-05.xlsx
+++ b/jogos_2025-09-05.xlsx
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3</v>
+        <v>2.43</v>
       </c>
       <c r="M32" t="n">
-        <v>2.51</v>
+        <v>2.59</v>
       </c>
       <c r="N32" t="n">
-        <v>2.58</v>
+        <v>3.11</v>
       </c>
       <c r="O32" t="n">
-        <v>4.2</v>
+        <v>3.26</v>
       </c>
       <c r="P32" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.32</v>
+        <v>4.71</v>
       </c>
       <c r="R32" t="n">
-        <v>1.63</v>
+        <v>1.77</v>
       </c>
       <c r="S32" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="T32" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="U32" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="V32" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W32" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="X32" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="Y32" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AA32" t="n">
-        <v>6.3</v>
+        <v>7.4</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.42</v>
+        <v>2.6</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         <v>1.39</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.3</v>
+        <v>1.56</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.43</v>
+        <v>3</v>
       </c>
       <c r="M34" t="n">
-        <v>2.59</v>
+        <v>2.51</v>
       </c>
       <c r="N34" t="n">
-        <v>3.11</v>
+        <v>2.58</v>
       </c>
       <c r="O34" t="n">
-        <v>3.26</v>
+        <v>4.2</v>
       </c>
       <c r="P34" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.71</v>
+        <v>3.32</v>
       </c>
       <c r="R34" t="n">
-        <v>1.77</v>
+        <v>1.63</v>
       </c>
       <c r="S34" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="T34" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="U34" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="V34" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="W34" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="X34" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="Y34" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AA34" t="n">
-        <v>7.4</v>
+        <v>6.3</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>1.39</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.56</v>
+        <v>1.3</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>

--- a/jogos_2025-09-05.xlsx
+++ b/jogos_2025-09-05.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK39"/>
+  <dimension ref="A1:AK42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -963,7 +963,7 @@
         <v>1.28</v>
       </c>
       <c r="X4" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="Y4" t="n">
         <v>1.9</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1052,17 +1052,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O6" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S6" t="n">
         <v>2.5</v>
       </c>
-      <c r="P6" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.52</v>
-      </c>
       <c r="T6" t="n">
-        <v>3.27</v>
+        <v>3.48</v>
       </c>
       <c r="U6" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="V6" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W6" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="X6" t="n">
-        <v>2.74</v>
+        <v>2.45</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.78</v>
+        <v>4.65</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.74</v>
+        <v>1.4</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1310,17 +1310,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>3.05</v>
       </c>
       <c r="M8" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N8" t="n">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="M9" t="n">
-        <v>2.95</v>
+        <v>3.15</v>
       </c>
       <c r="N9" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="O9" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.88</v>
+        <v>2</v>
       </c>
       <c r="M10" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N10" t="n">
-        <v>2.23</v>
+        <v>3.55</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,43 +1830,43 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>2.85</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="N11" t="n">
-        <v>3.55</v>
+        <v>2.4</v>
       </c>
       <c r="O11" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
         <v>2.1</v>
@@ -1875,16 +1875,16 @@
         <v>1.65</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1968,52 +1968,52 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Real Betis II</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gimnàstic de Tarragona</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45905.59375</v>
+        <v>45905.58333333334</v>
       </c>
     </row>
     <row r="14">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Real Betis II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Gimnàstic de Tarragona</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45905.60416666666</v>
+        <v>45905.59375</v>
       </c>
     </row>
     <row r="15">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45905.625</v>
+        <v>45905.60416666666</v>
       </c>
     </row>
     <row r="16">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,16 +2643,16 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45905.64583333334</v>
+        <v>45905.625</v>
       </c>
     </row>
     <row r="18">
@@ -2692,27 +2692,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>6.33</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45905.64583333334</v>
+        <v>45905.625</v>
       </c>
     </row>
     <row r="19">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.39</v>
+        <v>1.74</v>
       </c>
       <c r="M19" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="N19" t="n">
-        <v>2.2</v>
+        <v>6</v>
       </c>
       <c r="O19" t="n">
-        <v>4.55</v>
+        <v>2.67</v>
       </c>
       <c r="P19" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="R19" t="n">
         <v>1.76</v>
       </c>
-      <c r="Q19" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.62</v>
-      </c>
       <c r="S19" t="n">
-        <v>2.14</v>
+        <v>1.91</v>
       </c>
       <c r="T19" t="n">
-        <v>3.98</v>
+        <v>4.5</v>
       </c>
       <c r="U19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="V19" t="n">
         <v>1.19</v>
       </c>
-      <c r="V19" t="n">
-        <v>1.1</v>
-      </c>
       <c r="W19" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="X19" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AA19" t="n">
-        <v>5.5</v>
+        <v>6.33</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.35</v>
+        <v>3.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.23</v>
+        <v>1.87</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.89</v>
+        <v>3.39</v>
       </c>
       <c r="M20" t="n">
-        <v>3.18</v>
+        <v>2.7</v>
       </c>
       <c r="N20" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="O20" t="n">
-        <v>3.52</v>
+        <v>4.6</v>
       </c>
       <c r="P20" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="R20" t="n">
-        <v>1.35</v>
+        <v>1.62</v>
       </c>
       <c r="S20" t="n">
-        <v>2.93</v>
+        <v>2.14</v>
       </c>
       <c r="T20" t="n">
-        <v>2.65</v>
+        <v>3.98</v>
       </c>
       <c r="U20" t="n">
-        <v>1.42</v>
+        <v>1.21</v>
       </c>
       <c r="V20" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="W20" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="X20" t="n">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.85</v>
+        <v>2.9</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.85</v>
+        <v>1.36</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.13</v>
+        <v>5.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.31</v>
+        <v>1.12</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.05</v>
+        <v>1.48</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45905.65625</v>
+        <v>45905.64583333334</v>
       </c>
     </row>
     <row r="21">
@@ -3079,27 +3079,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="M21" t="n">
-        <v>3.94</v>
+        <v>4.05</v>
       </c>
       <c r="N21" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="O21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="Z21" t="n">
         <v>2.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45905.65625</v>
+        <v>45905.64583333334</v>
       </c>
     </row>
     <row r="22">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,34 +3249,34 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.67</v>
+        <v>2.89</v>
       </c>
       <c r="M22" t="n">
-        <v>3.02</v>
+        <v>3.18</v>
       </c>
       <c r="N22" t="n">
-        <v>2.42</v>
+        <v>2.18</v>
       </c>
       <c r="O22" t="n">
-        <v>3.36</v>
+        <v>3.52</v>
       </c>
       <c r="P22" t="n">
-        <v>2.21</v>
+        <v>2.05</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.12</v>
+        <v>2.88</v>
       </c>
       <c r="R22" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="S22" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="T22" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="U22" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="V22" t="n">
         <v>1.01</v>
@@ -3288,22 +3288,22 @@
         <v>3.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.98</v>
+        <v>2.09</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>4.8</v>
+        <v>3.66</v>
       </c>
       <c r="M23" t="n">
-        <v>3.84</v>
+        <v>3.55</v>
       </c>
       <c r="N23" t="n">
-        <v>1.54</v>
+        <v>1.77</v>
       </c>
       <c r="O23" t="n">
-        <v>4.95</v>
+        <v>3.98</v>
       </c>
       <c r="P23" t="n">
-        <v>2.46</v>
+        <v>2.15</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.08</v>
+        <v>2.29</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S23" t="n">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="T23" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="U23" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="V23" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W23" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X23" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.65</v>
+        <v>1.81</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.52</v>
+        <v>3.05</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>2.28</v>
+        <v>1.18</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.66</v>
+        <v>1.48</v>
       </c>
       <c r="M24" t="n">
-        <v>3.55</v>
+        <v>3.94</v>
       </c>
       <c r="N24" t="n">
-        <v>1.77</v>
+        <v>5.2</v>
       </c>
       <c r="O24" t="n">
-        <v>3.98</v>
+        <v>1.95</v>
       </c>
       <c r="P24" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.29</v>
+        <v>5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="S24" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="T24" t="n">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="U24" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="V24" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W24" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="X24" t="n">
-        <v>3.5</v>
+        <v>4.22</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.81</v>
+        <v>1.6</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.05</v>
+        <v>2.16</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.93</v>
+        <v>2.14</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>1.18</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.18</v>
+        <v>2.28</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3595,27 +3595,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45905.6875</v>
+        <v>45905.65625</v>
       </c>
     </row>
     <row r="26">
@@ -3724,27 +3724,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.15</v>
+        <v>2.67</v>
       </c>
       <c r="M26" t="n">
-        <v>3.55</v>
+        <v>3.02</v>
       </c>
       <c r="N26" t="n">
-        <v>3.09</v>
+        <v>2.42</v>
       </c>
       <c r="O26" t="n">
-        <v>2.81</v>
+        <v>3.36</v>
       </c>
       <c r="P26" t="n">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.44</v>
+        <v>3.12</v>
       </c>
       <c r="R26" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="S26" t="n">
-        <v>3.28</v>
+        <v>2.8</v>
       </c>
       <c r="T26" t="n">
-        <v>2.38</v>
+        <v>2.85</v>
       </c>
       <c r="U26" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="V26" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W26" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="X26" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.2</v>
+        <v>1.81</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.53</v>
+        <v>3.14</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.53</v>
+        <v>1.32</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.4</v>
+        <v>1.98</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45905.6875</v>
+        <v>45905.65625</v>
       </c>
     </row>
     <row r="27">
@@ -3853,27 +3853,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45905.70833333334</v>
+        <v>45905.66666666666</v>
       </c>
     </row>
     <row r="28">
@@ -3982,27 +3982,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="M28" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="N28" t="n">
-        <v>3.6</v>
+        <v>3.09</v>
       </c>
       <c r="O28" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="P28" t="n">
-        <v>1.98</v>
+        <v>2.21</v>
       </c>
       <c r="Q28" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="R28" t="n">
-        <v>1.47</v>
+        <v>1.27</v>
       </c>
       <c r="S28" t="n">
-        <v>2.54</v>
+        <v>3.28</v>
       </c>
       <c r="T28" t="n">
-        <v>3.2</v>
+        <v>2.38</v>
       </c>
       <c r="U28" t="n">
-        <v>1.29</v>
+        <v>1.55</v>
       </c>
       <c r="V28" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="W28" t="n">
-        <v>1.39</v>
+        <v>1.16</v>
       </c>
       <c r="X28" t="n">
-        <v>2.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.12</v>
+        <v>1.65</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.64</v>
+        <v>2.2</v>
       </c>
       <c r="AA28" t="n">
-        <v>4.42</v>
+        <v>2.53</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.2</v>
+        <v>1.53</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.11</v>
+        <v>1.55</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.73</v>
+        <v>2.4</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45905.70833333334</v>
+        <v>45905.6875</v>
       </c>
     </row>
     <row r="29">
@@ -4111,27 +4111,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45905.79166666666</v>
+        <v>45905.6875</v>
       </c>
     </row>
     <row r="30">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.86</v>
+        <v>2.05</v>
       </c>
       <c r="M30" t="n">
-        <v>2.91</v>
+        <v>3.2</v>
       </c>
       <c r="N30" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="O30" t="n">
-        <v>2.49</v>
+        <v>2.83</v>
       </c>
       <c r="P30" t="n">
-        <v>1.81</v>
+        <v>1.98</v>
       </c>
       <c r="Q30" t="n">
-        <v>6.62</v>
+        <v>4.22</v>
       </c>
       <c r="R30" t="n">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="S30" t="n">
-        <v>2.16</v>
+        <v>2.54</v>
       </c>
       <c r="T30" t="n">
-        <v>4.15</v>
+        <v>3.2</v>
       </c>
       <c r="U30" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="V30" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="W30" t="n">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="X30" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.9</v>
+        <v>2.12</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.36</v>
+        <v>1.64</v>
       </c>
       <c r="AA30" t="n">
-        <v>6.09</v>
+        <v>4.42</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.6</v>
+        <v>2.11</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.43</v>
+        <v>1.74</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.95</v>
+        <v>1.66</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45905.79166666666</v>
+        <v>45905.70833333334</v>
       </c>
     </row>
     <row r="31">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="M31" t="n">
-        <v>2.98</v>
+        <v>3.55</v>
       </c>
       <c r="N31" t="n">
-        <v>3.86</v>
+        <v>3</v>
       </c>
       <c r="O31" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45905.79166666666</v>
+        <v>45905.70833333334</v>
       </c>
     </row>
     <row r="32">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.43</v>
+        <v>1.86</v>
       </c>
       <c r="M32" t="n">
-        <v>2.59</v>
+        <v>2.91</v>
       </c>
       <c r="N32" t="n">
-        <v>3.11</v>
+        <v>4.2</v>
       </c>
       <c r="O32" t="n">
-        <v>3.26</v>
+        <v>2.65</v>
       </c>
       <c r="P32" t="n">
-        <v>1.71</v>
+        <v>1.91</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.71</v>
+        <v>5</v>
       </c>
       <c r="R32" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="S32" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="T32" t="n">
-        <v>4.7</v>
+        <v>4.15</v>
       </c>
       <c r="U32" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="V32" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="W32" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="X32" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="Y32" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AA32" t="n">
-        <v>7.4</v>
+        <v>6.1</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AC32" t="n">
         <v>2.6</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.56</v>
+        <v>1.98</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4618,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
-        <v>45905.83333333334</v>
+        <v>45905.79166666666</v>
       </c>
     </row>
     <row r="33">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M33" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="N33" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="O33" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="R33" t="n">
         <v>1.5</v>
       </c>
-      <c r="M33" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N33" t="n">
-        <v>6.81</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4747,7 +4747,7 @@
         <v>0</v>
       </c>
       <c r="AK33" s="3" t="n">
-        <v>45905.83333333334</v>
+        <v>45905.79166666666</v>
       </c>
     </row>
     <row r="34">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3</v>
+        <v>2.35</v>
       </c>
       <c r="M34" t="n">
-        <v>2.51</v>
+        <v>3.3</v>
       </c>
       <c r="N34" t="n">
-        <v>2.58</v>
+        <v>2.8</v>
       </c>
       <c r="O34" t="n">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="P34" t="n">
-        <v>1.73</v>
+        <v>2.15</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.32</v>
+        <v>3.5</v>
       </c>
       <c r="R34" t="n">
-        <v>1.63</v>
+        <v>1.34</v>
       </c>
       <c r="S34" t="n">
-        <v>2.05</v>
+        <v>2.98</v>
       </c>
       <c r="T34" t="n">
-        <v>4.3</v>
+        <v>2.55</v>
       </c>
       <c r="U34" t="n">
-        <v>1.16</v>
+        <v>1.5</v>
       </c>
       <c r="V34" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="W34" t="n">
-        <v>1.74</v>
+        <v>1.22</v>
       </c>
       <c r="X34" t="n">
-        <v>1.96</v>
+        <v>3.5</v>
       </c>
       <c r="Y34" t="n">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="AA34" t="n">
-        <v>6.3</v>
+        <v>2.81</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.06</v>
+        <v>1.38</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.42</v>
+        <v>1.61</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.49</v>
+        <v>2.21</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>45905.83333333334</v>
+        <v>45905.79166666666</v>
       </c>
     </row>
     <row r="35">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="M35" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="N35" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="O35" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="T35" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC35" t="n">
         <v>2.7</v>
       </c>
-      <c r="M35" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N35" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" t="n">
-        <v>0</v>
-      </c>
-      <c r="X35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>0</v>
-      </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5005,7 +5005,7 @@
         <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
-        <v>45905.85416666666</v>
+        <v>45905.83333333334</v>
       </c>
     </row>
     <row r="36">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.1</v>
+        <v>1.62</v>
       </c>
       <c r="M36" t="n">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="N36" t="n">
-        <v>2.25</v>
+        <v>6.02</v>
       </c>
       <c r="O36" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45905.875</v>
+        <v>45905.83333333334</v>
       </c>
     </row>
     <row r="37">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.52</v>
+        <v>3</v>
       </c>
       <c r="M37" t="n">
-        <v>3.37</v>
+        <v>2.51</v>
       </c>
       <c r="N37" t="n">
-        <v>6</v>
+        <v>2.58</v>
       </c>
       <c r="O37" t="n">
-        <v>2.25</v>
+        <v>4.3</v>
       </c>
       <c r="P37" t="n">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="Q37" t="n">
-        <v>5.8</v>
+        <v>3.3</v>
       </c>
       <c r="R37" t="n">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="S37" t="n">
-        <v>2.38</v>
+        <v>2.06</v>
       </c>
       <c r="T37" t="n">
-        <v>3.48</v>
+        <v>4.33</v>
       </c>
       <c r="U37" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="V37" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="W37" t="n">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="X37" t="n">
-        <v>2.53</v>
+        <v>1.96</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AA37" t="n">
-        <v>5.25</v>
+        <v>6.45</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,11 +5251,11 @@
         </is>
       </c>
       <c r="AG37" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AH37" t="n">
         <v>1.29</v>
       </c>
-      <c r="AH37" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AI37" t="n">
         <v>0</v>
       </c>
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="AK37" s="3" t="n">
-        <v>45905.89583333334</v>
+        <v>45905.83333333334</v>
       </c>
     </row>
     <row r="38">
@@ -5272,7 +5272,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,14 +5313,14 @@
         </is>
       </c>
       <c r="L38" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M38" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N38" t="n">
         <v>2.35</v>
       </c>
-      <c r="M38" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N38" t="n">
-        <v>2.7</v>
-      </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
@@ -5352,11 +5352,11 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z38" t="n">
         <v>1.75</v>
       </c>
-      <c r="Z38" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AA38" t="n">
         <v>0</v>
       </c>
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45905.97916666666</v>
+        <v>45905.85416666666</v>
       </c>
     </row>
     <row r="39">
@@ -5401,126 +5401,513 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Racing Louisville</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Portland Thorns</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M39" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N39" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O39" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X39" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK39" s="3" t="n">
+        <v>45905.875</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>45905</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Ferroviária</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M40" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="N40" t="n">
+        <v>6</v>
+      </c>
+      <c r="O40" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P40" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S40" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X40" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK40" s="3" t="n">
+        <v>45905.89583333334</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>45905</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
           <t>23:30</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>USA USL Championship</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>Phoenix Rising</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>Las Vegas Lights</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="inlineStr">
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L39" t="n">
+      <c r="L41" t="n">
         <v>1.65</v>
       </c>
-      <c r="M39" t="n">
+      <c r="M41" t="n">
         <v>3.8</v>
       </c>
-      <c r="N39" t="n">
+      <c r="N41" t="n">
         <v>4.7</v>
       </c>
-      <c r="O39" t="n">
+      <c r="O41" t="n">
         <v>2.24</v>
       </c>
-      <c r="P39" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="Q39" t="n">
+      <c r="P41" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q41" t="n">
         <v>4.78</v>
       </c>
-      <c r="R39" t="n">
+      <c r="R41" t="n">
         <v>1.33</v>
       </c>
-      <c r="S39" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="T39" t="n">
+      <c r="S41" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T41" t="n">
         <v>2.57</v>
       </c>
-      <c r="U39" t="n">
+      <c r="U41" t="n">
         <v>1.44</v>
       </c>
-      <c r="V39" t="n">
+      <c r="V41" t="n">
         <v>1</v>
       </c>
-      <c r="W39" t="n">
+      <c r="W41" t="n">
         <v>1.22</v>
       </c>
-      <c r="X39" t="n">
+      <c r="X41" t="n">
         <v>3.5</v>
       </c>
-      <c r="Y39" t="n">
+      <c r="Y41" t="n">
         <v>1.8</v>
       </c>
-      <c r="Z39" t="n">
+      <c r="Z41" t="n">
         <v>1.9</v>
       </c>
-      <c r="AA39" t="n">
+      <c r="AA41" t="n">
         <v>2.83</v>
       </c>
-      <c r="AB39" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG39" t="n">
+      <c r="AB41" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG41" t="n">
         <v>1.29</v>
       </c>
-      <c r="AH39" t="n">
+      <c r="AH41" t="n">
         <v>1.95</v>
       </c>
-      <c r="AI39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK39" s="3" t="n">
+      <c r="AI41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK41" s="3" t="n">
+        <v>45905.97916666666</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>45905</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Canada Canadian Premier League</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Vancouver FC</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Valour FC</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="M42" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N42" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="3" t="n">
         <v>45905.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-09-05.xlsx
+++ b/jogos_2025-09-05.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK42"/>
+  <dimension ref="A1:AK43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1015,27 +1015,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.05</v>
+        <v>2.36</v>
       </c>
       <c r="M5" t="n">
         <v>3.3</v>
       </c>
       <c r="N5" t="n">
-        <v>3.45</v>
+        <v>2.36</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.05</v>
+        <v>1.89</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45905.5625</v>
+        <v>45905.54166666666</v>
       </c>
     </row>
     <row r="6">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="M6" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="N6" t="n">
-        <v>2.75</v>
+        <v>2.87</v>
       </c>
       <c r="O6" t="n">
-        <v>3.52</v>
+        <v>3.07</v>
       </c>
       <c r="P6" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.35</v>
+        <v>3.78</v>
       </c>
       <c r="R6" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="S6" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="T6" t="n">
-        <v>3.48</v>
+        <v>3.1</v>
       </c>
       <c r="U6" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="V6" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>1.49</v>
+        <v>1.31</v>
       </c>
       <c r="X6" t="n">
-        <v>2.45</v>
+        <v>2.92</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.65</v>
+        <v>3.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.02</v>
+        <v>1.81</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.69</v>
+        <v>1.85</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1310,65 +1310,65 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1568,17 +1568,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="M10" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="N10" t="n">
-        <v>3.55</v>
+        <v>3.19</v>
       </c>
       <c r="O10" t="n">
-        <v>2.71</v>
+        <v>2.8</v>
       </c>
       <c r="P10" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.2</v>
+        <v>4.03</v>
       </c>
       <c r="R10" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S10" t="n">
-        <v>2.72</v>
+        <v>2.67</v>
       </c>
       <c r="T10" t="n">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="U10" t="n">
         <v>1.32</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W10" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="X10" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Z10" t="n">
         <v>1.65</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.72</v>
+        <v>3.74</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="M11" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N11" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,77 +1959,77 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O12" t="n">
-        <v>2.5</v>
+        <v>3.78</v>
       </c>
       <c r="P12" t="n">
-        <v>2.11</v>
+        <v>1.95</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="S12" t="n">
-        <v>2.52</v>
+        <v>2.45</v>
       </c>
       <c r="T12" t="n">
-        <v>3.27</v>
+        <v>3.55</v>
       </c>
       <c r="U12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
         <v>1.31</v>
       </c>
-      <c r="V12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH12" t="n">
-        <v>1.74</v>
+        <v>1.36</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45905.58333333334</v>
+        <v>45905.5625</v>
       </c>
     </row>
     <row r="14">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Real Betis II</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gimnàstic de Tarragona</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45905.59375</v>
+        <v>45905.58333333334</v>
       </c>
     </row>
     <row r="15">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Real Betis II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Gimnàstic de Tarragona</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45905.60416666666</v>
+        <v>45905.59375</v>
       </c>
     </row>
     <row r="16">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="M16" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>4.33</v>
+        <v>3.92</v>
       </c>
       <c r="O16" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="P16" t="n">
-        <v>2.56</v>
+        <v>2.04</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="R16" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>3.5</v>
+        <v>2.67</v>
       </c>
       <c r="T16" t="n">
-        <v>2.3</v>
+        <v>3.06</v>
       </c>
       <c r="U16" t="n">
-        <v>1.59</v>
+        <v>1.37</v>
       </c>
       <c r="V16" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W16" t="n">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="X16" t="n">
-        <v>4.75</v>
+        <v>3.25</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.57</v>
+        <v>2.06</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.31</v>
+        <v>1.81</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.35</v>
+        <v>3.55</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.57</v>
+        <v>1.29</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.32</v>
+        <v>1.88</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.2</v>
+        <v>1.86</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45905.625</v>
+        <v>45905.60416666666</v>
       </c>
     </row>
     <row r="17">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2821,27 +2821,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>6.33</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45905.64583333334</v>
+        <v>45905.625</v>
       </c>
     </row>
     <row r="20">
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.39</v>
+        <v>1.6</v>
       </c>
       <c r="M20" t="n">
-        <v>2.7</v>
+        <v>4.05</v>
       </c>
       <c r="N20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z20" t="n">
         <v>2.2</v>
       </c>
-      <c r="O20" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W20" t="n">
+      <c r="AA20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB20" t="n">
         <v>1.6</v>
       </c>
-      <c r="X20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AC20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="M21" t="n">
-        <v>4.05</v>
+        <v>2.62</v>
       </c>
       <c r="N21" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.58</v>
+        <v>3.3</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.2</v>
+        <v>1.28</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.2</v>
+        <v>6.33</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.6</v>
+        <v>1.05</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3208,12 +3208,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,62 +3249,62 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.89</v>
+        <v>3.39</v>
       </c>
       <c r="M22" t="n">
-        <v>3.18</v>
+        <v>2.7</v>
       </c>
       <c r="N22" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="O22" t="n">
-        <v>3.52</v>
+        <v>4.6</v>
       </c>
       <c r="P22" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="R22" t="n">
-        <v>1.35</v>
+        <v>1.62</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>2.14</v>
       </c>
       <c r="T22" t="n">
-        <v>2.62</v>
+        <v>3.98</v>
       </c>
       <c r="U22" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD22" t="n">
         <v>1.48</v>
       </c>
-      <c r="V22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>2.09</v>
-      </c>
       <c r="AE22" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45905.65625</v>
+        <v>45905.64583333334</v>
       </c>
     </row>
     <row r="23">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.66</v>
+        <v>2.67</v>
       </c>
       <c r="M23" t="n">
-        <v>3.55</v>
+        <v>3.02</v>
       </c>
       <c r="N23" t="n">
-        <v>1.77</v>
+        <v>2.42</v>
       </c>
       <c r="O23" t="n">
-        <v>3.98</v>
+        <v>3.36</v>
       </c>
       <c r="P23" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.29</v>
+        <v>3.12</v>
       </c>
       <c r="R23" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S23" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="T23" t="n">
-        <v>2.55</v>
+        <v>2.85</v>
       </c>
       <c r="U23" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V23" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W23" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="X23" t="n">
         <v>3.5</v>
       </c>
       <c r="Y23" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Z23" t="n">
         <v>1.81</v>
       </c>
-      <c r="Z23" t="n">
-        <v>1.89</v>
-      </c>
       <c r="AA23" t="n">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="AB23" t="n">
         <v>1.32</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="O24" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U24" t="n">
         <v>1.48</v>
       </c>
-      <c r="M24" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="N24" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>5</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.53</v>
-      </c>
       <c r="V24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="X24" t="n">
-        <v>4.22</v>
+        <v>3.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.16</v>
+        <v>3.13</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.57</v>
+        <v>1.31</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.28</v>
+        <v>1.4</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.8</v>
+        <v>3.66</v>
       </c>
       <c r="M25" t="n">
-        <v>3.84</v>
+        <v>3.55</v>
       </c>
       <c r="N25" t="n">
-        <v>1.54</v>
+        <v>1.77</v>
       </c>
       <c r="O25" t="n">
-        <v>4.95</v>
+        <v>3.98</v>
       </c>
       <c r="P25" t="n">
-        <v>2.46</v>
+        <v>2.15</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.08</v>
+        <v>2.29</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S25" t="n">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="T25" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="U25" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V25" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W25" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X25" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.65</v>
+        <v>1.81</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.52</v>
+        <v>3.05</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.67</v>
+        <v>1.48</v>
       </c>
       <c r="M26" t="n">
-        <v>3.02</v>
+        <v>3.94</v>
       </c>
       <c r="N26" t="n">
-        <v>2.42</v>
+        <v>5.2</v>
       </c>
       <c r="O26" t="n">
-        <v>3.36</v>
+        <v>1.95</v>
       </c>
       <c r="P26" t="n">
-        <v>2.21</v>
+        <v>2.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.12</v>
+        <v>5</v>
       </c>
       <c r="R26" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="S26" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="T26" t="n">
-        <v>2.85</v>
+        <v>2.48</v>
       </c>
       <c r="U26" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="V26" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W26" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="X26" t="n">
-        <v>3.5</v>
+        <v>4.22</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.89</v>
+        <v>1.6</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.81</v>
+        <v>2.2</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.14</v>
+        <v>2.16</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.41</v>
+        <v>2.28</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3853,27 +3853,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45905.66666666666</v>
+        <v>45905.65625</v>
       </c>
     </row>
     <row r="28">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45905.6875</v>
+        <v>45905.66666666666</v>
       </c>
     </row>
     <row r="29">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4240,27 +4240,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,78 +4281,78 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="M30" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="N30" t="n">
-        <v>3.6</v>
+        <v>2.85</v>
       </c>
       <c r="O30" t="n">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="P30" t="n">
-        <v>1.98</v>
+        <v>2.28</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.22</v>
+        <v>3.13</v>
       </c>
       <c r="R30" t="n">
-        <v>1.47</v>
+        <v>1.29</v>
       </c>
       <c r="S30" t="n">
-        <v>2.54</v>
+        <v>3.28</v>
       </c>
       <c r="T30" t="n">
-        <v>3.2</v>
+        <v>2.38</v>
       </c>
       <c r="U30" t="n">
-        <v>1.29</v>
+        <v>1.49</v>
       </c>
       <c r="V30" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W30" t="n">
-        <v>1.45</v>
+        <v>1.18</v>
       </c>
       <c r="X30" t="n">
-        <v>2.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.12</v>
+        <v>1.65</v>
       </c>
       <c r="Z30" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH30" t="n">
         <v>1.64</v>
       </c>
-      <c r="AA30" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AI30" t="n">
         <v>0</v>
       </c>
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45905.70833333334</v>
+        <v>45905.6875</v>
       </c>
     </row>
     <row r="31">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.86</v>
+        <v>2.05</v>
       </c>
       <c r="M32" t="n">
-        <v>2.91</v>
+        <v>3.2</v>
       </c>
       <c r="N32" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="O32" t="n">
-        <v>2.65</v>
+        <v>2.83</v>
       </c>
       <c r="P32" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="Q32" t="n">
-        <v>5</v>
+        <v>4.22</v>
       </c>
       <c r="R32" t="n">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="S32" t="n">
-        <v>2.04</v>
+        <v>2.54</v>
       </c>
       <c r="T32" t="n">
-        <v>4.15</v>
+        <v>3.2</v>
       </c>
       <c r="U32" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="V32" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="W32" t="n">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="X32" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.9</v>
+        <v>2.12</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.36</v>
+        <v>1.64</v>
       </c>
       <c r="AA32" t="n">
-        <v>6.1</v>
+        <v>4.42</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.6</v>
+        <v>2.11</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.44</v>
+        <v>1.74</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         <v>1.3</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.98</v>
+        <v>1.66</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4618,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
-        <v>45905.79166666666</v>
+        <v>45905.70833333334</v>
       </c>
     </row>
     <row r="33">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.35</v>
+        <v>2.17</v>
       </c>
       <c r="M34" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="N34" t="n">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="O34" t="n">
         <v>2.8</v>
@@ -4812,7 +4812,7 @@
         <v>2.15</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.5</v>
+        <v>3.62</v>
       </c>
       <c r="R34" t="n">
         <v>1.34</v>
@@ -4830,28 +4830,28 @@
         <v>1</v>
       </c>
       <c r="W34" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X34" t="n">
         <v>3.5</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.8</v>
+        <v>2.01</v>
       </c>
       <c r="AA34" t="n">
         <v>2.81</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AC34" t="n">
         <v>1.61</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,78 +4926,78 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.43</v>
+        <v>1.86</v>
       </c>
       <c r="M35" t="n">
-        <v>2.59</v>
+        <v>2.91</v>
       </c>
       <c r="N35" t="n">
-        <v>3.11</v>
+        <v>4.2</v>
       </c>
       <c r="O35" t="n">
-        <v>3.3</v>
+        <v>2.65</v>
       </c>
       <c r="P35" t="n">
-        <v>1.69</v>
+        <v>1.91</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="R35" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="S35" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="T35" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X35" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH35" t="n">
         <v>1.98</v>
       </c>
-      <c r="T35" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.56</v>
-      </c>
       <c r="AI35" t="n">
         <v>0</v>
       </c>
@@ -5005,7 +5005,7 @@
         <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
-        <v>45905.83333333334</v>
+        <v>45905.79166666666</v>
       </c>
     </row>
     <row r="36">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3</v>
+        <v>2.43</v>
       </c>
       <c r="M37" t="n">
-        <v>2.51</v>
+        <v>2.59</v>
       </c>
       <c r="N37" t="n">
-        <v>2.58</v>
+        <v>3.11</v>
       </c>
       <c r="O37" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="P37" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="R37" t="n">
-        <v>1.63</v>
+        <v>1.77</v>
       </c>
       <c r="S37" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="T37" t="n">
-        <v>4.33</v>
+        <v>4.7</v>
       </c>
       <c r="U37" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="V37" t="n">
         <v>1.12</v>
       </c>
       <c r="W37" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="X37" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="Y37" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AA37" t="n">
-        <v>6.45</v>
+        <v>7.4</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.29</v>
+        <v>1.56</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5272,12 +5272,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="M38" t="n">
-        <v>3.45</v>
+        <v>2.51</v>
       </c>
       <c r="N38" t="n">
-        <v>2.35</v>
+        <v>2.58</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.95</v>
+        <v>3.2</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.75</v>
+        <v>1.3</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45905.85416666666</v>
+        <v>45905.83333333334</v>
       </c>
     </row>
     <row r="39">
@@ -5401,12 +5401,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="M39" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="N39" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="O39" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AA39" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5521,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="AK39" s="3" t="n">
-        <v>45905.875</v>
+        <v>45905.85416666666</v>
       </c>
     </row>
     <row r="40">
@@ -5530,12 +5530,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,77 +5571,77 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.52</v>
+        <v>3.39</v>
       </c>
       <c r="M40" t="n">
-        <v>3.37</v>
+        <v>3.24</v>
       </c>
       <c r="N40" t="n">
-        <v>6</v>
+        <v>2.1</v>
       </c>
       <c r="O40" t="n">
-        <v>2.25</v>
+        <v>3.96</v>
       </c>
       <c r="P40" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="Q40" t="n">
-        <v>6.25</v>
+        <v>2.69</v>
       </c>
       <c r="R40" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="S40" t="n">
-        <v>2.4</v>
+        <v>2.72</v>
       </c>
       <c r="T40" t="n">
-        <v>3.48</v>
+        <v>2.79</v>
       </c>
       <c r="U40" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X40" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG40" t="n">
         <v>1.25</v>
       </c>
-      <c r="V40" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X40" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AH40" t="n">
-        <v>1.97</v>
+        <v>1.34</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5650,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="AK40" s="3" t="n">
-        <v>45905.89583333334</v>
+        <v>45905.875</v>
       </c>
     </row>
     <row r="41">
@@ -5659,12 +5659,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="M41" t="n">
-        <v>3.8</v>
+        <v>3.37</v>
       </c>
       <c r="N41" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="O41" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="P41" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.78</v>
+        <v>6.25</v>
       </c>
       <c r="R41" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="S41" t="n">
-        <v>3.15</v>
+        <v>2.4</v>
       </c>
       <c r="T41" t="n">
-        <v>2.57</v>
+        <v>3.48</v>
       </c>
       <c r="U41" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="V41" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="W41" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="X41" t="n">
-        <v>3.5</v>
+        <v>2.53</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.83</v>
+        <v>5.25</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.77</v>
+        <v>2.3</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.99</v>
+        <v>1.57</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5779,7 +5779,7 @@
         <v>0</v>
       </c>
       <c r="AK41" s="3" t="n">
-        <v>45905.97916666666</v>
+        <v>45905.89583333334</v>
       </c>
     </row>
     <row r="42">
@@ -5908,6 +5908,135 @@
         <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
+        <v>45905.97916666666</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>45905</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Phoenix Rising</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Las Vegas Lights</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="M43" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N43" t="n">
+        <v>4</v>
+      </c>
+      <c r="O43" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S43" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X43" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG43" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK43" s="3" t="n">
         <v>45905.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-09-05.xlsx
+++ b/jogos_2025-09-05.xlsx
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="M6" t="n">
         <v>2.9</v>
       </c>
       <c r="N6" t="n">
-        <v>2.87</v>
+        <v>2.37</v>
       </c>
       <c r="O6" t="n">
-        <v>3.07</v>
+        <v>3.71</v>
       </c>
       <c r="P6" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.78</v>
+        <v>3.05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S6" t="n">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="T6" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="U6" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W6" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="X6" t="n">
-        <v>2.92</v>
+        <v>2.81</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.7</v>
+        <v>3.96</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="M7" t="n">
         <v>2.9</v>
       </c>
       <c r="N7" t="n">
-        <v>2.37</v>
+        <v>2.87</v>
       </c>
       <c r="O7" t="n">
-        <v>3.71</v>
+        <v>3.07</v>
       </c>
       <c r="P7" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.05</v>
+        <v>3.78</v>
       </c>
       <c r="R7" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S7" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="T7" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="U7" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W7" t="n">
         <v>1.31</v>
       </c>
-      <c r="V7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.33</v>
-      </c>
       <c r="X7" t="n">
-        <v>2.81</v>
+        <v>2.92</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.96</v>
+        <v>3.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1568,65 +1568,65 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,77 +1830,77 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N11" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="O11" t="n">
-        <v>3.82</v>
+        <v>3.78</v>
       </c>
       <c r="P11" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="R11" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="S11" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X11" t="n">
         <v>2.65</v>
       </c>
-      <c r="T11" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W11" t="n">
+      <c r="Y11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
         <v>1.31</v>
       </c>
-      <c r="X11" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH11" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="M12" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N12" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="O12" t="n">
-        <v>3.78</v>
+        <v>3.82</v>
       </c>
       <c r="P12" t="n">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="R12" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="S12" t="n">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="T12" t="n">
-        <v>3.55</v>
+        <v>3.04</v>
       </c>
       <c r="U12" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="V12" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>1.48</v>
+        <v>1.31</v>
       </c>
       <c r="X12" t="n">
-        <v>2.65</v>
+        <v>2.92</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.38</v>
+        <v>1.96</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.46</v>
+        <v>1.69</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.7</v>
+        <v>3.58</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.12</v>
+        <v>1.81</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.66</v>
+        <v>1.88</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2084,65 +2084,65 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="M20" t="n">
-        <v>4.05</v>
+        <v>2.62</v>
       </c>
       <c r="N20" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.58</v>
+        <v>3.2</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.2</v>
+        <v>1.25</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.2</v>
+        <v>8</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.6</v>
+        <v>1.05</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="M21" t="n">
-        <v>2.62</v>
+        <v>4.05</v>
       </c>
       <c r="N21" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="O21" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>3.3</v>
+        <v>1.58</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.28</v>
+        <v>2.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>6.33</v>
+        <v>2.2</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.05</v>
+        <v>1.6</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3249,25 +3249,25 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="M22" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="N22" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="O22" t="n">
-        <v>4.6</v>
+        <v>4.88</v>
       </c>
       <c r="P22" t="n">
         <v>1.75</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="R22" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="S22" t="n">
         <v>2.14</v>
@@ -3276,34 +3276,34 @@
         <v>3.98</v>
       </c>
       <c r="U22" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="V22" t="n">
         <v>1.1</v>
       </c>
       <c r="W22" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="X22" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AA22" t="n">
-        <v>5.5</v>
+        <v>5.55</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AC22" t="n">
         <v>2.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.67</v>
+        <v>5.17</v>
       </c>
       <c r="M23" t="n">
-        <v>3.02</v>
+        <v>4.22</v>
       </c>
       <c r="N23" t="n">
-        <v>2.42</v>
+        <v>1.53</v>
       </c>
       <c r="O23" t="n">
-        <v>3.36</v>
+        <v>5.5</v>
       </c>
       <c r="P23" t="n">
-        <v>2.21</v>
+        <v>2.51</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.12</v>
+        <v>2.05</v>
       </c>
       <c r="R23" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="S23" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="T23" t="n">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="U23" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V23" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W23" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="X23" t="n">
-        <v>3.5</v>
+        <v>3.98</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.89</v>
+        <v>1.66</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.81</v>
+        <v>2.12</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.14</v>
+        <v>2.52</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.41</v>
+        <v>1.08</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.89</v>
+        <v>2.82</v>
       </c>
       <c r="M24" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="N24" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="O24" t="n">
         <v>3.52</v>
@@ -3528,13 +3528,13 @@
         <v>1.35</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="T24" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="U24" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="V24" t="n">
         <v>1.01</v>
@@ -3543,13 +3543,13 @@
         <v>1.3</v>
       </c>
       <c r="X24" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="Y24" t="n">
         <v>1.85</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AA24" t="n">
         <v>3.13</v>
@@ -3561,7 +3561,7 @@
         <v>1.67</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.5</v>
+        <v>1.26</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.66</v>
+        <v>1.5</v>
       </c>
       <c r="M25" t="n">
-        <v>3.55</v>
+        <v>4.25</v>
       </c>
       <c r="N25" t="n">
-        <v>1.77</v>
+        <v>6</v>
       </c>
       <c r="O25" t="n">
-        <v>3.98</v>
+        <v>1.95</v>
       </c>
       <c r="P25" t="n">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.29</v>
+        <v>5.79</v>
       </c>
       <c r="R25" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="S25" t="n">
-        <v>2.88</v>
+        <v>3.42</v>
       </c>
       <c r="T25" t="n">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="U25" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="V25" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W25" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="X25" t="n">
-        <v>3.5</v>
+        <v>4.22</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.81</v>
+        <v>1.61</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.89</v>
+        <v>2.25</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.05</v>
+        <v>2.35</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.83</v>
+        <v>1.63</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.93</v>
+        <v>2.12</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.18</v>
+        <v>2.4</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.48</v>
+        <v>2.7</v>
       </c>
       <c r="M26" t="n">
-        <v>3.94</v>
+        <v>3.14</v>
       </c>
       <c r="N26" t="n">
-        <v>5.2</v>
+        <v>2.45</v>
       </c>
       <c r="O26" t="n">
-        <v>1.95</v>
+        <v>3.36</v>
       </c>
       <c r="P26" t="n">
-        <v>2.5</v>
+        <v>2.21</v>
       </c>
       <c r="Q26" t="n">
-        <v>5</v>
+        <v>3.12</v>
       </c>
       <c r="R26" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="S26" t="n">
-        <v>3.4</v>
+        <v>2.84</v>
       </c>
       <c r="T26" t="n">
-        <v>2.48</v>
+        <v>2.85</v>
       </c>
       <c r="U26" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="V26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W26" t="n">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="X26" t="n">
-        <v>4.22</v>
+        <v>3.28</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.16</v>
+        <v>3.08</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.28</v>
+        <v>1.41</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>4.8</v>
+        <v>4.11</v>
       </c>
       <c r="M27" t="n">
-        <v>3.84</v>
+        <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>1.54</v>
+        <v>1.77</v>
       </c>
       <c r="O27" t="n">
-        <v>4.95</v>
+        <v>4.25</v>
       </c>
       <c r="P27" t="n">
-        <v>2.46</v>
+        <v>2.15</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="S27" t="n">
-        <v>3.3</v>
+        <v>2.93</v>
       </c>
       <c r="T27" t="n">
-        <v>2.4</v>
+        <v>2.76</v>
       </c>
       <c r="U27" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="V27" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W27" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X27" t="n">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.52</v>
+        <v>2.9</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4155,58 +4155,58 @@
         <v>2.2</v>
       </c>
       <c r="M29" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="N29" t="n">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4284,58 +4284,58 @@
         <v>2.2</v>
       </c>
       <c r="M30" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N30" t="n">
         <v>3.3</v>
       </c>
-      <c r="N30" t="n">
-        <v>2.85</v>
-      </c>
       <c r="O30" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="M31" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="N31" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="M32" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="N32" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="O32" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="M33" t="n">
-        <v>2.98</v>
+        <v>3.11</v>
       </c>
       <c r="N33" t="n">
-        <v>3.86</v>
+        <v>3.75</v>
       </c>
       <c r="O33" t="n">
         <v>2.73</v>
@@ -4689,7 +4689,7 @@
         <v>1.5</v>
       </c>
       <c r="S33" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="T33" t="n">
         <v>3.34</v>
@@ -4701,28 +4701,28 @@
         <v>1.07</v>
       </c>
       <c r="W33" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="X33" t="n">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AA33" t="n">
         <v>4.4</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AC33" t="n">
         <v>2.07</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.17</v>
+        <v>1.88</v>
       </c>
       <c r="M34" t="n">
-        <v>3.34</v>
+        <v>2.9</v>
       </c>
       <c r="N34" t="n">
-        <v>2.95</v>
+        <v>5</v>
       </c>
       <c r="O34" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="P34" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.62</v>
+        <v>6</v>
       </c>
       <c r="R34" t="n">
-        <v>1.34</v>
+        <v>1.67</v>
       </c>
       <c r="S34" t="n">
-        <v>2.98</v>
+        <v>2.13</v>
       </c>
       <c r="T34" t="n">
-        <v>2.55</v>
+        <v>4.15</v>
       </c>
       <c r="U34" t="n">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="V34" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="W34" t="n">
-        <v>1.2</v>
+        <v>1.64</v>
       </c>
       <c r="X34" t="n">
-        <v>3.5</v>
+        <v>2.22</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.77</v>
+        <v>2.97</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.01</v>
+        <v>1.37</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.81</v>
+        <v>6.1</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.33</v>
+        <v>1.06</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.61</v>
+        <v>2.57</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.15</v>
+        <v>1.44</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.86</v>
+        <v>2.17</v>
       </c>
       <c r="M35" t="n">
-        <v>2.91</v>
+        <v>3.34</v>
       </c>
       <c r="N35" t="n">
-        <v>4.2</v>
+        <v>2.95</v>
       </c>
       <c r="O35" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="P35" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="Q35" t="n">
-        <v>5</v>
+        <v>3.62</v>
       </c>
       <c r="R35" t="n">
-        <v>1.65</v>
+        <v>1.34</v>
       </c>
       <c r="S35" t="n">
-        <v>2.04</v>
+        <v>2.98</v>
       </c>
       <c r="T35" t="n">
-        <v>4.15</v>
+        <v>2.55</v>
       </c>
       <c r="U35" t="n">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="V35" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="W35" t="n">
-        <v>1.65</v>
+        <v>1.2</v>
       </c>
       <c r="X35" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.9</v>
+        <v>1.77</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.36</v>
+        <v>2.01</v>
       </c>
       <c r="AA35" t="n">
-        <v>6.1</v>
+        <v>2.81</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.1</v>
+        <v>1.33</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.6</v>
+        <v>1.61</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.44</v>
+        <v>2.15</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.98</v>
+        <v>1.57</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5014,7 +5014,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.62</v>
+        <v>3.16</v>
       </c>
       <c r="M36" t="n">
-        <v>3.42</v>
+        <v>2.69</v>
       </c>
       <c r="N36" t="n">
-        <v>6.02</v>
+        <v>2.5</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45905.83333333334</v>
+        <v>45905.79166666666</v>
       </c>
     </row>
     <row r="37">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.43</v>
+        <v>2.35</v>
       </c>
       <c r="M37" t="n">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="N37" t="n">
-        <v>3.11</v>
+        <v>3.22</v>
       </c>
       <c r="O37" t="n">
         <v>3.3</v>
@@ -5199,13 +5199,13 @@
         <v>1.69</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.6</v>
+        <v>4.77</v>
       </c>
       <c r="R37" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="S37" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="T37" t="n">
         <v>4.7</v>
@@ -5220,10 +5220,10 @@
         <v>1.79</v>
       </c>
       <c r="X37" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Y37" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="Z37" t="n">
         <v>1.28</v>
@@ -5235,10 +5235,10 @@
         <v>1.07</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>1.4</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3</v>
+        <v>1.62</v>
       </c>
       <c r="M38" t="n">
-        <v>2.51</v>
+        <v>3.3</v>
       </c>
       <c r="N38" t="n">
-        <v>2.58</v>
+        <v>6.02</v>
       </c>
       <c r="O38" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5445,10 +5445,10 @@
         <v>2.7</v>
       </c>
       <c r="M39" t="n">
-        <v>3.45</v>
+        <v>3.24</v>
       </c>
       <c r="N39" t="n">
-        <v>2.35</v>
+        <v>2.21</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5700,16 +5700,16 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="M41" t="n">
-        <v>3.37</v>
+        <v>3.5</v>
       </c>
       <c r="N41" t="n">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="O41" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="P41" t="n">
         <v>2.05</v>
@@ -5718,19 +5718,19 @@
         <v>6.25</v>
       </c>
       <c r="R41" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="S41" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="T41" t="n">
         <v>3.48</v>
       </c>
       <c r="U41" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="V41" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W41" t="n">
         <v>1.5</v>
@@ -5739,7 +5739,7 @@
         <v>2.53</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="Z41" t="n">
         <v>1.5</v>
@@ -5748,7 +5748,7 @@
         <v>5.25</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AC41" t="n">
         <v>2.3</v>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.97</v>
+        <v>2.15</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,77 +5829,77 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.35</v>
+        <v>1.71</v>
       </c>
       <c r="M42" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N42" t="n">
+        <v>4</v>
+      </c>
+      <c r="O42" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="P42" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X42" t="n">
         <v>3.5</v>
       </c>
-      <c r="N42" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" t="n">
-        <v>0</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" t="n">
-        <v>0</v>
-      </c>
-      <c r="W42" t="n">
-        <v>0</v>
-      </c>
-      <c r="X42" t="n">
-        <v>0</v>
-      </c>
       <c r="Y42" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="Z42" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG42" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH42" t="n">
         <v>1.95</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>0</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.71</v>
+        <v>2.35</v>
       </c>
       <c r="M43" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N43" t="n">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="O43" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>

--- a/jogos_2025-09-05.xlsx
+++ b/jogos_2025-09-05.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK43"/>
+  <dimension ref="A1:AK33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1015,27 +1015,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="M5" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="N5" t="n">
-        <v>2.36</v>
+        <v>2.75</v>
       </c>
       <c r="O5" t="n">
-        <v>3.22</v>
+        <v>3.99</v>
       </c>
       <c r="P5" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC5" t="n">
         <v>2.09</v>
       </c>
-      <c r="Q5" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.71</v>
-      </c>
       <c r="AD5" t="n">
-        <v>1.94</v>
+        <v>1.68</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.43</v>
+        <v>1.31</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45905.54166666666</v>
+        <v>45905.5625</v>
       </c>
     </row>
     <row r="6">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1181,65 +1181,65 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.07</v>
+        <v>2.6</v>
       </c>
       <c r="P7" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.78</v>
+        <v>4.67</v>
       </c>
       <c r="R7" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S7" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="T7" t="n">
-        <v>3.1</v>
+        <v>3.27</v>
       </c>
       <c r="U7" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W7" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="X7" t="n">
-        <v>2.92</v>
+        <v>2.74</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.09</v>
+        <v>2.21</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.51</v>
+        <v>1.74</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,77 +1443,77 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O8" t="n">
-        <v>2.59</v>
+        <v>3.06</v>
       </c>
       <c r="P8" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.67</v>
+        <v>3.29</v>
       </c>
       <c r="R8" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S8" t="n">
-        <v>2.67</v>
+        <v>2.58</v>
       </c>
       <c r="T8" t="n">
-        <v>3.27</v>
+        <v>3.1</v>
       </c>
       <c r="U8" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
         <v>1.31</v>
       </c>
-      <c r="V8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X8" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH8" t="n">
-        <v>1.74</v>
+        <v>1.51</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,58 +1575,58 @@
         <v>2.05</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="N9" t="n">
-        <v>3.49</v>
+        <v>3.45</v>
       </c>
       <c r="O9" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="P9" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.2</v>
+        <v>3.42</v>
       </c>
       <c r="R9" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S9" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="T9" t="n">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="U9" t="n">
         <v>1.32</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W9" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="X9" t="n">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,62 +1701,62 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.15</v>
+        <v>2.85</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="N10" t="n">
-        <v>3.19</v>
+        <v>2.4</v>
       </c>
       <c r="O10" t="n">
-        <v>2.8</v>
+        <v>3.45</v>
       </c>
       <c r="P10" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="Y10" t="n">
         <v>2.1</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2.12</v>
       </c>
       <c r="Z10" t="n">
         <v>1.65</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.74</v>
+        <v>3.95</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AC10" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AD10" t="n">
         <v>1.85</v>
       </c>
-      <c r="AD10" t="n">
-        <v>1.84</v>
-      </c>
       <c r="AE10" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.82</v>
+        <v>3.05</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="O11" t="n">
-        <v>3.78</v>
+        <v>3.9</v>
       </c>
       <c r="P11" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="R11" t="n">
         <v>1.46</v>
       </c>
       <c r="S11" t="n">
-        <v>2.45</v>
+        <v>2.52</v>
       </c>
       <c r="T11" t="n">
-        <v>3.55</v>
+        <v>3.14</v>
       </c>
       <c r="U11" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="V11" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W11" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="X11" t="n">
-        <v>2.65</v>
+        <v>2.78</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.46</v>
+        <v>1.65</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>1.31</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="T12" t="n">
         <v>2.9</v>
       </c>
-      <c r="M12" t="n">
-        <v>3</v>
-      </c>
-      <c r="N12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="O12" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3.04</v>
-      </c>
       <c r="U12" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W12" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="X12" t="n">
-        <v>2.92</v>
+        <v>2.74</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45905.5625</v>
+        <v>45905.58333333334</v>
       </c>
     </row>
     <row r="14">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45905.58333333334</v>
+        <v>45905.625</v>
       </c>
     </row>
     <row r="15">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Real Betis II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gimnàstic de Tarragona</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45905.59375</v>
+        <v>45905.625</v>
       </c>
     </row>
     <row r="16">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="M16" t="n">
-        <v>3.25</v>
+        <v>4.05</v>
       </c>
       <c r="N16" t="n">
-        <v>3.92</v>
+        <v>4.8</v>
       </c>
       <c r="O16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.06</v>
+        <v>1.58</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.81</v>
+        <v>2.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.55</v>
+        <v>2.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.29</v>
+        <v>1.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45905.60416666666</v>
+        <v>45905.64583333334</v>
       </c>
     </row>
     <row r="17">
@@ -2563,27 +2563,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="M17" t="n">
-        <v>4.3</v>
+        <v>2.62</v>
       </c>
       <c r="N17" t="n">
-        <v>4.33</v>
+        <v>5.5</v>
       </c>
       <c r="O17" t="n">
-        <v>2.12</v>
+        <v>2.66</v>
       </c>
       <c r="P17" t="n">
-        <v>2.56</v>
+        <v>1.81</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.33</v>
+        <v>6.75</v>
       </c>
       <c r="R17" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Z17" t="n">
         <v>1.25</v>
       </c>
-      <c r="S17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X17" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.31</v>
-      </c>
       <c r="AA17" t="n">
-        <v>2.35</v>
+        <v>8</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.57</v>
+        <v>1.05</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.55</v>
+        <v>2.84</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.32</v>
+        <v>1.36</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.19</v>
+        <v>1.83</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45905.625</v>
+        <v>45905.64583333334</v>
       </c>
     </row>
     <row r="18">
@@ -2692,27 +2692,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45905.625</v>
+        <v>45905.64583333334</v>
       </c>
     </row>
     <row r="19">
@@ -2821,27 +2821,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>5.79</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45905.625</v>
+        <v>45905.65625</v>
       </c>
     </row>
     <row r="20">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z20" t="n">
         <v>1.9</v>
       </c>
-      <c r="M20" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="N20" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="O20" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="T20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AA20" t="n">
-        <v>8</v>
+        <v>3.13</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.05</v>
+        <v>1.31</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.84</v>
+        <v>1.67</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.36</v>
+        <v>2.1</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.83</v>
+        <v>1.37</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45905.64583333334</v>
+        <v>45905.65625</v>
       </c>
     </row>
     <row r="21">
@@ -3079,27 +3079,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="M21" t="n">
-        <v>4.05</v>
+        <v>3.14</v>
       </c>
       <c r="N21" t="n">
-        <v>4.8</v>
+        <v>2.45</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.2</v>
+        <v>3.08</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.6</v>
+        <v>1.28</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45905.64583333334</v>
+        <v>45905.65625</v>
       </c>
     </row>
     <row r="22">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,77 +3249,77 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.4</v>
+        <v>5.17</v>
       </c>
       <c r="M22" t="n">
-        <v>2.75</v>
+        <v>4.22</v>
       </c>
       <c r="N22" t="n">
-        <v>2.15</v>
+        <v>1.53</v>
       </c>
       <c r="O22" t="n">
-        <v>4.88</v>
+        <v>5.5</v>
       </c>
       <c r="P22" t="n">
-        <v>1.75</v>
+        <v>2.51</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.06</v>
+        <v>2.05</v>
       </c>
       <c r="R22" t="n">
-        <v>1.69</v>
+        <v>1.3</v>
       </c>
       <c r="S22" t="n">
-        <v>2.14</v>
+        <v>3.2</v>
       </c>
       <c r="T22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X22" t="n">
         <v>3.98</v>
       </c>
-      <c r="U22" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.17</v>
-      </c>
       <c r="Y22" t="n">
-        <v>2.98</v>
+        <v>1.66</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.34</v>
+        <v>2.12</v>
       </c>
       <c r="AA22" t="n">
-        <v>5.55</v>
+        <v>2.52</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.11</v>
+        <v>1.41</v>
       </c>
       <c r="AC22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
         <v>2.3</v>
       </c>
-      <c r="AD22" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AH22" t="n">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45905.64583333334</v>
+        <v>45905.65625</v>
       </c>
     </row>
     <row r="23">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>5.17</v>
+        <v>4.11</v>
       </c>
       <c r="M23" t="n">
-        <v>4.22</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="O23" t="n">
-        <v>5.5</v>
+        <v>4.25</v>
       </c>
       <c r="P23" t="n">
-        <v>2.51</v>
+        <v>2.15</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="S23" t="n">
-        <v>3.2</v>
+        <v>2.93</v>
       </c>
       <c r="T23" t="n">
-        <v>2.4</v>
+        <v>2.76</v>
       </c>
       <c r="U23" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="V23" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W23" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X23" t="n">
-        <v>3.98</v>
+        <v>3.6</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.52</v>
+        <v>2.9</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>2.3</v>
+        <v>1.24</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3466,27 +3466,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45905.65625</v>
+        <v>45905.66666666666</v>
       </c>
     </row>
     <row r="25">
@@ -3595,12 +3595,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.5</v>
+        <v>2.09</v>
       </c>
       <c r="M25" t="n">
-        <v>4.25</v>
+        <v>3.15</v>
       </c>
       <c r="N25" t="n">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="O25" t="n">
-        <v>1.95</v>
+        <v>2.83</v>
       </c>
       <c r="P25" t="n">
-        <v>2.23</v>
+        <v>1.98</v>
       </c>
       <c r="Q25" t="n">
-        <v>5.79</v>
+        <v>4.22</v>
       </c>
       <c r="R25" t="n">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="S25" t="n">
-        <v>3.42</v>
+        <v>2.5</v>
       </c>
       <c r="T25" t="n">
-        <v>2.48</v>
+        <v>3.2</v>
       </c>
       <c r="U25" t="n">
-        <v>1.56</v>
+        <v>1.29</v>
       </c>
       <c r="V25" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W25" t="n">
-        <v>1.12</v>
+        <v>1.45</v>
       </c>
       <c r="X25" t="n">
-        <v>4.22</v>
+        <v>2.6</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.61</v>
+        <v>2.33</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.25</v>
+        <v>1.58</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.35</v>
+        <v>4.42</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.45</v>
+        <v>1.2</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.63</v>
+        <v>2.11</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.12</v>
+        <v>1.77</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.4</v>
+        <v>1.66</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45905.65625</v>
+        <v>45905.70833333334</v>
       </c>
     </row>
     <row r="26">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,77 +3765,77 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.7</v>
+        <v>1.88</v>
       </c>
       <c r="M26" t="n">
-        <v>3.14</v>
+        <v>2.9</v>
       </c>
       <c r="N26" t="n">
-        <v>2.45</v>
+        <v>5</v>
       </c>
       <c r="O26" t="n">
-        <v>3.36</v>
+        <v>2.65</v>
       </c>
       <c r="P26" t="n">
-        <v>2.21</v>
+        <v>1.85</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.12</v>
+        <v>6</v>
       </c>
       <c r="R26" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="T26" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="X26" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="Z26" t="n">
         <v>1.37</v>
       </c>
-      <c r="S26" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W26" t="n">
+      <c r="AA26" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
         <v>1.3</v>
       </c>
-      <c r="X26" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH26" t="n">
-        <v>1.41</v>
+        <v>1.91</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45905.65625</v>
+        <v>45905.79166666666</v>
       </c>
     </row>
     <row r="27">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,77 +3894,77 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>4.11</v>
+        <v>2.05</v>
       </c>
       <c r="M27" t="n">
-        <v>3.4</v>
+        <v>3.11</v>
       </c>
       <c r="N27" t="n">
-        <v>1.77</v>
+        <v>3.75</v>
       </c>
       <c r="O27" t="n">
-        <v>4.25</v>
+        <v>2.73</v>
       </c>
       <c r="P27" t="n">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.4</v>
+        <v>4.7</v>
       </c>
       <c r="R27" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="S27" t="n">
-        <v>2.93</v>
+        <v>2.5</v>
       </c>
       <c r="T27" t="n">
-        <v>2.76</v>
+        <v>3.34</v>
       </c>
       <c r="U27" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="V27" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="W27" t="n">
-        <v>1.22</v>
+        <v>1.48</v>
       </c>
       <c r="X27" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.85</v>
+        <v>2.33</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.89</v>
+        <v>1.54</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.9</v>
+        <v>4.4</v>
       </c>
       <c r="AB27" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
         <v>1.34</v>
       </c>
-      <c r="AC27" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AH27" t="n">
-        <v>1.18</v>
+        <v>1.72</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45905.65625</v>
+        <v>45905.79166666666</v>
       </c>
     </row>
     <row r="28">
@@ -3982,27 +3982,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45905.66666666666</v>
+        <v>45905.79166666666</v>
       </c>
     </row>
     <row r="29">
@@ -4111,27 +4111,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="M29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="O29" t="n">
         <v>3.3</v>
       </c>
-      <c r="N29" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="O29" t="n">
-        <v>2.78</v>
-      </c>
       <c r="P29" t="n">
-        <v>2.28</v>
+        <v>1.69</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.13</v>
+        <v>4.77</v>
       </c>
       <c r="R29" t="n">
-        <v>1.29</v>
+        <v>1.76</v>
       </c>
       <c r="S29" t="n">
-        <v>3.28</v>
+        <v>2</v>
       </c>
       <c r="T29" t="n">
-        <v>2.38</v>
+        <v>4.7</v>
       </c>
       <c r="U29" t="n">
-        <v>1.49</v>
+        <v>1.14</v>
       </c>
       <c r="V29" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="W29" t="n">
-        <v>1.18</v>
+        <v>1.79</v>
       </c>
       <c r="X29" t="n">
-        <v>4.5</v>
+        <v>1.92</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.65</v>
+        <v>3.6</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.22</v>
+        <v>1.28</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.56</v>
+        <v>7.4</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.53</v>
+        <v>1.07</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.57</v>
+        <v>2.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45905.6875</v>
+        <v>45905.83333333334</v>
       </c>
     </row>
     <row r="30">
@@ -4240,27 +4240,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.2</v>
+        <v>1.62</v>
       </c>
       <c r="M30" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="N30" t="n">
-        <v>3.3</v>
+        <v>6.02</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45905.6875</v>
+        <v>45905.83333333334</v>
       </c>
     </row>
     <row r="31">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.09</v>
+        <v>2.7</v>
       </c>
       <c r="M31" t="n">
-        <v>3.15</v>
+        <v>3.24</v>
       </c>
       <c r="N31" t="n">
-        <v>3.6</v>
+        <v>2.21</v>
       </c>
       <c r="O31" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AA31" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45905.70833333334</v>
+        <v>45905.85416666666</v>
       </c>
     </row>
     <row r="32">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="M32" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="N32" t="n">
-        <v>3</v>
+        <v>5.25</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4618,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
-        <v>45905.70833333334</v>
+        <v>45905.89583333334</v>
       </c>
     </row>
     <row r="33">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="M33" t="n">
-        <v>3.11</v>
+        <v>3.5</v>
       </c>
       <c r="N33" t="n">
-        <v>3.75</v>
+        <v>2.7</v>
       </c>
       <c r="O33" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.33</v>
+        <v>1.8</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.54</v>
+        <v>2</v>
       </c>
       <c r="AA33" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4747,1296 +4747,6 @@
         <v>0</v>
       </c>
       <c r="AK33" s="3" t="n">
-        <v>45905.79166666666</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="n">
-        <v>45905</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Argentina Prim B Nacional</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Estudiantes Caseros</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Nueva Chicago</t>
-        </is>
-      </c>
-      <c r="G34" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L34" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="M34" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N34" t="n">
-        <v>5</v>
-      </c>
-      <c r="O34" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="P34" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>6</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="T34" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="X34" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK34" s="3" t="n">
-        <v>45905.79166666666</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="n">
-        <v>45905</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Lexington</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>North Carolina FC</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L35" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="M35" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="N35" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="O35" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X35" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK35" s="3" t="n">
-        <v>45905.79166666666</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="n">
-        <v>45905</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Argentina Prim B Nacional</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Colegiales</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>San Martín Tucumán</t>
-        </is>
-      </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L36" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="M36" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="N36" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O36" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="P36" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="S36" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="T36" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="X36" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK36" s="3" t="n">
-        <v>45905.79166666666</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="n">
-        <v>45905</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Argentina Prim B Nacional</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>All Boys</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Gimnasia y Tiro</t>
-        </is>
-      </c>
-      <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L37" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="M37" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="N37" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="O37" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P37" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="S37" t="n">
-        <v>2</v>
-      </c>
-      <c r="T37" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="X37" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK37" s="3" t="n">
-        <v>45905.83333333334</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="n">
-        <v>45905</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Argentina Prim B Nacional</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Temperley</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Talleres Remedios</t>
-        </is>
-      </c>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L38" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="M38" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N38" t="n">
-        <v>6.02</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" t="n">
-        <v>0</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK38" s="3" t="n">
-        <v>45905.83333333334</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="n">
-        <v>45905</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Canada Canadian Premier League</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>York9 FC</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Cavalry FC</t>
-        </is>
-      </c>
-      <c r="G39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L39" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="M39" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="N39" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK39" s="3" t="n">
-        <v>45905.85416666666</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="n">
-        <v>45905</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Racing Louisville</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Portland Thorns</t>
-        </is>
-      </c>
-      <c r="G40" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L40" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="M40" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="N40" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="O40" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="P40" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S40" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="T40" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X40" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK40" s="3" t="n">
-        <v>45905.875</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="n">
-        <v>45905</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Coritiba</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Ferroviária</t>
-        </is>
-      </c>
-      <c r="G41" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L41" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="M41" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N41" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="O41" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="P41" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="R41" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S41" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T41" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X41" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK41" s="3" t="n">
-        <v>45905.89583333334</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="n">
-        <v>45905</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Phoenix Rising</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Las Vegas Lights</t>
-        </is>
-      </c>
-      <c r="G42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L42" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="M42" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N42" t="n">
-        <v>4</v>
-      </c>
-      <c r="O42" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="P42" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S42" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="T42" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X42" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG42" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK42" s="3" t="n">
-        <v>45905.97916666666</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="n">
-        <v>45905</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Canada Canadian Premier League</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Vancouver FC</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Valour FC</t>
-        </is>
-      </c>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L43" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="M43" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N43" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" t="n">
-        <v>0</v>
-      </c>
-      <c r="W43" t="n">
-        <v>0</v>
-      </c>
-      <c r="X43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK43" s="3" t="n">
         <v>45905.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-09-05.xlsx
+++ b/jogos_2025-09-05.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK33"/>
+  <dimension ref="A1:AK43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,22 +762,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1015,27 +1015,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="M5" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="N5" t="n">
-        <v>2.75</v>
+        <v>2.36</v>
       </c>
       <c r="O5" t="n">
-        <v>3.99</v>
+        <v>3.22</v>
       </c>
       <c r="P5" t="n">
-        <v>1.95</v>
+        <v>2.09</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.92</v>
+        <v>3.04</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="S5" t="n">
-        <v>2.41</v>
+        <v>2.79</v>
       </c>
       <c r="T5" t="n">
-        <v>3.4</v>
+        <v>2.72</v>
       </c>
       <c r="U5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AB5" t="n">
         <v>1.27</v>
       </c>
-      <c r="V5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AC5" t="n">
-        <v>2.09</v>
+        <v>1.71</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.68</v>
+        <v>1.94</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45905.5625</v>
+        <v>45905.54166666666</v>
       </c>
     </row>
     <row r="6">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1181,65 +1181,65 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -1323,52 +1323,52 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,43 +1443,43 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.55</v>
+        <v>3.05</v>
       </c>
       <c r="M8" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N8" t="n">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="O8" t="n">
-        <v>3.06</v>
+        <v>3.9</v>
       </c>
       <c r="P8" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.29</v>
+        <v>2.95</v>
       </c>
       <c r="R8" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S8" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="T8" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="U8" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W8" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="X8" t="n">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="Y8" t="n">
         <v>2.1</v>
@@ -1488,16 +1488,16 @@
         <v>1.65</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>1.31</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.51</v>
+        <v>1.32</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,22 +1572,22 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.05</v>
+        <v>2.55</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="N9" t="n">
-        <v>3.45</v>
+        <v>2.7</v>
       </c>
       <c r="O9" t="n">
-        <v>2.72</v>
+        <v>3.06</v>
       </c>
       <c r="P9" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.42</v>
+        <v>3.29</v>
       </c>
       <c r="R9" t="n">
         <v>1.44</v>
@@ -1602,31 +1602,31 @@
         <v>1.32</v>
       </c>
       <c r="V9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="X9" t="n">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.45</v>
+        <v>2.6</v>
       </c>
       <c r="P10" t="n">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.05</v>
+        <v>4.67</v>
       </c>
       <c r="R10" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S10" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="T10" t="n">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="U10" t="n">
         <v>1.31</v>
       </c>
       <c r="V10" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W10" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X10" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.36</v>
+        <v>1.74</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.05</v>
+        <v>2.05</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N11" t="n">
-        <v>2.25</v>
+        <v>3.45</v>
       </c>
       <c r="O11" t="n">
-        <v>3.9</v>
+        <v>2.72</v>
       </c>
       <c r="P11" t="n">
         <v>1.96</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.95</v>
+        <v>3.42</v>
       </c>
       <c r="R11" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="S11" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="T11" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="U11" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="V11" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W11" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="X11" t="n">
         <v>2.78</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AA11" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.08</v>
+        <v>1.85</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.32</v>
+        <v>1.6</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="M12" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="N12" t="n">
-        <v>3.55</v>
+        <v>2.75</v>
       </c>
       <c r="O12" t="n">
-        <v>2.51</v>
+        <v>3.99</v>
       </c>
       <c r="P12" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.3</v>
+        <v>2.92</v>
       </c>
       <c r="R12" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="S12" t="n">
-        <v>2.61</v>
+        <v>2.41</v>
       </c>
       <c r="T12" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="U12" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="V12" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W12" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="X12" t="n">
-        <v>2.74</v>
+        <v>2.45</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AB12" t="n">
         <v>1.17</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.91</v>
+        <v>2.09</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.63</v>
+        <v>1.32</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45905.58333333334</v>
+        <v>45905.5625</v>
       </c>
     </row>
     <row r="14">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45905.625</v>
+        <v>45905.58333333334</v>
       </c>
     </row>
     <row r="15">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Real Betis II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Gimnàstic de Tarragona</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>2.12</v>
+        <v>3.44</v>
       </c>
       <c r="P15" t="n">
-        <v>2.56</v>
+        <v>1.95</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.33</v>
+        <v>3.18</v>
       </c>
       <c r="R15" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="S15" t="n">
-        <v>3.5</v>
+        <v>2.55</v>
       </c>
       <c r="T15" t="n">
-        <v>2.3</v>
+        <v>3.26</v>
       </c>
       <c r="U15" t="n">
-        <v>1.59</v>
+        <v>1.29</v>
       </c>
       <c r="V15" t="n">
         <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="X15" t="n">
-        <v>4.75</v>
+        <v>2.74</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.31</v>
+        <v>1.6</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.35</v>
+        <v>4.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.57</v>
+        <v>1.16</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.32</v>
+        <v>1.82</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.19</v>
+        <v>1.4</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45905.625</v>
+        <v>45905.59375</v>
       </c>
     </row>
     <row r="16">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.6</v>
+        <v>1.87</v>
       </c>
       <c r="M16" t="n">
-        <v>4.05</v>
+        <v>3.6</v>
       </c>
       <c r="N16" t="n">
-        <v>4.8</v>
+        <v>3.89</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.58</v>
+        <v>1.98</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.2</v>
+        <v>1.77</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.2</v>
+        <v>3.55</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45905.64583333334</v>
+        <v>45905.60416666666</v>
       </c>
     </row>
     <row r="17">
@@ -2563,27 +2563,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="M17" t="n">
-        <v>2.62</v>
+        <v>4.3</v>
       </c>
       <c r="N17" t="n">
-        <v>5.5</v>
+        <v>4.33</v>
       </c>
       <c r="O17" t="n">
-        <v>2.66</v>
+        <v>2.12</v>
       </c>
       <c r="P17" t="n">
-        <v>1.81</v>
+        <v>2.56</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.75</v>
+        <v>4.33</v>
       </c>
       <c r="R17" t="n">
-        <v>1.76</v>
+        <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>1.94</v>
+        <v>3.5</v>
       </c>
       <c r="T17" t="n">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="U17" t="n">
-        <v>1.15</v>
+        <v>1.59</v>
       </c>
       <c r="V17" t="n">
-        <v>1.19</v>
+        <v>1.02</v>
       </c>
       <c r="W17" t="n">
-        <v>1.82</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
-        <v>1.9</v>
+        <v>4.75</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.2</v>
+        <v>1.57</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.25</v>
+        <v>2.31</v>
       </c>
       <c r="AA17" t="n">
-        <v>8</v>
+        <v>2.35</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.05</v>
+        <v>1.57</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.84</v>
+        <v>1.55</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.36</v>
+        <v>2.32</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.83</v>
+        <v>2.19</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45905.64583333334</v>
+        <v>45905.625</v>
       </c>
     </row>
     <row r="18">
@@ -2692,27 +2692,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>4.88</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45905.64583333334</v>
+        <v>45905.625</v>
       </c>
     </row>
     <row r="19">
@@ -2821,27 +2821,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.79</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45905.65625</v>
+        <v>45905.625</v>
       </c>
     </row>
     <row r="20">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.82</v>
+        <v>3.4</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="N20" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="O20" t="n">
-        <v>3.52</v>
+        <v>4.88</v>
       </c>
       <c r="P20" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.88</v>
+        <v>3.06</v>
       </c>
       <c r="R20" t="n">
-        <v>1.35</v>
+        <v>1.69</v>
       </c>
       <c r="S20" t="n">
-        <v>2.93</v>
+        <v>2.14</v>
       </c>
       <c r="T20" t="n">
-        <v>2.65</v>
+        <v>3.98</v>
       </c>
       <c r="U20" t="n">
-        <v>1.42</v>
+        <v>1.19</v>
       </c>
       <c r="V20" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="W20" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="X20" t="n">
-        <v>3.7</v>
+        <v>2.17</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.85</v>
+        <v>2.98</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.9</v>
+        <v>1.34</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.13</v>
+        <v>5.55</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.31</v>
+        <v>1.11</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.1</v>
+        <v>1.54</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.37</v>
+        <v>1.23</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45905.65625</v>
+        <v>45905.64583333334</v>
       </c>
     </row>
     <row r="21">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="M21" t="n">
-        <v>3.14</v>
+        <v>2.62</v>
       </c>
       <c r="N21" t="n">
-        <v>2.45</v>
+        <v>5.5</v>
       </c>
       <c r="O21" t="n">
-        <v>3.36</v>
+        <v>2.66</v>
       </c>
       <c r="P21" t="n">
-        <v>2.21</v>
+        <v>1.81</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.12</v>
+        <v>6.75</v>
       </c>
       <c r="R21" t="n">
-        <v>1.37</v>
+        <v>1.76</v>
       </c>
       <c r="S21" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="T21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC21" t="n">
         <v>2.84</v>
       </c>
-      <c r="T21" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X21" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AD21" t="n">
-        <v>2.04</v>
+        <v>1.36</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.41</v>
+        <v>1.83</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45905.65625</v>
+        <v>45905.64583333334</v>
       </c>
     </row>
     <row r="22">
@@ -3208,27 +3208,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>5.17</v>
+        <v>1.6</v>
       </c>
       <c r="M22" t="n">
-        <v>4.22</v>
+        <v>4.05</v>
       </c>
       <c r="N22" t="n">
-        <v>1.53</v>
+        <v>4.8</v>
       </c>
       <c r="O22" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.52</v>
+        <v>2.2</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45905.65625</v>
+        <v>45905.64583333334</v>
       </c>
     </row>
     <row r="23">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,22 +3378,22 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>4.11</v>
+        <v>2.82</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N23" t="n">
-        <v>1.77</v>
+        <v>2.25</v>
       </c>
       <c r="O23" t="n">
-        <v>4.25</v>
+        <v>3.52</v>
       </c>
       <c r="P23" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="R23" t="n">
         <v>1.35</v>
@@ -3402,37 +3402,37 @@
         <v>2.93</v>
       </c>
       <c r="T23" t="n">
-        <v>2.76</v>
+        <v>2.65</v>
       </c>
       <c r="U23" t="n">
         <v>1.42</v>
       </c>
       <c r="V23" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="X23" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Y23" t="n">
         <v>1.85</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.9</v>
+        <v>3.13</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3466,27 +3466,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45905.66666666666</v>
+        <v>45905.65625</v>
       </c>
     </row>
     <row r="25">
@@ -3595,12 +3595,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.09</v>
+        <v>1.5</v>
       </c>
       <c r="M25" t="n">
-        <v>3.15</v>
+        <v>4.25</v>
       </c>
       <c r="N25" t="n">
-        <v>3.6</v>
+        <v>6</v>
       </c>
       <c r="O25" t="n">
-        <v>2.83</v>
+        <v>1.95</v>
       </c>
       <c r="P25" t="n">
-        <v>1.98</v>
+        <v>2.23</v>
       </c>
       <c r="Q25" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X25" t="n">
         <v>4.22</v>
       </c>
-      <c r="R25" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W25" t="n">
+      <c r="Y25" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB25" t="n">
         <v>1.45</v>
       </c>
-      <c r="X25" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AC25" t="n">
-        <v>2.11</v>
+        <v>1.63</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.77</v>
+        <v>2.12</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.66</v>
+        <v>2.4</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45905.70833333334</v>
+        <v>45905.65625</v>
       </c>
     </row>
     <row r="26">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.88</v>
+        <v>5.17</v>
       </c>
       <c r="M26" t="n">
-        <v>2.9</v>
+        <v>4.22</v>
       </c>
       <c r="N26" t="n">
-        <v>5</v>
+        <v>1.53</v>
       </c>
       <c r="O26" t="n">
-        <v>2.65</v>
+        <v>5.5</v>
       </c>
       <c r="P26" t="n">
-        <v>1.85</v>
+        <v>2.51</v>
       </c>
       <c r="Q26" t="n">
-        <v>6</v>
+        <v>2.05</v>
       </c>
       <c r="R26" t="n">
-        <v>1.67</v>
+        <v>1.3</v>
       </c>
       <c r="S26" t="n">
-        <v>2.13</v>
+        <v>3.2</v>
       </c>
       <c r="T26" t="n">
-        <v>4.15</v>
+        <v>2.4</v>
       </c>
       <c r="U26" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="V26" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="W26" t="n">
-        <v>1.64</v>
+        <v>1.2</v>
       </c>
       <c r="X26" t="n">
-        <v>2.22</v>
+        <v>3.98</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.97</v>
+        <v>1.66</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.37</v>
+        <v>2.12</v>
       </c>
       <c r="AA26" t="n">
-        <v>6.1</v>
+        <v>2.52</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.06</v>
+        <v>1.41</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.57</v>
+        <v>1.7</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.44</v>
+        <v>1.95</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.91</v>
+        <v>1.08</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45905.79166666666</v>
+        <v>45905.65625</v>
       </c>
     </row>
     <row r="27">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,78 +3894,78 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.05</v>
+        <v>4.11</v>
       </c>
       <c r="M27" t="n">
-        <v>3.11</v>
+        <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>3.75</v>
+        <v>1.77</v>
       </c>
       <c r="O27" t="n">
-        <v>2.73</v>
+        <v>4.25</v>
       </c>
       <c r="P27" t="n">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.7</v>
+        <v>2.4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="S27" t="n">
-        <v>2.5</v>
+        <v>2.93</v>
       </c>
       <c r="T27" t="n">
-        <v>3.34</v>
+        <v>2.76</v>
       </c>
       <c r="U27" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="V27" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="W27" t="n">
-        <v>1.48</v>
+        <v>1.22</v>
       </c>
       <c r="X27" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.33</v>
+        <v>1.85</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.54</v>
+        <v>1.89</v>
       </c>
       <c r="AA27" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="AB27" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH27" t="n">
         <v>1.18</v>
       </c>
-      <c r="AC27" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AI27" t="n">
         <v>0</v>
       </c>
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45905.79166666666</v>
+        <v>45905.65625</v>
       </c>
     </row>
     <row r="28">
@@ -3982,27 +3982,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>4.34</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45905.79166666666</v>
+        <v>45905.66666666666</v>
       </c>
     </row>
     <row r="29">
@@ -4111,27 +4111,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O29" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X29" t="n">
         <v>2.35</v>
       </c>
-      <c r="M29" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="N29" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="O29" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P29" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T29" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1.92</v>
-      </c>
       <c r="Y29" t="n">
-        <v>3.6</v>
+        <v>2.49</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="AA29" t="n">
-        <v>7.4</v>
+        <v>5</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.6</v>
+        <v>2.09</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45905.83333333334</v>
+        <v>45905.6875</v>
       </c>
     </row>
     <row r="30">
@@ -4240,27 +4240,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.62</v>
+        <v>2.15</v>
       </c>
       <c r="M30" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="N30" t="n">
-        <v>6.02</v>
+        <v>3.09</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45905.83333333334</v>
+        <v>45905.6875</v>
       </c>
     </row>
     <row r="31">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.7</v>
+        <v>2.05</v>
       </c>
       <c r="M31" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="N31" t="n">
-        <v>2.21</v>
+        <v>3.6</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y31" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45905.85416666666</v>
+        <v>45905.70833333334</v>
       </c>
     </row>
     <row r="32">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="M32" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N32" t="n">
-        <v>5.25</v>
+        <v>3</v>
       </c>
       <c r="O32" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4618,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
-        <v>45905.89583333334</v>
+        <v>45905.70833333334</v>
       </c>
     </row>
     <row r="33">
@@ -4627,126 +4627,1416 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Lexington</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>North Carolina FC</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="M33" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O33" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" s="3" t="n">
+        <v>45905.79166666666</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>45905</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Paysandu</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Volta Redonda</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M34" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="N34" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="O34" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X34" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK34" s="3" t="n">
+        <v>45905.79166666666</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>45905</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Estudiantes Caseros</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Nueva Chicago</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="M35" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N35" t="n">
+        <v>5</v>
+      </c>
+      <c r="O35" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>6</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="T35" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="X35" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK35" s="3" t="n">
+        <v>45905.79166666666</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>45905</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Colegiales</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>San Martín Tucumán</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="M36" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="N36" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O36" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="T36" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="X36" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK36" s="3" t="n">
+        <v>45905.79166666666</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>45905</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>All Boys</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Gimnasia y Tiro</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="M37" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="N37" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="O37" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2</v>
+      </c>
+      <c r="T37" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK37" s="3" t="n">
+        <v>45905.83333333334</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>45905</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Temperley</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Talleres Remedios</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="M38" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N38" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" s="3" t="n">
+        <v>45905.83333333334</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>45905</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Canada Canadian Premier League</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>York9 FC</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Cavalry FC</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M39" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N39" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK39" s="3" t="n">
+        <v>45905.85416666666</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>45905</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Racing Louisville</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Portland Thorns</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M40" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N40" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O40" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P40" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S40" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X40" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK40" s="3" t="n">
+        <v>45905.875</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>45905</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Ferroviária</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M41" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="N41" t="n">
+        <v>6</v>
+      </c>
+      <c r="O41" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="P41" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S41" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X41" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG41" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK41" s="3" t="n">
+        <v>45905.89583333334</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>45905</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
           <t>23:30</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Phoenix Rising</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Las Vegas Lights</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="M42" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="N42" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O42" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="P42" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X42" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG42" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="3" t="n">
+        <v>45905.97916666666</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>45905</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
         <is>
           <t>Canada Canadian Premier League</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>Vancouver FC</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>Valour FC</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="inlineStr">
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L33" t="n">
+      <c r="L43" t="n">
         <v>2.35</v>
       </c>
-      <c r="M33" t="n">
+      <c r="M43" t="n">
         <v>3.5</v>
       </c>
-      <c r="N33" t="n">
+      <c r="N43" t="n">
         <v>2.7</v>
       </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0</v>
-      </c>
-      <c r="X33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK33" s="3" t="n">
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK43" s="3" t="n">
         <v>45905.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-09-05.xlsx
+++ b/jogos_2025-09-05.xlsx
@@ -757,7 +757,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>45905.54166666666</v>
+        <v>45905.5</v>
       </c>
     </row>
     <row r="4">
@@ -886,27 +886,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>45905.54166666666</v>
+        <v>45905.5</v>
       </c>
     </row>
     <row r="5">
@@ -1015,27 +1015,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45905.54166666666</v>
+        <v>45905.5</v>
       </c>
     </row>
     <row r="6">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45905.5625</v>
+        <v>45905.5</v>
       </c>
     </row>
     <row r="7">
@@ -1273,27 +1273,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1310,17 +1310,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45905.5625</v>
+        <v>45905.54166666666</v>
       </c>
     </row>
     <row r="8">
@@ -1402,27 +1402,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.05</v>
+        <v>2.55</v>
       </c>
       <c r="M8" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N8" t="n">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="O8" t="n">
-        <v>3.9</v>
+        <v>3.72</v>
       </c>
       <c r="P8" t="n">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.95</v>
+        <v>2.68</v>
       </c>
       <c r="R8" t="n">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="S8" t="n">
-        <v>2.52</v>
+        <v>2.85</v>
       </c>
       <c r="T8" t="n">
-        <v>3.14</v>
+        <v>2.61</v>
       </c>
       <c r="U8" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="V8" t="n">
         <v>1.02</v>
       </c>
       <c r="W8" t="n">
-        <v>1.39</v>
+        <v>1.23</v>
       </c>
       <c r="X8" t="n">
-        <v>2.78</v>
+        <v>3.42</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AA8" t="n">
-        <v>4</v>
+        <v>2.92</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.08</v>
+        <v>1.71</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.7</v>
+        <v>1.94</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45905.5625</v>
+        <v>45905.54166666666</v>
       </c>
     </row>
     <row r="9">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,43 +1572,43 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.55</v>
+        <v>2.85</v>
       </c>
       <c r="M9" t="n">
         <v>3.15</v>
       </c>
       <c r="N9" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="O9" t="n">
-        <v>3.06</v>
+        <v>3.71</v>
       </c>
       <c r="P9" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.29</v>
+        <v>3.08</v>
       </c>
       <c r="R9" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S9" t="n">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="T9" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="U9" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="X9" t="n">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="Y9" t="n">
         <v>2.1</v>
@@ -1617,16 +1617,16 @@
         <v>1.65</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>1.31</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O10" t="n">
-        <v>2.6</v>
+        <v>3.07</v>
       </c>
       <c r="P10" t="n">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.67</v>
+        <v>3.78</v>
       </c>
       <c r="R10" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="S10" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="T10" t="n">
-        <v>3.27</v>
+        <v>3.13</v>
       </c>
       <c r="U10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W10" t="n">
         <v>1.31</v>
       </c>
-      <c r="V10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.35</v>
-      </c>
       <c r="X10" t="n">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.74</v>
+        <v>1.51</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
         <v>3.3</v>
       </c>
       <c r="N11" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="O11" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="P11" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.42</v>
+        <v>3.79</v>
       </c>
       <c r="R11" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S11" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="T11" t="n">
-        <v>3.1</v>
+        <v>3.26</v>
       </c>
       <c r="U11" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="V11" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W11" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="X11" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="M12" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="N12" t="n">
-        <v>2.75</v>
+        <v>3.45</v>
       </c>
       <c r="O12" t="n">
-        <v>3.99</v>
+        <v>2.8</v>
       </c>
       <c r="P12" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.92</v>
+        <v>4.03</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S12" t="n">
-        <v>2.41</v>
+        <v>2.58</v>
       </c>
       <c r="T12" t="n">
-        <v>3.4</v>
+        <v>3.19</v>
       </c>
       <c r="U12" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="V12" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W12" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="X12" t="n">
-        <v>2.45</v>
+        <v>2.78</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.09</v>
+        <v>1.85</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.68</v>
+        <v>1.84</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.32</v>
+        <v>1.6</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2084,65 +2084,65 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45905.58333333334</v>
+        <v>45905.5625</v>
       </c>
     </row>
     <row r="15">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Real Betis II</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gimnàstic de Tarragona</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,37 +2346,37 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O15" t="n">
-        <v>3.44</v>
+        <v>2.6</v>
       </c>
       <c r="P15" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.18</v>
+        <v>4.67</v>
       </c>
       <c r="R15" t="n">
         <v>1.45</v>
       </c>
       <c r="S15" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="T15" t="n">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="U15" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="V15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W15" t="n">
         <v>1.35</v>
@@ -2385,22 +2385,22 @@
         <v>2.74</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AA15" t="n">
-        <v>4.1</v>
+        <v>3.78</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.4</v>
+        <v>1.74</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45905.59375</v>
+        <v>45905.5625</v>
       </c>
     </row>
     <row r="16">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.87</v>
+        <v>3.05</v>
       </c>
       <c r="M16" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>3.89</v>
+        <v>2.25</v>
       </c>
       <c r="O16" t="n">
-        <v>2.3</v>
+        <v>3.41</v>
       </c>
       <c r="P16" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.11</v>
+        <v>2.95</v>
       </c>
       <c r="R16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W16" t="n">
         <v>1.39</v>
       </c>
-      <c r="S16" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.32</v>
-      </c>
       <c r="X16" t="n">
-        <v>3.25</v>
+        <v>2.78</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.55</v>
+        <v>3.88</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>1.31</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.86</v>
+        <v>1.32</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45905.60416666666</v>
+        <v>45905.5625</v>
       </c>
     </row>
     <row r="17">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Real Betis II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Gimnàstic de Tarragona</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>2.12</v>
+        <v>3.46</v>
       </c>
       <c r="P17" t="n">
-        <v>2.56</v>
+        <v>1.95</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.33</v>
+        <v>3.18</v>
       </c>
       <c r="R17" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="S17" t="n">
-        <v>3.5</v>
+        <v>2.52</v>
       </c>
       <c r="T17" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="U17" t="n">
-        <v>1.59</v>
+        <v>1.28</v>
       </c>
       <c r="V17" t="n">
         <v>1.02</v>
       </c>
       <c r="W17" t="n">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="X17" t="n">
-        <v>4.75</v>
+        <v>2.74</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.57</v>
+        <v>2.22</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.31</v>
+        <v>1.59</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.35</v>
+        <v>4.15</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.57</v>
+        <v>1.16</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.55</v>
+        <v>1.88</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.32</v>
+        <v>1.81</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.19</v>
+        <v>1.39</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45905.625</v>
+        <v>45905.59375</v>
       </c>
     </row>
     <row r="18">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45905.625</v>
+        <v>45905.60416666666</v>
       </c>
     </row>
     <row r="19">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2950,27 +2950,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>4.88</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45905.64583333334</v>
+        <v>45905.625</v>
       </c>
     </row>
     <row r="21">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.9</v>
+        <v>3.39</v>
       </c>
       <c r="M21" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="N21" t="n">
-        <v>5.5</v>
+        <v>2.2</v>
       </c>
       <c r="O21" t="n">
-        <v>2.66</v>
+        <v>4.88</v>
       </c>
       <c r="P21" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="Q21" t="n">
-        <v>6.75</v>
+        <v>3.06</v>
       </c>
       <c r="R21" t="n">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="S21" t="n">
-        <v>1.94</v>
+        <v>2.14</v>
       </c>
       <c r="T21" t="n">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="U21" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="V21" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="W21" t="n">
-        <v>1.82</v>
+        <v>1.6</v>
       </c>
       <c r="X21" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="Y21" t="n">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AA21" t="n">
-        <v>8</v>
+        <v>5.55</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.84</v>
+        <v>2.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.36</v>
+        <v>1.54</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.83</v>
+        <v>1.24</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="M22" t="n">
-        <v>4.05</v>
+        <v>2.62</v>
       </c>
       <c r="N22" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.58</v>
+        <v>3.41</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.2</v>
+        <v>1.27</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.2</v>
+        <v>6.65</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.6</v>
+        <v>1.05</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3337,27 +3337,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.82</v>
+        <v>1.6</v>
       </c>
       <c r="M23" t="n">
-        <v>3.2</v>
+        <v>4.05</v>
       </c>
       <c r="N23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z23" t="n">
         <v>2.25</v>
       </c>
-      <c r="O23" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X23" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AA23" t="n">
-        <v>3.13</v>
+        <v>2.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.31</v>
+        <v>1.6</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45905.65625</v>
+        <v>45905.64583333334</v>
       </c>
     </row>
     <row r="24">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.7</v>
+        <v>2.89</v>
       </c>
       <c r="M24" t="n">
-        <v>3.14</v>
+        <v>3.18</v>
       </c>
       <c r="N24" t="n">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="O24" t="n">
-        <v>3.36</v>
+        <v>3.52</v>
       </c>
       <c r="P24" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.12</v>
+        <v>2.85</v>
       </c>
       <c r="R24" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="S24" t="n">
-        <v>2.84</v>
+        <v>2.93</v>
       </c>
       <c r="T24" t="n">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="U24" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V24" t="n">
         <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="X24" t="n">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="Z24" t="n">
         <v>1.85</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.08</v>
+        <v>3.13</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,77 +3636,77 @@
         </is>
       </c>
       <c r="L25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="O25" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="U25" t="n">
         <v>1.5</v>
       </c>
-      <c r="M25" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="N25" t="n">
-        <v>6</v>
-      </c>
-      <c r="O25" t="n">
+      <c r="V25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD25" t="n">
         <v>1.95</v>
       </c>
-      <c r="P25" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>5.79</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W25" t="n">
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH25" t="n">
         <v>1.12</v>
-      </c>
-      <c r="X25" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>2.4</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>5.17</v>
+        <v>3.66</v>
       </c>
       <c r="M26" t="n">
-        <v>4.22</v>
+        <v>3.55</v>
       </c>
       <c r="N26" t="n">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="O26" t="n">
-        <v>5.5</v>
+        <v>3.98</v>
       </c>
       <c r="P26" t="n">
-        <v>2.51</v>
+        <v>2.13</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.05</v>
+        <v>2.34</v>
       </c>
       <c r="R26" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="S26" t="n">
-        <v>3.2</v>
+        <v>2.93</v>
       </c>
       <c r="T26" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="U26" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="V26" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W26" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X26" t="n">
-        <v>3.98</v>
+        <v>3.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.66</v>
+        <v>1.81</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.52</v>
+        <v>3.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>2.3</v>
+        <v>1.24</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>4.11</v>
+        <v>2.67</v>
       </c>
       <c r="M27" t="n">
-        <v>3.4</v>
+        <v>3.02</v>
       </c>
       <c r="N27" t="n">
-        <v>1.77</v>
+        <v>2.42</v>
       </c>
       <c r="O27" t="n">
-        <v>4.25</v>
+        <v>3.05</v>
       </c>
       <c r="P27" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.4</v>
+        <v>2.99</v>
       </c>
       <c r="R27" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S27" t="n">
-        <v>2.93</v>
+        <v>2.84</v>
       </c>
       <c r="T27" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="U27" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V27" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W27" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="X27" t="n">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3982,27 +3982,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45905.66666666666</v>
+        <v>45905.65625</v>
       </c>
     </row>
     <row r="29">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="M29" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="N29" t="n">
-        <v>3.3</v>
+        <v>3.09</v>
       </c>
       <c r="O29" t="n">
-        <v>3.44</v>
+        <v>2.78</v>
       </c>
       <c r="P29" t="n">
-        <v>1.93</v>
+        <v>2.22</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.86</v>
+        <v>3.48</v>
       </c>
       <c r="R29" t="n">
-        <v>1.57</v>
+        <v>1.27</v>
       </c>
       <c r="S29" t="n">
-        <v>2.31</v>
+        <v>3.28</v>
       </c>
       <c r="T29" t="n">
-        <v>3.65</v>
+        <v>2.38</v>
       </c>
       <c r="U29" t="n">
-        <v>1.22</v>
+        <v>1.49</v>
       </c>
       <c r="V29" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="W29" t="n">
-        <v>1.52</v>
+        <v>1.16</v>
       </c>
       <c r="X29" t="n">
-        <v>2.35</v>
+        <v>4.33</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.49</v>
+        <v>1.65</v>
       </c>
       <c r="Z29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AB29" t="n">
         <v>1.42</v>
       </c>
-      <c r="AA29" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AC29" t="n">
-        <v>2.09</v>
+        <v>1.53</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.65</v>
+        <v>2.37</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.48</v>
+        <v>1.64</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,62 +4281,62 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="M30" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O30" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T30" t="n">
         <v>3.55</v>
       </c>
-      <c r="N30" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="O30" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S30" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.38</v>
-      </c>
       <c r="U30" t="n">
-        <v>1.49</v>
+        <v>1.22</v>
       </c>
       <c r="V30" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W30" t="n">
-        <v>1.18</v>
+        <v>1.52</v>
       </c>
       <c r="X30" t="n">
-        <v>4.33</v>
+        <v>2.35</v>
       </c>
       <c r="Y30" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AD30" t="n">
         <v>1.65</v>
       </c>
-      <c r="Z30" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AE30" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.64</v>
+        <v>1.44</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.17</v>
+        <v>1.9</v>
       </c>
       <c r="M33" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="N33" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="O33" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="T33" t="n">
         <v>3.34</v>
       </c>
-      <c r="N33" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O33" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="P33" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S33" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.55</v>
-      </c>
       <c r="U33" t="n">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="V33" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="W33" t="n">
-        <v>1.2</v>
+        <v>1.52</v>
       </c>
       <c r="X33" t="n">
-        <v>3.5</v>
+        <v>2.35</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.77</v>
+        <v>2.34</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.81</v>
+        <v>4.75</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.62</v>
+        <v>2.07</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.15</v>
+        <v>1.68</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>1.34</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="M34" t="n">
-        <v>2.98</v>
+        <v>2.91</v>
       </c>
       <c r="N34" t="n">
-        <v>3.86</v>
+        <v>4.2</v>
       </c>
       <c r="O34" t="n">
-        <v>2.73</v>
+        <v>2.54</v>
       </c>
       <c r="P34" t="n">
-        <v>2.04</v>
+        <v>1.78</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="R34" t="n">
-        <v>1.51</v>
+        <v>1.67</v>
       </c>
       <c r="S34" t="n">
-        <v>2.39</v>
+        <v>2.12</v>
       </c>
       <c r="T34" t="n">
-        <v>3.34</v>
+        <v>4.15</v>
       </c>
       <c r="U34" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="V34" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB34" t="n">
         <v>1.07</v>
       </c>
-      <c r="W34" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="X34" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AC34" t="n">
-        <v>2.07</v>
+        <v>2.57</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.68</v>
+        <v>1.42</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.34</v>
+        <v>1.12</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.72</v>
+        <v>1.96</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.88</v>
+        <v>2.35</v>
       </c>
       <c r="M35" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="N35" t="n">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="O35" t="n">
-        <v>2.65</v>
+        <v>2.81</v>
       </c>
       <c r="P35" t="n">
-        <v>1.85</v>
+        <v>2.11</v>
       </c>
       <c r="Q35" t="n">
-        <v>6</v>
+        <v>3.62</v>
       </c>
       <c r="R35" t="n">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="S35" t="n">
-        <v>2.13</v>
+        <v>2.98</v>
       </c>
       <c r="T35" t="n">
-        <v>4.15</v>
+        <v>2.55</v>
       </c>
       <c r="U35" t="n">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="V35" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="W35" t="n">
-        <v>1.64</v>
+        <v>1.25</v>
       </c>
       <c r="X35" t="n">
-        <v>2.22</v>
+        <v>3.95</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.97</v>
+        <v>1.9</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.37</v>
+        <v>1.8</v>
       </c>
       <c r="AA35" t="n">
-        <v>6.1</v>
+        <v>2.6</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.06</v>
+        <v>1.38</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.57</v>
+        <v>1.62</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.44</v>
+        <v>2.15</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.16</v>
+        <v>3</v>
       </c>
       <c r="M36" t="n">
-        <v>2.69</v>
+        <v>2.51</v>
       </c>
       <c r="N36" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="O36" t="n">
         <v>4.34</v>
@@ -5073,7 +5073,7 @@
         <v>3.38</v>
       </c>
       <c r="R36" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="S36" t="n">
         <v>2.05</v>
@@ -5088,13 +5088,13 @@
         <v>1.12</v>
       </c>
       <c r="W36" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="X36" t="n">
-        <v>2.14</v>
+        <v>1.96</v>
       </c>
       <c r="Y36" t="n">
-        <v>3.41</v>
+        <v>3.34</v>
       </c>
       <c r="Z36" t="n">
         <v>1.28</v>
@@ -5109,7 +5109,7 @@
         <v>2.42</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.35</v>
+        <v>1.72</v>
       </c>
       <c r="M37" t="n">
-        <v>2.75</v>
+        <v>2.96</v>
       </c>
       <c r="N37" t="n">
-        <v>3.22</v>
+        <v>5.17</v>
       </c>
       <c r="O37" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.62</v>
+        <v>2.43</v>
       </c>
       <c r="M38" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="N38" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="O38" t="n">
         <v>3.3</v>
       </c>
-      <c r="N38" t="n">
-        <v>6.02</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5598,7 +5598,7 @@
         <v>2.6</v>
       </c>
       <c r="U40" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="V40" t="n">
         <v>1.03</v>
@@ -5607,7 +5607,7 @@
         <v>1.32</v>
       </c>
       <c r="X40" t="n">
-        <v>3.08</v>
+        <v>3.45</v>
       </c>
       <c r="Y40" t="n">
         <v>2</v>
@@ -5616,7 +5616,7 @@
         <v>1.72</v>
       </c>
       <c r="AA40" t="n">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="AB40" t="n">
         <v>1.25</v>
@@ -5625,7 +5625,7 @@
         <v>1.8</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.71</v>
+        <v>2.35</v>
       </c>
       <c r="M42" t="n">
-        <v>4.12</v>
+        <v>3.5</v>
       </c>
       <c r="N42" t="n">
-        <v>4.6</v>
+        <v>2.7</v>
       </c>
       <c r="O42" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,77 +5958,77 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.35</v>
+        <v>1.65</v>
       </c>
       <c r="M43" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="N43" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O43" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S43" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T43" t="n">
         <v>2.7</v>
       </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" t="n">
-        <v>0</v>
-      </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="Z43" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG43" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AH43" t="n">
         <v>1.95</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>0</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>

--- a/jogos_2025-09-05.xlsx
+++ b/jogos_2025-09-05.xlsx
@@ -757,27 +757,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>45905.5</v>
+        <v>45905.54166666666</v>
       </c>
     </row>
     <row r="4">
@@ -886,7 +886,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>45905.5</v>
+        <v>45905.54166666666</v>
       </c>
     </row>
     <row r="5">
@@ -1015,27 +1015,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45905.5</v>
+        <v>45905.54166666666</v>
       </c>
     </row>
     <row r="6">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45905.5</v>
+        <v>45905.5625</v>
       </c>
     </row>
     <row r="7">
@@ -1273,27 +1273,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="N7" t="n">
-        <v>2.18</v>
+        <v>2.7</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45905.54166666666</v>
+        <v>45905.5625</v>
       </c>
     </row>
     <row r="8">
@@ -1402,27 +1402,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="M8" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N8" t="n">
-        <v>2.55</v>
+        <v>3.45</v>
       </c>
       <c r="O8" t="n">
-        <v>3.72</v>
+        <v>2.8</v>
       </c>
       <c r="P8" t="n">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.68</v>
+        <v>4.03</v>
       </c>
       <c r="R8" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="S8" t="n">
-        <v>2.85</v>
+        <v>2.58</v>
       </c>
       <c r="T8" t="n">
-        <v>2.61</v>
+        <v>3.19</v>
       </c>
       <c r="U8" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="V8" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W8" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="X8" t="n">
-        <v>3.42</v>
+        <v>2.78</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.92</v>
+        <v>3.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.28</v>
+        <v>1.6</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45905.54166666666</v>
+        <v>45905.5625</v>
       </c>
     </row>
     <row r="9">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.85</v>
+        <v>1.97</v>
       </c>
       <c r="M9" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N9" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="O9" t="n">
-        <v>3.71</v>
+        <v>2.6</v>
       </c>
       <c r="P9" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.08</v>
+        <v>4.67</v>
       </c>
       <c r="R9" t="n">
         <v>1.45</v>
       </c>
       <c r="S9" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="T9" t="n">
-        <v>2.95</v>
+        <v>3.27</v>
       </c>
       <c r="U9" t="n">
         <v>1.31</v>
       </c>
       <c r="V9" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W9" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X9" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.95</v>
+        <v>3.78</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.36</v>
+        <v>1.74</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,43 +1701,43 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.55</v>
+        <v>3.05</v>
       </c>
       <c r="M10" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N10" t="n">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="O10" t="n">
-        <v>3.07</v>
+        <v>3.41</v>
       </c>
       <c r="P10" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.78</v>
+        <v>2.95</v>
       </c>
       <c r="R10" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S10" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="T10" t="n">
-        <v>3.13</v>
+        <v>3.32</v>
       </c>
       <c r="U10" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W10" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="X10" t="n">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="Y10" t="n">
         <v>2.1</v>
@@ -1746,16 +1746,16 @@
         <v>1.65</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.75</v>
+        <v>3.88</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>1.31</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.51</v>
+        <v>1.32</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="N11" t="n">
-        <v>3.55</v>
+        <v>2.75</v>
       </c>
       <c r="O11" t="n">
-        <v>2.73</v>
+        <v>3.99</v>
       </c>
       <c r="P11" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.79</v>
+        <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="S11" t="n">
-        <v>2.52</v>
+        <v>2.41</v>
       </c>
       <c r="T11" t="n">
-        <v>3.26</v>
+        <v>3.4</v>
       </c>
       <c r="U11" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="V11" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W11" t="n">
-        <v>1.27</v>
+        <v>1.49</v>
       </c>
       <c r="X11" t="n">
-        <v>2.74</v>
+        <v>2.45</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.63</v>
+        <v>1.32</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="M12" t="n">
         <v>3.3</v>
       </c>
       <c r="N12" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="O12" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="P12" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.03</v>
+        <v>3.79</v>
       </c>
       <c r="R12" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S12" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="T12" t="n">
-        <v>3.19</v>
+        <v>3.26</v>
       </c>
       <c r="U12" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="V12" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W12" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="X12" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45905.5625</v>
+        <v>45905.58333333334</v>
       </c>
     </row>
     <row r="15">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Real Betis II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Gimnàstic de Tarragona</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,37 +2346,37 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>2.6</v>
+        <v>3.46</v>
       </c>
       <c r="P15" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.67</v>
+        <v>3.18</v>
       </c>
       <c r="R15" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S15" t="n">
         <v>2.52</v>
       </c>
       <c r="T15" t="n">
-        <v>3.27</v>
+        <v>3.3</v>
       </c>
       <c r="U15" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="V15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W15" t="n">
         <v>1.35</v>
@@ -2385,22 +2385,22 @@
         <v>2.74</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.78</v>
+        <v>4.15</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.74</v>
+        <v>1.39</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45905.5625</v>
+        <v>45905.59375</v>
       </c>
     </row>
     <row r="16">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.05</v>
+        <v>1.87</v>
       </c>
       <c r="M16" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="N16" t="n">
-        <v>2.25</v>
+        <v>3.89</v>
       </c>
       <c r="O16" t="n">
-        <v>3.41</v>
+        <v>2.3</v>
       </c>
       <c r="P16" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.95</v>
+        <v>4.11</v>
       </c>
       <c r="R16" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="S16" t="n">
-        <v>2.52</v>
+        <v>2.88</v>
       </c>
       <c r="T16" t="n">
-        <v>3.32</v>
+        <v>3.07</v>
       </c>
       <c r="U16" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="V16" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="W16" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="X16" t="n">
-        <v>2.78</v>
+        <v>3.2</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.88</v>
+        <v>3.4</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>1.31</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.32</v>
+        <v>1.86</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45905.5625</v>
+        <v>45905.60416666666</v>
       </c>
     </row>
     <row r="17">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Real Betis II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gimnàstic de Tarragona</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,77 +2604,77 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O17" t="n">
-        <v>3.46</v>
+        <v>2.16</v>
       </c>
       <c r="P17" t="n">
-        <v>1.95</v>
+        <v>2.41</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.18</v>
+        <v>4.15</v>
       </c>
       <c r="R17" t="n">
-        <v>1.46</v>
+        <v>1.24</v>
       </c>
       <c r="S17" t="n">
-        <v>2.52</v>
+        <v>3.5</v>
       </c>
       <c r="T17" t="n">
-        <v>3.3</v>
+        <v>2.27</v>
       </c>
       <c r="U17" t="n">
-        <v>1.28</v>
+        <v>1.59</v>
       </c>
       <c r="V17" t="n">
         <v>1.02</v>
       </c>
       <c r="W17" t="n">
-        <v>1.35</v>
+        <v>1.12</v>
       </c>
       <c r="X17" t="n">
-        <v>2.74</v>
+        <v>4.75</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.22</v>
+        <v>1.49</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.59</v>
+        <v>2.31</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.15</v>
+        <v>2.28</v>
       </c>
       <c r="AB17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
         <v>1.16</v>
       </c>
-      <c r="AC17" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AH17" t="n">
-        <v>1.39</v>
+        <v>2.15</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45905.59375</v>
+        <v>45905.625</v>
       </c>
     </row>
     <row r="18">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t